--- a/光伏配储项目/电价数据/2026/济海站.xlsx
+++ b/光伏配储项目/电价数据/2026/济海站.xlsx
@@ -16,10 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="yyyy/mm/dd"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -64,7 +63,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -430,13 +429,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CS116"/>
+  <dimension ref="A1:CS143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>日期</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -34613,6 +34612,7917 @@
       </c>
       <c r="CS116" t="n">
         <v>0.75574</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="n">
+        <v>46138</v>
+      </c>
+      <c r="B117" t="n">
+        <v>0.38461</v>
+      </c>
+      <c r="C117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="D117" t="n">
+        <v>0.84537</v>
+      </c>
+      <c r="E117" t="n">
+        <v>0.5919500000000001</v>
+      </c>
+      <c r="F117" t="n">
+        <v>0.72401</v>
+      </c>
+      <c r="G117" t="n">
+        <v>1.10025</v>
+      </c>
+      <c r="H117" t="n">
+        <v>0.44222</v>
+      </c>
+      <c r="I117" t="n">
+        <v>0.45981</v>
+      </c>
+      <c r="J117" t="n">
+        <v>0.43194</v>
+      </c>
+      <c r="K117" t="n">
+        <v>0.42662</v>
+      </c>
+      <c r="L117" t="n">
+        <v>0.42495</v>
+      </c>
+      <c r="M117" t="n">
+        <v>0.41289</v>
+      </c>
+      <c r="N117" t="n">
+        <v>0.4005</v>
+      </c>
+      <c r="O117" t="n">
+        <v>0.39995</v>
+      </c>
+      <c r="P117" t="n">
+        <v>0.3878</v>
+      </c>
+      <c r="Q117" t="n">
+        <v>0.40475</v>
+      </c>
+      <c r="R117" t="n">
+        <v>0.4281</v>
+      </c>
+      <c r="S117" t="n">
+        <v>0.41669</v>
+      </c>
+      <c r="T117" t="n">
+        <v>0.35566</v>
+      </c>
+      <c r="U117" t="n">
+        <v>0.39471</v>
+      </c>
+      <c r="V117" t="n">
+        <v>0.38786</v>
+      </c>
+      <c r="W117" t="n">
+        <v>0.42055</v>
+      </c>
+      <c r="X117" t="n">
+        <v>0.39512</v>
+      </c>
+      <c r="Y117" t="n">
+        <v>0.42443</v>
+      </c>
+      <c r="Z117" t="n">
+        <v>0.41746</v>
+      </c>
+      <c r="AA117" t="n">
+        <v>0.42762</v>
+      </c>
+      <c r="AB117" t="n">
+        <v>0.41519</v>
+      </c>
+      <c r="AC117" t="n">
+        <v>0.44739</v>
+      </c>
+      <c r="AD117" t="n">
+        <v>0.502</v>
+      </c>
+      <c r="AE117" t="n">
+        <v>0.30002</v>
+      </c>
+      <c r="AF117" t="n">
+        <v>0.40085</v>
+      </c>
+      <c r="AG117" t="n">
+        <v>0.30827</v>
+      </c>
+      <c r="AH117" t="n">
+        <v>0.31177</v>
+      </c>
+      <c r="AI117" t="n">
+        <v>0.32796</v>
+      </c>
+      <c r="AJ117" t="n">
+        <v>0.35114</v>
+      </c>
+      <c r="AK117" t="n">
+        <v>0.37445</v>
+      </c>
+      <c r="AL117" t="n">
+        <v>0.32286</v>
+      </c>
+      <c r="AM117" t="n">
+        <v>0.34943</v>
+      </c>
+      <c r="AN117" t="n">
+        <v>0.12566</v>
+      </c>
+      <c r="AO117" t="n">
+        <v>0.13822</v>
+      </c>
+      <c r="AP117" t="n">
+        <v>0.33252</v>
+      </c>
+      <c r="AQ117" t="n">
+        <v>0.14387</v>
+      </c>
+      <c r="AR117" t="n">
+        <v>0.07778</v>
+      </c>
+      <c r="AS117" t="n">
+        <v>0.11712</v>
+      </c>
+      <c r="AT117" t="n">
+        <v>0.46035</v>
+      </c>
+      <c r="AU117" t="n">
+        <v>0.20116</v>
+      </c>
+      <c r="AV117" t="n">
+        <v>0.31098</v>
+      </c>
+      <c r="AW117" t="n">
+        <v>0.28744</v>
+      </c>
+      <c r="AX117" t="n">
+        <v>0.05156</v>
+      </c>
+      <c r="AY117" t="n">
+        <v>0.8475499999999999</v>
+      </c>
+      <c r="AZ117" t="n">
+        <v>1.3305</v>
+      </c>
+      <c r="BA117" t="n">
+        <v>0.14831</v>
+      </c>
+      <c r="BB117" t="n">
+        <v>0.21988</v>
+      </c>
+      <c r="BC117" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="BD117" t="n">
+        <v>0.23538</v>
+      </c>
+      <c r="BE117" t="n">
+        <v>0.2192</v>
+      </c>
+      <c r="BF117" t="n">
+        <v>0.7501100000000001</v>
+      </c>
+      <c r="BG117" t="n">
+        <v>0.25837</v>
+      </c>
+      <c r="BH117" t="n">
+        <v>0.44165</v>
+      </c>
+      <c r="BI117" t="n">
+        <v>0.15181</v>
+      </c>
+      <c r="BJ117" t="n">
+        <v>0.33551</v>
+      </c>
+      <c r="BK117" t="n">
+        <v>0.34908</v>
+      </c>
+      <c r="BL117" t="n">
+        <v>0.29087</v>
+      </c>
+      <c r="BM117" t="n">
+        <v>0.29223</v>
+      </c>
+      <c r="BN117" t="n">
+        <v>0.46494</v>
+      </c>
+      <c r="BO117" t="n">
+        <v>0.63539</v>
+      </c>
+      <c r="BP117" t="n">
+        <v>0.7272999999999999</v>
+      </c>
+      <c r="BQ117" t="n">
+        <v>0.9712799999999999</v>
+      </c>
+      <c r="BR117" t="n">
+        <v>0.7310599999999999</v>
+      </c>
+      <c r="BS117" t="n">
+        <v>1.67941</v>
+      </c>
+      <c r="BT117" t="n">
+        <v>0.39449</v>
+      </c>
+      <c r="BU117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BV117" t="n">
+        <v>0.43133</v>
+      </c>
+      <c r="BW117" t="n">
+        <v>0.43643</v>
+      </c>
+      <c r="BX117" t="n">
+        <v>0.65813</v>
+      </c>
+      <c r="BY117" t="n">
+        <v>1.3205</v>
+      </c>
+      <c r="BZ117" t="n">
+        <v>0.92833</v>
+      </c>
+      <c r="CA117" t="n">
+        <v>1.65724</v>
+      </c>
+      <c r="CB117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CC117" t="n">
+        <v>1.50479</v>
+      </c>
+      <c r="CD117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CE117" t="n">
+        <v>1.73757</v>
+      </c>
+      <c r="CF117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CG117" t="n">
+        <v>0.8965299999999999</v>
+      </c>
+      <c r="CH117" t="n">
+        <v>1.13986</v>
+      </c>
+      <c r="CI117" t="n">
+        <v>1.19605</v>
+      </c>
+      <c r="CJ117" t="n">
+        <v>1.65538</v>
+      </c>
+      <c r="CK117" t="n">
+        <v>1.26052</v>
+      </c>
+      <c r="CL117" t="n">
+        <v>0.86983</v>
+      </c>
+      <c r="CM117" t="n">
+        <v>0.79634</v>
+      </c>
+      <c r="CN117" t="n">
+        <v>0.75693</v>
+      </c>
+      <c r="CO117" t="n">
+        <v>0.51795</v>
+      </c>
+      <c r="CP117" t="n">
+        <v>0.47938</v>
+      </c>
+      <c r="CQ117" t="n">
+        <v>0.46939</v>
+      </c>
+      <c r="CR117" t="n">
+        <v>0.41566</v>
+      </c>
+      <c r="CS117" t="n">
+        <v>0.4253</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="n">
+        <v>46139</v>
+      </c>
+      <c r="B118" t="n">
+        <v>0.32887</v>
+      </c>
+      <c r="C118" t="n">
+        <v>0.70809</v>
+      </c>
+      <c r="D118" t="n">
+        <v>1.76579</v>
+      </c>
+      <c r="E118" t="n">
+        <v>0.87018</v>
+      </c>
+      <c r="F118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="G118" t="n">
+        <v>0.9145399999999999</v>
+      </c>
+      <c r="H118" t="n">
+        <v>0.49383</v>
+      </c>
+      <c r="I118" t="n">
+        <v>0.5143</v>
+      </c>
+      <c r="J118" t="n">
+        <v>0.5022799999999999</v>
+      </c>
+      <c r="K118" t="n">
+        <v>0.50252</v>
+      </c>
+      <c r="L118" t="n">
+        <v>0.4848</v>
+      </c>
+      <c r="M118" t="n">
+        <v>0.39921</v>
+      </c>
+      <c r="N118" t="n">
+        <v>0.46695</v>
+      </c>
+      <c r="O118" t="n">
+        <v>0.37795</v>
+      </c>
+      <c r="P118" t="n">
+        <v>0.37803</v>
+      </c>
+      <c r="Q118" t="n">
+        <v>0.37737</v>
+      </c>
+      <c r="R118" t="n">
+        <v>0.33621</v>
+      </c>
+      <c r="S118" t="n">
+        <v>0.36576</v>
+      </c>
+      <c r="T118" t="n">
+        <v>0.35119</v>
+      </c>
+      <c r="U118" t="n">
+        <v>0.35112</v>
+      </c>
+      <c r="V118" t="n">
+        <v>0.36336</v>
+      </c>
+      <c r="W118" t="n">
+        <v>0.36715</v>
+      </c>
+      <c r="X118" t="n">
+        <v>0.35061</v>
+      </c>
+      <c r="Y118" t="n">
+        <v>0.37332</v>
+      </c>
+      <c r="Z118" t="n">
+        <v>0.40679</v>
+      </c>
+      <c r="AA118" t="n">
+        <v>0.86705</v>
+      </c>
+      <c r="AB118" t="n">
+        <v>0.71058</v>
+      </c>
+      <c r="AC118" t="n">
+        <v>0.80588</v>
+      </c>
+      <c r="AD118" t="n">
+        <v>0.45495</v>
+      </c>
+      <c r="AE118" t="n">
+        <v>0.43587</v>
+      </c>
+      <c r="AF118" t="n">
+        <v>0.37696</v>
+      </c>
+      <c r="AG118" t="n">
+        <v>0.34746</v>
+      </c>
+      <c r="AH118" t="n">
+        <v>0.38705</v>
+      </c>
+      <c r="AI118" t="n">
+        <v>0.42662</v>
+      </c>
+      <c r="AJ118" t="n">
+        <v>0.5087699999999999</v>
+      </c>
+      <c r="AK118" t="n">
+        <v>0.3563</v>
+      </c>
+      <c r="AL118" t="n">
+        <v>0.33954</v>
+      </c>
+      <c r="AM118" t="n">
+        <v>0.3567</v>
+      </c>
+      <c r="AN118" t="n">
+        <v>0.33264</v>
+      </c>
+      <c r="AO118" t="n">
+        <v>0.32911</v>
+      </c>
+      <c r="AP118" t="n">
+        <v>0.37279</v>
+      </c>
+      <c r="AQ118" t="n">
+        <v>0.30221</v>
+      </c>
+      <c r="AR118" t="n">
+        <v>0.33216</v>
+      </c>
+      <c r="AS118" t="n">
+        <v>0.34044</v>
+      </c>
+      <c r="AT118" t="n">
+        <v>0.3752</v>
+      </c>
+      <c r="AU118" t="n">
+        <v>0.50883</v>
+      </c>
+      <c r="AV118" t="n">
+        <v>0.7805299999999999</v>
+      </c>
+      <c r="AW118" t="n">
+        <v>0.99487</v>
+      </c>
+      <c r="AX118" t="n">
+        <v>0.33353</v>
+      </c>
+      <c r="AY118" t="n">
+        <v>0.52585</v>
+      </c>
+      <c r="AZ118" t="n">
+        <v>0.89562</v>
+      </c>
+      <c r="BA118" t="n">
+        <v>0.8508</v>
+      </c>
+      <c r="BB118" t="n">
+        <v>0.50107</v>
+      </c>
+      <c r="BC118" t="n">
+        <v>0.72719</v>
+      </c>
+      <c r="BD118" t="n">
+        <v>1.40477</v>
+      </c>
+      <c r="BE118" t="n">
+        <v>1.08843</v>
+      </c>
+      <c r="BF118" t="n">
+        <v>1.0338</v>
+      </c>
+      <c r="BG118" t="n">
+        <v>0.29536</v>
+      </c>
+      <c r="BH118" t="n">
+        <v>0.35197</v>
+      </c>
+      <c r="BI118" t="n">
+        <v>0.37511</v>
+      </c>
+      <c r="BJ118" t="n">
+        <v>0.4728</v>
+      </c>
+      <c r="BK118" t="n">
+        <v>0.54692</v>
+      </c>
+      <c r="BL118" t="n">
+        <v>0.49996</v>
+      </c>
+      <c r="BM118" t="n">
+        <v>0.5249299999999999</v>
+      </c>
+      <c r="BN118" t="n">
+        <v>0.90598</v>
+      </c>
+      <c r="BO118" t="n">
+        <v>0.6250399999999999</v>
+      </c>
+      <c r="BP118" t="n">
+        <v>0.8932599999999999</v>
+      </c>
+      <c r="BQ118" t="n">
+        <v>1.1585</v>
+      </c>
+      <c r="BR118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BS118" t="n">
+        <v>1.42638</v>
+      </c>
+      <c r="BT118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BU118" t="n">
+        <v>1.18101</v>
+      </c>
+      <c r="BV118" t="n">
+        <v>1.03814</v>
+      </c>
+      <c r="BW118" t="n">
+        <v>1.47257</v>
+      </c>
+      <c r="BX118" t="n">
+        <v>1.37473</v>
+      </c>
+      <c r="BY118" t="n">
+        <v>1.53014</v>
+      </c>
+      <c r="BZ118" t="n">
+        <v>1.30919</v>
+      </c>
+      <c r="CA118" t="n">
+        <v>1.3597</v>
+      </c>
+      <c r="CB118" t="n">
+        <v>0.91603</v>
+      </c>
+      <c r="CC118" t="n">
+        <v>1.25213</v>
+      </c>
+      <c r="CD118" t="n">
+        <v>0.90147</v>
+      </c>
+      <c r="CE118" t="n">
+        <v>1.31372</v>
+      </c>
+      <c r="CF118" t="n">
+        <v>1.35531</v>
+      </c>
+      <c r="CG118" t="n">
+        <v>1.24431</v>
+      </c>
+      <c r="CH118" t="n">
+        <v>1.03946</v>
+      </c>
+      <c r="CI118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CJ118" t="n">
+        <v>0.45019</v>
+      </c>
+      <c r="CK118" t="n">
+        <v>0.78869</v>
+      </c>
+      <c r="CL118" t="n">
+        <v>0.80855</v>
+      </c>
+      <c r="CM118" t="n">
+        <v>0.44889</v>
+      </c>
+      <c r="CN118" t="n">
+        <v>0.42805</v>
+      </c>
+      <c r="CO118" t="n">
+        <v>0.44356</v>
+      </c>
+      <c r="CP118" t="n">
+        <v>0.33361</v>
+      </c>
+      <c r="CQ118" t="n">
+        <v>0.37558</v>
+      </c>
+      <c r="CR118" t="n">
+        <v>0.35465</v>
+      </c>
+      <c r="CS118" t="n">
+        <v>0.33459</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="n">
+        <v>46140</v>
+      </c>
+      <c r="B119" t="n">
+        <v>0.32142</v>
+      </c>
+      <c r="C119" t="n">
+        <v>0.50746</v>
+      </c>
+      <c r="D119" t="n">
+        <v>0.48639</v>
+      </c>
+      <c r="E119" t="n">
+        <v>0.48723</v>
+      </c>
+      <c r="F119" t="n">
+        <v>0.37909</v>
+      </c>
+      <c r="G119" t="n">
+        <v>0.44803</v>
+      </c>
+      <c r="H119" t="n">
+        <v>0.41411</v>
+      </c>
+      <c r="I119" t="n">
+        <v>0.36861</v>
+      </c>
+      <c r="J119" t="n">
+        <v>0.3891</v>
+      </c>
+      <c r="K119" t="n">
+        <v>0.38261</v>
+      </c>
+      <c r="L119" t="n">
+        <v>0.36305</v>
+      </c>
+      <c r="M119" t="n">
+        <v>0.42748</v>
+      </c>
+      <c r="N119" t="n">
+        <v>0.44289</v>
+      </c>
+      <c r="O119" t="n">
+        <v>0.33568</v>
+      </c>
+      <c r="P119" t="n">
+        <v>0.36996</v>
+      </c>
+      <c r="Q119" t="n">
+        <v>0.39536</v>
+      </c>
+      <c r="R119" t="n">
+        <v>0.36677</v>
+      </c>
+      <c r="S119" t="n">
+        <v>0.36765</v>
+      </c>
+      <c r="T119" t="n">
+        <v>0.35556</v>
+      </c>
+      <c r="U119" t="n">
+        <v>0.36103</v>
+      </c>
+      <c r="V119" t="n">
+        <v>0.35161</v>
+      </c>
+      <c r="W119" t="n">
+        <v>0.36284</v>
+      </c>
+      <c r="X119" t="n">
+        <v>0.35696</v>
+      </c>
+      <c r="Y119" t="n">
+        <v>0.3832</v>
+      </c>
+      <c r="Z119" t="n">
+        <v>0.39491</v>
+      </c>
+      <c r="AA119" t="n">
+        <v>0.47183</v>
+      </c>
+      <c r="AB119" t="n">
+        <v>0.44381</v>
+      </c>
+      <c r="AC119" t="n">
+        <v>0.43768</v>
+      </c>
+      <c r="AD119" t="n">
+        <v>0.34727</v>
+      </c>
+      <c r="AE119" t="n">
+        <v>0.39416</v>
+      </c>
+      <c r="AF119" t="n">
+        <v>0.35268</v>
+      </c>
+      <c r="AG119" t="n">
+        <v>0.36726</v>
+      </c>
+      <c r="AH119" t="n">
+        <v>0.34736</v>
+      </c>
+      <c r="AI119" t="n">
+        <v>0.45329</v>
+      </c>
+      <c r="AJ119" t="n">
+        <v>0.57438</v>
+      </c>
+      <c r="AK119" t="n">
+        <v>0.77862</v>
+      </c>
+      <c r="AL119" t="n">
+        <v>0.72603</v>
+      </c>
+      <c r="AM119" t="n">
+        <v>0.65895</v>
+      </c>
+      <c r="AN119" t="n">
+        <v>0.24253</v>
+      </c>
+      <c r="AO119" t="n">
+        <v>0.37847</v>
+      </c>
+      <c r="AP119" t="n">
+        <v>0.36809</v>
+      </c>
+      <c r="AQ119" t="n">
+        <v>0.33122</v>
+      </c>
+      <c r="AR119" t="n">
+        <v>0.36844</v>
+      </c>
+      <c r="AS119" t="n">
+        <v>0.39862</v>
+      </c>
+      <c r="AT119" t="n">
+        <v>0.41256</v>
+      </c>
+      <c r="AU119" t="n">
+        <v>0.55884</v>
+      </c>
+      <c r="AV119" t="n">
+        <v>0.50156</v>
+      </c>
+      <c r="AW119" t="n">
+        <v>0.82623</v>
+      </c>
+      <c r="AX119" t="n">
+        <v>0.39888</v>
+      </c>
+      <c r="AY119" t="n">
+        <v>0.59657</v>
+      </c>
+      <c r="AZ119" t="n">
+        <v>0.72764</v>
+      </c>
+      <c r="BA119" t="n">
+        <v>0.81565</v>
+      </c>
+      <c r="BB119" t="n">
+        <v>0.5311900000000001</v>
+      </c>
+      <c r="BC119" t="n">
+        <v>0.5398200000000001</v>
+      </c>
+      <c r="BD119" t="n">
+        <v>0.80116</v>
+      </c>
+      <c r="BE119" t="n">
+        <v>1.12886</v>
+      </c>
+      <c r="BF119" t="n">
+        <v>0.6774600000000001</v>
+      </c>
+      <c r="BG119" t="n">
+        <v>0.60134</v>
+      </c>
+      <c r="BH119" t="n">
+        <v>0.49403</v>
+      </c>
+      <c r="BI119" t="n">
+        <v>0.45093</v>
+      </c>
+      <c r="BJ119" t="n">
+        <v>0.42529</v>
+      </c>
+      <c r="BK119" t="n">
+        <v>0.39551</v>
+      </c>
+      <c r="BL119" t="n">
+        <v>0.72092</v>
+      </c>
+      <c r="BM119" t="n">
+        <v>0.5161100000000001</v>
+      </c>
+      <c r="BN119" t="n">
+        <v>0.50551</v>
+      </c>
+      <c r="BO119" t="n">
+        <v>0.57045</v>
+      </c>
+      <c r="BP119" t="n">
+        <v>0.5960599999999999</v>
+      </c>
+      <c r="BQ119" t="n">
+        <v>0.54479</v>
+      </c>
+      <c r="BR119" t="n">
+        <v>0.56479</v>
+      </c>
+      <c r="BS119" t="n">
+        <v>1.2642</v>
+      </c>
+      <c r="BT119" t="n">
+        <v>0.61609</v>
+      </c>
+      <c r="BU119" t="n">
+        <v>1.20173</v>
+      </c>
+      <c r="BV119" t="n">
+        <v>0.50571</v>
+      </c>
+      <c r="BW119" t="n">
+        <v>0.5259299999999999</v>
+      </c>
+      <c r="BX119" t="n">
+        <v>0.56598</v>
+      </c>
+      <c r="BY119" t="n">
+        <v>0.8688400000000001</v>
+      </c>
+      <c r="BZ119" t="n">
+        <v>0.9028999999999999</v>
+      </c>
+      <c r="CA119" t="n">
+        <v>1.41997</v>
+      </c>
+      <c r="CB119" t="n">
+        <v>0.70198</v>
+      </c>
+      <c r="CC119" t="n">
+        <v>0.7307</v>
+      </c>
+      <c r="CD119" t="n">
+        <v>0.59617</v>
+      </c>
+      <c r="CE119" t="n">
+        <v>0.7890499999999999</v>
+      </c>
+      <c r="CF119" t="n">
+        <v>0.6099</v>
+      </c>
+      <c r="CG119" t="n">
+        <v>0.82914</v>
+      </c>
+      <c r="CH119" t="n">
+        <v>0.5627000000000001</v>
+      </c>
+      <c r="CI119" t="n">
+        <v>1.14238</v>
+      </c>
+      <c r="CJ119" t="n">
+        <v>0.80174</v>
+      </c>
+      <c r="CK119" t="n">
+        <v>0.56059</v>
+      </c>
+      <c r="CL119" t="n">
+        <v>0.48383</v>
+      </c>
+      <c r="CM119" t="n">
+        <v>0.6174700000000001</v>
+      </c>
+      <c r="CN119" t="n">
+        <v>0.4996</v>
+      </c>
+      <c r="CO119" t="n">
+        <v>0.45662</v>
+      </c>
+      <c r="CP119" t="n">
+        <v>0.39737</v>
+      </c>
+      <c r="CQ119" t="n">
+        <v>0.36206</v>
+      </c>
+      <c r="CR119" t="n">
+        <v>0.34848</v>
+      </c>
+      <c r="CS119" t="n">
+        <v>0.34194</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="n">
+        <v>46141</v>
+      </c>
+      <c r="B120" t="n">
+        <v>0.31894</v>
+      </c>
+      <c r="C120" t="n">
+        <v>0.52252</v>
+      </c>
+      <c r="D120" t="n">
+        <v>0.49312</v>
+      </c>
+      <c r="E120" t="n">
+        <v>0.44519</v>
+      </c>
+      <c r="F120" t="n">
+        <v>0.38904</v>
+      </c>
+      <c r="G120" t="n">
+        <v>0.38908</v>
+      </c>
+      <c r="H120" t="n">
+        <v>0.42335</v>
+      </c>
+      <c r="I120" t="n">
+        <v>0.36687</v>
+      </c>
+      <c r="J120" t="n">
+        <v>0.35876</v>
+      </c>
+      <c r="K120" t="n">
+        <v>0.38714</v>
+      </c>
+      <c r="L120" t="n">
+        <v>0.38532</v>
+      </c>
+      <c r="M120" t="n">
+        <v>0.36111</v>
+      </c>
+      <c r="N120" t="n">
+        <v>0.44847</v>
+      </c>
+      <c r="O120" t="n">
+        <v>0.35962</v>
+      </c>
+      <c r="P120" t="n">
+        <v>0.34835</v>
+      </c>
+      <c r="Q120" t="n">
+        <v>0.36269</v>
+      </c>
+      <c r="R120" t="n">
+        <v>0.35721</v>
+      </c>
+      <c r="S120" t="n">
+        <v>0.35828</v>
+      </c>
+      <c r="T120" t="n">
+        <v>0.33728</v>
+      </c>
+      <c r="U120" t="n">
+        <v>0.3348</v>
+      </c>
+      <c r="V120" t="n">
+        <v>0.33137</v>
+      </c>
+      <c r="W120" t="n">
+        <v>0.33393</v>
+      </c>
+      <c r="X120" t="n">
+        <v>0.33126</v>
+      </c>
+      <c r="Y120" t="n">
+        <v>0.34997</v>
+      </c>
+      <c r="Z120" t="n">
+        <v>0.33888</v>
+      </c>
+      <c r="AA120" t="n">
+        <v>0.35098</v>
+      </c>
+      <c r="AB120" t="n">
+        <v>0.38486</v>
+      </c>
+      <c r="AC120" t="n">
+        <v>0.38839</v>
+      </c>
+      <c r="AD120" t="n">
+        <v>0.34829</v>
+      </c>
+      <c r="AE120" t="n">
+        <v>0.3745</v>
+      </c>
+      <c r="AF120" t="n">
+        <v>0.34385</v>
+      </c>
+      <c r="AG120" t="n">
+        <v>0.39305</v>
+      </c>
+      <c r="AH120" t="n">
+        <v>0.41561</v>
+      </c>
+      <c r="AI120" t="n">
+        <v>0.49445</v>
+      </c>
+      <c r="AJ120" t="n">
+        <v>0.35628</v>
+      </c>
+      <c r="AK120" t="n">
+        <v>0.65013</v>
+      </c>
+      <c r="AL120" t="n">
+        <v>0.3404</v>
+      </c>
+      <c r="AM120" t="n">
+        <v>0.54698</v>
+      </c>
+      <c r="AN120" t="n">
+        <v>0.72234</v>
+      </c>
+      <c r="AO120" t="n">
+        <v>0.9563400000000001</v>
+      </c>
+      <c r="AP120" t="n">
+        <v>0.6692100000000001</v>
+      </c>
+      <c r="AQ120" t="n">
+        <v>0.73362</v>
+      </c>
+      <c r="AR120" t="n">
+        <v>1.10301</v>
+      </c>
+      <c r="AS120" t="n">
+        <v>0.5793400000000001</v>
+      </c>
+      <c r="AT120" t="n">
+        <v>1.21846</v>
+      </c>
+      <c r="AU120" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AV120" t="n">
+        <v>1.05903</v>
+      </c>
+      <c r="AW120" t="n">
+        <v>0.96999</v>
+      </c>
+      <c r="AX120" t="n">
+        <v>0.7664299999999999</v>
+      </c>
+      <c r="AY120" t="n">
+        <v>1.19227</v>
+      </c>
+      <c r="AZ120" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BA120" t="n">
+        <v>0.79659</v>
+      </c>
+      <c r="BB120" t="n">
+        <v>0.35098</v>
+      </c>
+      <c r="BC120" t="n">
+        <v>0.35661</v>
+      </c>
+      <c r="BD120" t="n">
+        <v>0.44571</v>
+      </c>
+      <c r="BE120" t="n">
+        <v>0.60305</v>
+      </c>
+      <c r="BF120" t="n">
+        <v>0.40263</v>
+      </c>
+      <c r="BG120" t="n">
+        <v>0.33791</v>
+      </c>
+      <c r="BH120" t="n">
+        <v>0.3213</v>
+      </c>
+      <c r="BI120" t="n">
+        <v>0.34818</v>
+      </c>
+      <c r="BJ120" t="n">
+        <v>0.4809</v>
+      </c>
+      <c r="BK120" t="n">
+        <v>0.40526</v>
+      </c>
+      <c r="BL120" t="n">
+        <v>0.39831</v>
+      </c>
+      <c r="BM120" t="n">
+        <v>0.7447999999999999</v>
+      </c>
+      <c r="BN120" t="n">
+        <v>0.7534299999999999</v>
+      </c>
+      <c r="BO120" t="n">
+        <v>0.67486</v>
+      </c>
+      <c r="BP120" t="n">
+        <v>1.16798</v>
+      </c>
+      <c r="BQ120" t="n">
+        <v>1.16387</v>
+      </c>
+      <c r="BR120" t="n">
+        <v>0.42671</v>
+      </c>
+      <c r="BS120" t="n">
+        <v>0.49435</v>
+      </c>
+      <c r="BT120" t="n">
+        <v>0.45016</v>
+      </c>
+      <c r="BU120" t="n">
+        <v>0.46145</v>
+      </c>
+      <c r="BV120" t="n">
+        <v>0.39946</v>
+      </c>
+      <c r="BW120" t="n">
+        <v>0.47394</v>
+      </c>
+      <c r="BX120" t="n">
+        <v>0.5205</v>
+      </c>
+      <c r="BY120" t="n">
+        <v>0.8927</v>
+      </c>
+      <c r="BZ120" t="n">
+        <v>0.7801900000000001</v>
+      </c>
+      <c r="CA120" t="n">
+        <v>1.17986</v>
+      </c>
+      <c r="CB120" t="n">
+        <v>0.83504</v>
+      </c>
+      <c r="CC120" t="n">
+        <v>0.75398</v>
+      </c>
+      <c r="CD120" t="n">
+        <v>0.50037</v>
+      </c>
+      <c r="CE120" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="CF120" t="n">
+        <v>0.6493099999999999</v>
+      </c>
+      <c r="CG120" t="n">
+        <v>0.57097</v>
+      </c>
+      <c r="CH120" t="n">
+        <v>0.41552</v>
+      </c>
+      <c r="CI120" t="n">
+        <v>0.48489</v>
+      </c>
+      <c r="CJ120" t="n">
+        <v>0.48749</v>
+      </c>
+      <c r="CK120" t="n">
+        <v>0.34626</v>
+      </c>
+      <c r="CL120" t="n">
+        <v>0.34138</v>
+      </c>
+      <c r="CM120" t="n">
+        <v>0.31904</v>
+      </c>
+      <c r="CN120" t="n">
+        <v>0.32306</v>
+      </c>
+      <c r="CO120" t="n">
+        <v>0.32042</v>
+      </c>
+      <c r="CP120" t="n">
+        <v>0.31415</v>
+      </c>
+      <c r="CQ120" t="n">
+        <v>0.31814</v>
+      </c>
+      <c r="CR120" t="n">
+        <v>0.31996</v>
+      </c>
+      <c r="CS120" t="n">
+        <v>0.31749</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="n">
+        <v>46142</v>
+      </c>
+      <c r="B121" t="n">
+        <v>0.3051</v>
+      </c>
+      <c r="C121" t="n">
+        <v>0.6592899999999999</v>
+      </c>
+      <c r="D121" t="n">
+        <v>0.75219</v>
+      </c>
+      <c r="E121" t="n">
+        <v>0.38238</v>
+      </c>
+      <c r="F121" t="n">
+        <v>0.36141</v>
+      </c>
+      <c r="G121" t="n">
+        <v>0.35901</v>
+      </c>
+      <c r="H121" t="n">
+        <v>0.32931</v>
+      </c>
+      <c r="I121" t="n">
+        <v>0.32811</v>
+      </c>
+      <c r="J121" t="n">
+        <v>0.33232</v>
+      </c>
+      <c r="K121" t="n">
+        <v>0.32079</v>
+      </c>
+      <c r="L121" t="n">
+        <v>0.31905</v>
+      </c>
+      <c r="M121" t="n">
+        <v>0.31613</v>
+      </c>
+      <c r="N121" t="n">
+        <v>0.3189</v>
+      </c>
+      <c r="O121" t="n">
+        <v>0.31848</v>
+      </c>
+      <c r="P121" t="n">
+        <v>0.31515</v>
+      </c>
+      <c r="Q121" t="n">
+        <v>0.31634</v>
+      </c>
+      <c r="R121" t="n">
+        <v>0.3131</v>
+      </c>
+      <c r="S121" t="n">
+        <v>0.31449</v>
+      </c>
+      <c r="T121" t="n">
+        <v>0.31967</v>
+      </c>
+      <c r="U121" t="n">
+        <v>0.3161</v>
+      </c>
+      <c r="V121" t="n">
+        <v>0.3109</v>
+      </c>
+      <c r="W121" t="n">
+        <v>0.31026</v>
+      </c>
+      <c r="X121" t="n">
+        <v>0.3134</v>
+      </c>
+      <c r="Y121" t="n">
+        <v>0.31471</v>
+      </c>
+      <c r="Z121" t="n">
+        <v>0.31646</v>
+      </c>
+      <c r="AA121" t="n">
+        <v>0.32452</v>
+      </c>
+      <c r="AB121" t="n">
+        <v>0.32434</v>
+      </c>
+      <c r="AC121" t="n">
+        <v>0.3326</v>
+      </c>
+      <c r="AD121" t="n">
+        <v>0.32612</v>
+      </c>
+      <c r="AE121" t="n">
+        <v>0.32144</v>
+      </c>
+      <c r="AF121" t="n">
+        <v>0.32291</v>
+      </c>
+      <c r="AG121" t="n">
+        <v>1.32272</v>
+      </c>
+      <c r="AH121" t="n">
+        <v>0.33481</v>
+      </c>
+      <c r="AI121" t="n">
+        <v>0.42827</v>
+      </c>
+      <c r="AJ121" t="n">
+        <v>0.31487</v>
+      </c>
+      <c r="AK121" t="n">
+        <v>0.28649</v>
+      </c>
+      <c r="AL121" t="n">
+        <v>0.3328</v>
+      </c>
+      <c r="AM121" t="n">
+        <v>0.32787</v>
+      </c>
+      <c r="AN121" t="n">
+        <v>0.30755</v>
+      </c>
+      <c r="AO121" t="n">
+        <v>0.31869</v>
+      </c>
+      <c r="AP121" t="n">
+        <v>0.30379</v>
+      </c>
+      <c r="AQ121" t="n">
+        <v>0.30769</v>
+      </c>
+      <c r="AR121" t="n">
+        <v>0.20315</v>
+      </c>
+      <c r="AS121" t="n">
+        <v>0.46151</v>
+      </c>
+      <c r="AT121" t="n">
+        <v>0.43322</v>
+      </c>
+      <c r="AU121" t="n">
+        <v>0.22497</v>
+      </c>
+      <c r="AV121" t="n">
+        <v>0.15747</v>
+      </c>
+      <c r="AW121" t="n">
+        <v>0.29052</v>
+      </c>
+      <c r="AX121" t="n">
+        <v>0.4008</v>
+      </c>
+      <c r="AY121" t="n">
+        <v>0.40908</v>
+      </c>
+      <c r="AZ121" t="n">
+        <v>0.27389</v>
+      </c>
+      <c r="BA121" t="n">
+        <v>0.18953</v>
+      </c>
+      <c r="BB121" t="n">
+        <v>0.53792</v>
+      </c>
+      <c r="BC121" t="n">
+        <v>0.5085299999999999</v>
+      </c>
+      <c r="BD121" t="n">
+        <v>0.05547999999999999</v>
+      </c>
+      <c r="BE121" t="n">
+        <v>0.38342</v>
+      </c>
+      <c r="BF121" t="n">
+        <v>0.38095</v>
+      </c>
+      <c r="BG121" t="n">
+        <v>0.22455</v>
+      </c>
+      <c r="BH121" t="n">
+        <v>0.45835</v>
+      </c>
+      <c r="BI121" t="n">
+        <v>0.21319</v>
+      </c>
+      <c r="BJ121" t="n">
+        <v>0.06390999999999999</v>
+      </c>
+      <c r="BK121" t="n">
+        <v>0.11113</v>
+      </c>
+      <c r="BL121" t="n">
+        <v>0.00446</v>
+      </c>
+      <c r="BM121" t="n">
+        <v>0.00324</v>
+      </c>
+      <c r="BN121" t="n">
+        <v>1.07091</v>
+      </c>
+      <c r="BO121" t="n">
+        <v>0.27217</v>
+      </c>
+      <c r="BP121" t="n">
+        <v>0.29767</v>
+      </c>
+      <c r="BQ121" t="n">
+        <v>0.30001</v>
+      </c>
+      <c r="BR121" t="n">
+        <v>0.30811</v>
+      </c>
+      <c r="BS121" t="n">
+        <v>0.33157</v>
+      </c>
+      <c r="BT121" t="n">
+        <v>0.31965</v>
+      </c>
+      <c r="BU121" t="n">
+        <v>0.31995</v>
+      </c>
+      <c r="BV121" t="n">
+        <v>0.32957</v>
+      </c>
+      <c r="BW121" t="n">
+        <v>0.31546</v>
+      </c>
+      <c r="BX121" t="n">
+        <v>0.33545</v>
+      </c>
+      <c r="BY121" t="n">
+        <v>0.33572</v>
+      </c>
+      <c r="BZ121" t="n">
+        <v>0.33586</v>
+      </c>
+      <c r="CA121" t="n">
+        <v>0.3334</v>
+      </c>
+      <c r="CB121" t="n">
+        <v>0.37656</v>
+      </c>
+      <c r="CC121" t="n">
+        <v>0.38226</v>
+      </c>
+      <c r="CD121" t="n">
+        <v>0.37683</v>
+      </c>
+      <c r="CE121" t="n">
+        <v>0.37104</v>
+      </c>
+      <c r="CF121" t="n">
+        <v>0.35729</v>
+      </c>
+      <c r="CG121" t="n">
+        <v>0.38844</v>
+      </c>
+      <c r="CH121" t="n">
+        <v>0.39171</v>
+      </c>
+      <c r="CI121" t="n">
+        <v>0.40036</v>
+      </c>
+      <c r="CJ121" t="n">
+        <v>0.46066</v>
+      </c>
+      <c r="CK121" t="n">
+        <v>0.37059</v>
+      </c>
+      <c r="CL121" t="n">
+        <v>0.3899</v>
+      </c>
+      <c r="CM121" t="n">
+        <v>0.3915</v>
+      </c>
+      <c r="CN121" t="n">
+        <v>0.48483</v>
+      </c>
+      <c r="CO121" t="n">
+        <v>0.35218</v>
+      </c>
+      <c r="CP121" t="n">
+        <v>0.35663</v>
+      </c>
+      <c r="CQ121" t="n">
+        <v>0.34433</v>
+      </c>
+      <c r="CR121" t="n">
+        <v>0.35381</v>
+      </c>
+      <c r="CS121" t="n">
+        <v>0.34361</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="n">
+        <v>46143</v>
+      </c>
+      <c r="B122" t="n">
+        <v>0.36603</v>
+      </c>
+      <c r="C122" t="n">
+        <v>0.58327</v>
+      </c>
+      <c r="D122" t="n">
+        <v>0.37835</v>
+      </c>
+      <c r="E122" t="n">
+        <v>0.40139</v>
+      </c>
+      <c r="F122" t="n">
+        <v>0.38489</v>
+      </c>
+      <c r="G122" t="n">
+        <v>0.37951</v>
+      </c>
+      <c r="H122" t="n">
+        <v>0.35147</v>
+      </c>
+      <c r="I122" t="n">
+        <v>0.3434</v>
+      </c>
+      <c r="J122" t="n">
+        <v>0.35087</v>
+      </c>
+      <c r="K122" t="n">
+        <v>0.30192</v>
+      </c>
+      <c r="L122" t="n">
+        <v>0.30022</v>
+      </c>
+      <c r="M122" t="n">
+        <v>0.28455</v>
+      </c>
+      <c r="N122" t="n">
+        <v>0.33237</v>
+      </c>
+      <c r="O122" t="n">
+        <v>0.26321</v>
+      </c>
+      <c r="P122" t="n">
+        <v>0.34066</v>
+      </c>
+      <c r="Q122" t="n">
+        <v>0.33757</v>
+      </c>
+      <c r="R122" t="n">
+        <v>0.32849</v>
+      </c>
+      <c r="S122" t="n">
+        <v>0.28244</v>
+      </c>
+      <c r="T122" t="n">
+        <v>0.31219</v>
+      </c>
+      <c r="U122" t="n">
+        <v>0.30901</v>
+      </c>
+      <c r="V122" t="n">
+        <v>0.29408</v>
+      </c>
+      <c r="W122" t="n">
+        <v>0.29145</v>
+      </c>
+      <c r="X122" t="n">
+        <v>0.29004</v>
+      </c>
+      <c r="Y122" t="n">
+        <v>0.32878</v>
+      </c>
+      <c r="Z122" t="n">
+        <v>0.31926</v>
+      </c>
+      <c r="AA122" t="n">
+        <v>0.33271</v>
+      </c>
+      <c r="AB122" t="n">
+        <v>0.34548</v>
+      </c>
+      <c r="AC122" t="n">
+        <v>0.31166</v>
+      </c>
+      <c r="AD122" t="n">
+        <v>0.30536</v>
+      </c>
+      <c r="AE122" t="n">
+        <v>0.10251</v>
+      </c>
+      <c r="AF122" t="n">
+        <v>0.10278</v>
+      </c>
+      <c r="AG122" t="n">
+        <v>0.04358</v>
+      </c>
+      <c r="AH122" t="n">
+        <v>-0.04697999999999999</v>
+      </c>
+      <c r="AI122" t="n">
+        <v>-0.04574</v>
+      </c>
+      <c r="AJ122" t="n">
+        <v>-0.04621</v>
+      </c>
+      <c r="AK122" t="n">
+        <v>-0.0441</v>
+      </c>
+      <c r="AL122" t="n">
+        <v>-0.04621</v>
+      </c>
+      <c r="AM122" t="n">
+        <v>-0.04475</v>
+      </c>
+      <c r="AN122" t="n">
+        <v>-0.04398</v>
+      </c>
+      <c r="AO122" t="n">
+        <v>0.36351</v>
+      </c>
+      <c r="AP122" t="n">
+        <v>0.0162</v>
+      </c>
+      <c r="AQ122" t="n">
+        <v>0.21801</v>
+      </c>
+      <c r="AR122" t="n">
+        <v>0.05514</v>
+      </c>
+      <c r="AS122" t="n">
+        <v>0.29283</v>
+      </c>
+      <c r="AT122" t="n">
+        <v>0.20946</v>
+      </c>
+      <c r="AU122" t="n">
+        <v>0.07368999999999999</v>
+      </c>
+      <c r="AV122" t="n">
+        <v>-0.04392</v>
+      </c>
+      <c r="AW122" t="n">
+        <v>-0.04394</v>
+      </c>
+      <c r="AX122" t="n">
+        <v>-0.04574</v>
+      </c>
+      <c r="AY122" t="n">
+        <v>-0.0456</v>
+      </c>
+      <c r="AZ122" t="n">
+        <v>-0.04561</v>
+      </c>
+      <c r="BA122" t="n">
+        <v>-0.04369</v>
+      </c>
+      <c r="BB122" t="n">
+        <v>-0.04335</v>
+      </c>
+      <c r="BC122" t="n">
+        <v>-0.04549</v>
+      </c>
+      <c r="BD122" t="n">
+        <v>-0.04339</v>
+      </c>
+      <c r="BE122" t="n">
+        <v>0.37679</v>
+      </c>
+      <c r="BF122" t="n">
+        <v>-0.04529</v>
+      </c>
+      <c r="BG122" t="n">
+        <v>-0.04525</v>
+      </c>
+      <c r="BH122" t="n">
+        <v>-0.04538</v>
+      </c>
+      <c r="BI122" t="n">
+        <v>-0.04358</v>
+      </c>
+      <c r="BJ122" t="n">
+        <v>-0.04423</v>
+      </c>
+      <c r="BK122" t="n">
+        <v>0.07215000000000001</v>
+      </c>
+      <c r="BL122" t="n">
+        <v>0.0704</v>
+      </c>
+      <c r="BM122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BN122" t="n">
+        <v>-0.04471</v>
+      </c>
+      <c r="BO122" t="n">
+        <v>-0.04997</v>
+      </c>
+      <c r="BP122" t="n">
+        <v>-0.04984</v>
+      </c>
+      <c r="BQ122" t="n">
+        <v>-0.0474</v>
+      </c>
+      <c r="BR122" t="n">
+        <v>-0.04790999999999999</v>
+      </c>
+      <c r="BS122" t="n">
+        <v>0.19975</v>
+      </c>
+      <c r="BT122" t="n">
+        <v>0.14272</v>
+      </c>
+      <c r="BU122" t="n">
+        <v>0.28994</v>
+      </c>
+      <c r="BV122" t="n">
+        <v>0.29465</v>
+      </c>
+      <c r="BW122" t="n">
+        <v>0.30454</v>
+      </c>
+      <c r="BX122" t="n">
+        <v>0.29982</v>
+      </c>
+      <c r="BY122" t="n">
+        <v>0.29492</v>
+      </c>
+      <c r="BZ122" t="n">
+        <v>0.29282</v>
+      </c>
+      <c r="CA122" t="n">
+        <v>0.29329</v>
+      </c>
+      <c r="CB122" t="n">
+        <v>0.29225</v>
+      </c>
+      <c r="CC122" t="n">
+        <v>0.29678</v>
+      </c>
+      <c r="CD122" t="n">
+        <v>0.29074</v>
+      </c>
+      <c r="CE122" t="n">
+        <v>0.29497</v>
+      </c>
+      <c r="CF122" t="n">
+        <v>0.26875</v>
+      </c>
+      <c r="CG122" t="n">
+        <v>0.29381</v>
+      </c>
+      <c r="CH122" t="n">
+        <v>0.29802</v>
+      </c>
+      <c r="CI122" t="n">
+        <v>0.30855</v>
+      </c>
+      <c r="CJ122" t="n">
+        <v>0.30375</v>
+      </c>
+      <c r="CK122" t="n">
+        <v>0.30221</v>
+      </c>
+      <c r="CL122" t="n">
+        <v>0.31434</v>
+      </c>
+      <c r="CM122" t="n">
+        <v>0.31839</v>
+      </c>
+      <c r="CN122" t="n">
+        <v>0.34712</v>
+      </c>
+      <c r="CO122" t="n">
+        <v>0.34713</v>
+      </c>
+      <c r="CP122" t="n">
+        <v>0.3402</v>
+      </c>
+      <c r="CQ122" t="n">
+        <v>0.36027</v>
+      </c>
+      <c r="CR122" t="n">
+        <v>0.35985</v>
+      </c>
+      <c r="CS122" t="n">
+        <v>0.33114</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="n">
+        <v>46144</v>
+      </c>
+      <c r="B123" t="n">
+        <v>0.32413</v>
+      </c>
+      <c r="C123" t="n">
+        <v>1.31253</v>
+      </c>
+      <c r="D123" t="n">
+        <v>0.31031</v>
+      </c>
+      <c r="E123" t="n">
+        <v>0.39462</v>
+      </c>
+      <c r="F123" t="n">
+        <v>0.34484</v>
+      </c>
+      <c r="G123" t="n">
+        <v>0.32034</v>
+      </c>
+      <c r="H123" t="n">
+        <v>0.30704</v>
+      </c>
+      <c r="I123" t="n">
+        <v>0.31463</v>
+      </c>
+      <c r="J123" t="n">
+        <v>0.30134</v>
+      </c>
+      <c r="K123" t="n">
+        <v>0.28114</v>
+      </c>
+      <c r="L123" t="n">
+        <v>0.29441</v>
+      </c>
+      <c r="M123" t="n">
+        <v>0.29069</v>
+      </c>
+      <c r="N123" t="n">
+        <v>0.28802</v>
+      </c>
+      <c r="O123" t="n">
+        <v>0.28084</v>
+      </c>
+      <c r="P123" t="n">
+        <v>0.27116</v>
+      </c>
+      <c r="Q123" t="n">
+        <v>0.27089</v>
+      </c>
+      <c r="R123" t="n">
+        <v>0.2810299999999999</v>
+      </c>
+      <c r="S123" t="n">
+        <v>0.17236</v>
+      </c>
+      <c r="T123" t="n">
+        <v>0.1586</v>
+      </c>
+      <c r="U123" t="n">
+        <v>0.17092</v>
+      </c>
+      <c r="V123" t="n">
+        <v>0.1477</v>
+      </c>
+      <c r="W123" t="n">
+        <v>0.15943</v>
+      </c>
+      <c r="X123" t="n">
+        <v>0.15858</v>
+      </c>
+      <c r="Y123" t="n">
+        <v>0.23612</v>
+      </c>
+      <c r="Z123" t="n">
+        <v>0.214</v>
+      </c>
+      <c r="AA123" t="n">
+        <v>0.22651</v>
+      </c>
+      <c r="AB123" t="n">
+        <v>0.26883</v>
+      </c>
+      <c r="AC123" t="n">
+        <v>0.28566</v>
+      </c>
+      <c r="AD123" t="n">
+        <v>0.29075</v>
+      </c>
+      <c r="AE123" t="n">
+        <v>0.31932</v>
+      </c>
+      <c r="AF123" t="n">
+        <v>0.28069</v>
+      </c>
+      <c r="AG123" t="n">
+        <v>0.28084</v>
+      </c>
+      <c r="AH123" t="n">
+        <v>0.2810299999999999</v>
+      </c>
+      <c r="AI123" t="n">
+        <v>0.28043</v>
+      </c>
+      <c r="AJ123" t="n">
+        <v>0.27071</v>
+      </c>
+      <c r="AK123" t="n">
+        <v>0.28091</v>
+      </c>
+      <c r="AL123" t="n">
+        <v>0.32236</v>
+      </c>
+      <c r="AM123" t="n">
+        <v>0.31015</v>
+      </c>
+      <c r="AN123" t="n">
+        <v>0.30493</v>
+      </c>
+      <c r="AO123" t="n">
+        <v>0.3163</v>
+      </c>
+      <c r="AP123" t="n">
+        <v>0.30939</v>
+      </c>
+      <c r="AQ123" t="n">
+        <v>0.35894</v>
+      </c>
+      <c r="AR123" t="n">
+        <v>0.31626</v>
+      </c>
+      <c r="AS123" t="n">
+        <v>0.29732</v>
+      </c>
+      <c r="AT123" t="n">
+        <v>0.38719</v>
+      </c>
+      <c r="AU123" t="n">
+        <v>0.37942</v>
+      </c>
+      <c r="AV123" t="n">
+        <v>0.4275</v>
+      </c>
+      <c r="AW123" t="n">
+        <v>0.45524</v>
+      </c>
+      <c r="AX123" t="n">
+        <v>0.33182</v>
+      </c>
+      <c r="AY123" t="n">
+        <v>0.41845</v>
+      </c>
+      <c r="AZ123" t="n">
+        <v>0.41528</v>
+      </c>
+      <c r="BA123" t="n">
+        <v>0.38645</v>
+      </c>
+      <c r="BB123" t="n">
+        <v>0.40242</v>
+      </c>
+      <c r="BC123" t="n">
+        <v>0.30005</v>
+      </c>
+      <c r="BD123" t="n">
+        <v>0.30095</v>
+      </c>
+      <c r="BE123" t="n">
+        <v>0.2993</v>
+      </c>
+      <c r="BF123" t="n">
+        <v>0.29998</v>
+      </c>
+      <c r="BG123" t="n">
+        <v>0.15654</v>
+      </c>
+      <c r="BH123" t="n">
+        <v>0.29431</v>
+      </c>
+      <c r="BI123" t="n">
+        <v>0.31094</v>
+      </c>
+      <c r="BJ123" t="n">
+        <v>0.31343</v>
+      </c>
+      <c r="BK123" t="n">
+        <v>0.3127</v>
+      </c>
+      <c r="BL123" t="n">
+        <v>0.32184</v>
+      </c>
+      <c r="BM123" t="n">
+        <v>0.34628</v>
+      </c>
+      <c r="BN123" t="n">
+        <v>0.30067</v>
+      </c>
+      <c r="BO123" t="n">
+        <v>0.33083</v>
+      </c>
+      <c r="BP123" t="n">
+        <v>0.38546</v>
+      </c>
+      <c r="BQ123" t="n">
+        <v>0.47916</v>
+      </c>
+      <c r="BR123" t="n">
+        <v>0.5076700000000001</v>
+      </c>
+      <c r="BS123" t="n">
+        <v>0.79098</v>
+      </c>
+      <c r="BT123" t="n">
+        <v>0.6220399999999999</v>
+      </c>
+      <c r="BU123" t="n">
+        <v>0.78522</v>
+      </c>
+      <c r="BV123" t="n">
+        <v>0.40003</v>
+      </c>
+      <c r="BW123" t="n">
+        <v>0.49797</v>
+      </c>
+      <c r="BX123" t="n">
+        <v>0.7810199999999999</v>
+      </c>
+      <c r="BY123" t="n">
+        <v>0.92039</v>
+      </c>
+      <c r="BZ123" t="n">
+        <v>0.49456</v>
+      </c>
+      <c r="CA123" t="n">
+        <v>0.9142100000000001</v>
+      </c>
+      <c r="CB123" t="n">
+        <v>0.8628899999999999</v>
+      </c>
+      <c r="CC123" t="n">
+        <v>1.29622</v>
+      </c>
+      <c r="CD123" t="n">
+        <v>0.35366</v>
+      </c>
+      <c r="CE123" t="n">
+        <v>0.88751</v>
+      </c>
+      <c r="CF123" t="n">
+        <v>0.6316000000000001</v>
+      </c>
+      <c r="CG123" t="n">
+        <v>1.18709</v>
+      </c>
+      <c r="CH123" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CI123" t="n">
+        <v>1.407</v>
+      </c>
+      <c r="CJ123" t="n">
+        <v>1.33086</v>
+      </c>
+      <c r="CK123" t="n">
+        <v>1.03292</v>
+      </c>
+      <c r="CL123" t="n">
+        <v>0.5307999999999999</v>
+      </c>
+      <c r="CM123" t="n">
+        <v>0.79099</v>
+      </c>
+      <c r="CN123" t="n">
+        <v>0.85865</v>
+      </c>
+      <c r="CO123" t="n">
+        <v>0.77298</v>
+      </c>
+      <c r="CP123" t="n">
+        <v>0.77755</v>
+      </c>
+      <c r="CQ123" t="n">
+        <v>0.8767699999999999</v>
+      </c>
+      <c r="CR123" t="n">
+        <v>0.87387</v>
+      </c>
+      <c r="CS123" t="n">
+        <v>0.49316</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="n">
+        <v>46145</v>
+      </c>
+      <c r="B124" t="n">
+        <v>0.39868</v>
+      </c>
+      <c r="C124" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="D124" t="n">
+        <v>1.44995</v>
+      </c>
+      <c r="E124" t="n">
+        <v>1.207</v>
+      </c>
+      <c r="F124" t="n">
+        <v>0.87883</v>
+      </c>
+      <c r="G124" t="n">
+        <v>0.55102</v>
+      </c>
+      <c r="H124" t="n">
+        <v>0.62186</v>
+      </c>
+      <c r="I124" t="n">
+        <v>0.53832</v>
+      </c>
+      <c r="J124" t="n">
+        <v>0.49769</v>
+      </c>
+      <c r="K124" t="n">
+        <v>0.45582</v>
+      </c>
+      <c r="L124" t="n">
+        <v>0.42425</v>
+      </c>
+      <c r="M124" t="n">
+        <v>0.43714</v>
+      </c>
+      <c r="N124" t="n">
+        <v>0.44959</v>
+      </c>
+      <c r="O124" t="n">
+        <v>0.38817</v>
+      </c>
+      <c r="P124" t="n">
+        <v>0.45268</v>
+      </c>
+      <c r="Q124" t="n">
+        <v>0.41965</v>
+      </c>
+      <c r="R124" t="n">
+        <v>0.34667</v>
+      </c>
+      <c r="S124" t="n">
+        <v>0.39838</v>
+      </c>
+      <c r="T124" t="n">
+        <v>0.36261</v>
+      </c>
+      <c r="U124" t="n">
+        <v>0.38342</v>
+      </c>
+      <c r="V124" t="n">
+        <v>0.40877</v>
+      </c>
+      <c r="W124" t="n">
+        <v>0.42597</v>
+      </c>
+      <c r="X124" t="n">
+        <v>0.33944</v>
+      </c>
+      <c r="Y124" t="n">
+        <v>0.38673</v>
+      </c>
+      <c r="Z124" t="n">
+        <v>0.34554</v>
+      </c>
+      <c r="AA124" t="n">
+        <v>0.33578</v>
+      </c>
+      <c r="AB124" t="n">
+        <v>0.32931</v>
+      </c>
+      <c r="AC124" t="n">
+        <v>0.33994</v>
+      </c>
+      <c r="AD124" t="n">
+        <v>0.38361</v>
+      </c>
+      <c r="AE124" t="n">
+        <v>0.34745</v>
+      </c>
+      <c r="AF124" t="n">
+        <v>0.44919</v>
+      </c>
+      <c r="AG124" t="n">
+        <v>0.34635</v>
+      </c>
+      <c r="AH124" t="n">
+        <v>0.39213</v>
+      </c>
+      <c r="AI124" t="n">
+        <v>0.38291</v>
+      </c>
+      <c r="AJ124" t="n">
+        <v>0.55683</v>
+      </c>
+      <c r="AK124" t="n">
+        <v>0.40981</v>
+      </c>
+      <c r="AL124" t="n">
+        <v>0.5836</v>
+      </c>
+      <c r="AM124" t="n">
+        <v>0.70602</v>
+      </c>
+      <c r="AN124" t="n">
+        <v>0.87624</v>
+      </c>
+      <c r="AO124" t="n">
+        <v>0.46632</v>
+      </c>
+      <c r="AP124" t="n">
+        <v>0.39012</v>
+      </c>
+      <c r="AQ124" t="n">
+        <v>0.5500900000000001</v>
+      </c>
+      <c r="AR124" t="n">
+        <v>0.4328</v>
+      </c>
+      <c r="AS124" t="n">
+        <v>0.81268</v>
+      </c>
+      <c r="AT124" t="n">
+        <v>0.56586</v>
+      </c>
+      <c r="AU124" t="n">
+        <v>0.8526699999999999</v>
+      </c>
+      <c r="AV124" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AW124" t="n">
+        <v>0.87498</v>
+      </c>
+      <c r="AX124" t="n">
+        <v>0.34132</v>
+      </c>
+      <c r="AY124" t="n">
+        <v>0.41743</v>
+      </c>
+      <c r="AZ124" t="n">
+        <v>0.6237999999999999</v>
+      </c>
+      <c r="BA124" t="n">
+        <v>0.32995</v>
+      </c>
+      <c r="BB124" t="n">
+        <v>0.30268</v>
+      </c>
+      <c r="BC124" t="n">
+        <v>0.29359</v>
+      </c>
+      <c r="BD124" t="n">
+        <v>0.63002</v>
+      </c>
+      <c r="BE124" t="n">
+        <v>0.59302</v>
+      </c>
+      <c r="BF124" t="n">
+        <v>1.32764</v>
+      </c>
+      <c r="BG124" t="n">
+        <v>0.31056</v>
+      </c>
+      <c r="BH124" t="n">
+        <v>0.3524</v>
+      </c>
+      <c r="BI124" t="n">
+        <v>0.3301</v>
+      </c>
+      <c r="BJ124" t="n">
+        <v>0.32078</v>
+      </c>
+      <c r="BK124" t="n">
+        <v>0.40648</v>
+      </c>
+      <c r="BL124" t="n">
+        <v>0.33405</v>
+      </c>
+      <c r="BM124" t="n">
+        <v>0.31708</v>
+      </c>
+      <c r="BN124" t="n">
+        <v>0.31954</v>
+      </c>
+      <c r="BO124" t="n">
+        <v>0.31908</v>
+      </c>
+      <c r="BP124" t="n">
+        <v>0.31952</v>
+      </c>
+      <c r="BQ124" t="n">
+        <v>0.33538</v>
+      </c>
+      <c r="BR124" t="n">
+        <v>0.31733</v>
+      </c>
+      <c r="BS124" t="n">
+        <v>0.30858</v>
+      </c>
+      <c r="BT124" t="n">
+        <v>0.31878</v>
+      </c>
+      <c r="BU124" t="n">
+        <v>0.30139</v>
+      </c>
+      <c r="BV124" t="n">
+        <v>0.29585</v>
+      </c>
+      <c r="BW124" t="n">
+        <v>0.31127</v>
+      </c>
+      <c r="BX124" t="n">
+        <v>0.30956</v>
+      </c>
+      <c r="BY124" t="n">
+        <v>0.31065</v>
+      </c>
+      <c r="BZ124" t="n">
+        <v>0.28574</v>
+      </c>
+      <c r="CA124" t="n">
+        <v>0.29977</v>
+      </c>
+      <c r="CB124" t="n">
+        <v>0.30357</v>
+      </c>
+      <c r="CC124" t="n">
+        <v>0.31242</v>
+      </c>
+      <c r="CD124" t="n">
+        <v>0.30992</v>
+      </c>
+      <c r="CE124" t="n">
+        <v>0.31517</v>
+      </c>
+      <c r="CF124" t="n">
+        <v>0.34783</v>
+      </c>
+      <c r="CG124" t="n">
+        <v>0.33002</v>
+      </c>
+      <c r="CH124" t="n">
+        <v>0.33377</v>
+      </c>
+      <c r="CI124" t="n">
+        <v>0.33166</v>
+      </c>
+      <c r="CJ124" t="n">
+        <v>0.32396</v>
+      </c>
+      <c r="CK124" t="n">
+        <v>0.32798</v>
+      </c>
+      <c r="CL124" t="n">
+        <v>0.32625</v>
+      </c>
+      <c r="CM124" t="n">
+        <v>0.38675</v>
+      </c>
+      <c r="CN124" t="n">
+        <v>0.38887</v>
+      </c>
+      <c r="CO124" t="n">
+        <v>0.42138</v>
+      </c>
+      <c r="CP124" t="n">
+        <v>0.39077</v>
+      </c>
+      <c r="CQ124" t="n">
+        <v>0.37292</v>
+      </c>
+      <c r="CR124" t="n">
+        <v>0.35667</v>
+      </c>
+      <c r="CS124" t="n">
+        <v>0.3469</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="n">
+        <v>46146</v>
+      </c>
+      <c r="B125" t="n">
+        <v>0.32835</v>
+      </c>
+      <c r="C125" t="n">
+        <v>0.9135</v>
+      </c>
+      <c r="D125" t="n">
+        <v>0.34906</v>
+      </c>
+      <c r="E125" t="n">
+        <v>0.44264</v>
+      </c>
+      <c r="F125" t="n">
+        <v>0.40666</v>
+      </c>
+      <c r="G125" t="n">
+        <v>0.39262</v>
+      </c>
+      <c r="H125" t="n">
+        <v>0.43546</v>
+      </c>
+      <c r="I125" t="n">
+        <v>0.36581</v>
+      </c>
+      <c r="J125" t="n">
+        <v>0.38882</v>
+      </c>
+      <c r="K125" t="n">
+        <v>0.35161</v>
+      </c>
+      <c r="L125" t="n">
+        <v>0.35455</v>
+      </c>
+      <c r="M125" t="n">
+        <v>0.34022</v>
+      </c>
+      <c r="N125" t="n">
+        <v>0.33956</v>
+      </c>
+      <c r="O125" t="n">
+        <v>0.33465</v>
+      </c>
+      <c r="P125" t="n">
+        <v>0.32412</v>
+      </c>
+      <c r="Q125" t="n">
+        <v>0.34776</v>
+      </c>
+      <c r="R125" t="n">
+        <v>0.33601</v>
+      </c>
+      <c r="S125" t="n">
+        <v>0.31715</v>
+      </c>
+      <c r="T125" t="n">
+        <v>0.37625</v>
+      </c>
+      <c r="U125" t="n">
+        <v>0.45952</v>
+      </c>
+      <c r="V125" t="n">
+        <v>0.34557</v>
+      </c>
+      <c r="W125" t="n">
+        <v>0.36799</v>
+      </c>
+      <c r="X125" t="n">
+        <v>0.33349</v>
+      </c>
+      <c r="Y125" t="n">
+        <v>0.33933</v>
+      </c>
+      <c r="Z125" t="n">
+        <v>0.3427</v>
+      </c>
+      <c r="AA125" t="n">
+        <v>0.3548</v>
+      </c>
+      <c r="AB125" t="n">
+        <v>0.3453</v>
+      </c>
+      <c r="AC125" t="n">
+        <v>0.34936</v>
+      </c>
+      <c r="AD125" t="n">
+        <v>0.30695</v>
+      </c>
+      <c r="AE125" t="n">
+        <v>0.309</v>
+      </c>
+      <c r="AF125" t="n">
+        <v>0.32478</v>
+      </c>
+      <c r="AG125" t="n">
+        <v>0.32923</v>
+      </c>
+      <c r="AH125" t="n">
+        <v>0.33095</v>
+      </c>
+      <c r="AI125" t="n">
+        <v>0.34053</v>
+      </c>
+      <c r="AJ125" t="n">
+        <v>0.31249</v>
+      </c>
+      <c r="AK125" t="n">
+        <v>0.31088</v>
+      </c>
+      <c r="AL125" t="n">
+        <v>0.28797</v>
+      </c>
+      <c r="AM125" t="n">
+        <v>0.31285</v>
+      </c>
+      <c r="AN125" t="n">
+        <v>0.31284</v>
+      </c>
+      <c r="AO125" t="n">
+        <v>0.3011</v>
+      </c>
+      <c r="AP125" t="n">
+        <v>0.19104</v>
+      </c>
+      <c r="AQ125" t="n">
+        <v>0.30432</v>
+      </c>
+      <c r="AR125" t="n">
+        <v>0.30804</v>
+      </c>
+      <c r="AS125" t="n">
+        <v>0.34163</v>
+      </c>
+      <c r="AT125" t="n">
+        <v>0.33486</v>
+      </c>
+      <c r="AU125" t="n">
+        <v>0.36059</v>
+      </c>
+      <c r="AV125" t="n">
+        <v>0.31127</v>
+      </c>
+      <c r="AW125" t="n">
+        <v>0.27313</v>
+      </c>
+      <c r="AX125" t="n">
+        <v>0.19765</v>
+      </c>
+      <c r="AY125" t="n">
+        <v>0.30492</v>
+      </c>
+      <c r="AZ125" t="n">
+        <v>0.29874</v>
+      </c>
+      <c r="BA125" t="n">
+        <v>0.32009</v>
+      </c>
+      <c r="BB125" t="n">
+        <v>0.28138</v>
+      </c>
+      <c r="BC125" t="n">
+        <v>0.30897</v>
+      </c>
+      <c r="BD125" t="n">
+        <v>0.30942</v>
+      </c>
+      <c r="BE125" t="n">
+        <v>0.34787</v>
+      </c>
+      <c r="BF125" t="n">
+        <v>0.35602</v>
+      </c>
+      <c r="BG125" t="n">
+        <v>0.30828</v>
+      </c>
+      <c r="BH125" t="n">
+        <v>0.30133</v>
+      </c>
+      <c r="BI125" t="n">
+        <v>0.30983</v>
+      </c>
+      <c r="BJ125" t="n">
+        <v>0.31244</v>
+      </c>
+      <c r="BK125" t="n">
+        <v>0.31373</v>
+      </c>
+      <c r="BL125" t="n">
+        <v>0.30947</v>
+      </c>
+      <c r="BM125" t="n">
+        <v>0.29668</v>
+      </c>
+      <c r="BN125" t="n">
+        <v>0.29552</v>
+      </c>
+      <c r="BO125" t="n">
+        <v>0.30001</v>
+      </c>
+      <c r="BP125" t="n">
+        <v>0.30751</v>
+      </c>
+      <c r="BQ125" t="n">
+        <v>0.30659</v>
+      </c>
+      <c r="BR125" t="n">
+        <v>0.2884</v>
+      </c>
+      <c r="BS125" t="n">
+        <v>0.33663</v>
+      </c>
+      <c r="BT125" t="n">
+        <v>0.25356</v>
+      </c>
+      <c r="BU125" t="n">
+        <v>0.3372</v>
+      </c>
+      <c r="BV125" t="n">
+        <v>0.31208</v>
+      </c>
+      <c r="BW125" t="n">
+        <v>0.32584</v>
+      </c>
+      <c r="BX125" t="n">
+        <v>0.32807</v>
+      </c>
+      <c r="BY125" t="n">
+        <v>0.27423</v>
+      </c>
+      <c r="BZ125" t="n">
+        <v>0.33554</v>
+      </c>
+      <c r="CA125" t="n">
+        <v>0.32019</v>
+      </c>
+      <c r="CB125" t="n">
+        <v>0.32863</v>
+      </c>
+      <c r="CC125" t="n">
+        <v>0.30131</v>
+      </c>
+      <c r="CD125" t="n">
+        <v>0.33738</v>
+      </c>
+      <c r="CE125" t="n">
+        <v>0.32795</v>
+      </c>
+      <c r="CF125" t="n">
+        <v>0.3682</v>
+      </c>
+      <c r="CG125" t="n">
+        <v>0.33972</v>
+      </c>
+      <c r="CH125" t="n">
+        <v>0.41032</v>
+      </c>
+      <c r="CI125" t="n">
+        <v>0.27263</v>
+      </c>
+      <c r="CJ125" t="n">
+        <v>0.33194</v>
+      </c>
+      <c r="CK125" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="CL125" t="n">
+        <v>0.34421</v>
+      </c>
+      <c r="CM125" t="n">
+        <v>0.43947</v>
+      </c>
+      <c r="CN125" t="n">
+        <v>0.3264</v>
+      </c>
+      <c r="CO125" t="n">
+        <v>0.39918</v>
+      </c>
+      <c r="CP125" t="n">
+        <v>0.35109</v>
+      </c>
+      <c r="CQ125" t="n">
+        <v>0.37889</v>
+      </c>
+      <c r="CR125" t="n">
+        <v>0.37659</v>
+      </c>
+      <c r="CS125" t="n">
+        <v>0.5296799999999999</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="n">
+        <v>46147</v>
+      </c>
+      <c r="B126" t="n">
+        <v>0.31932</v>
+      </c>
+      <c r="C126" t="n">
+        <v>0.8647699999999999</v>
+      </c>
+      <c r="D126" t="n">
+        <v>1.44332</v>
+      </c>
+      <c r="E126" t="n">
+        <v>1.13732</v>
+      </c>
+      <c r="F126" t="n">
+        <v>0.68552</v>
+      </c>
+      <c r="G126" t="n">
+        <v>0.77577</v>
+      </c>
+      <c r="H126" t="n">
+        <v>0.6372000000000001</v>
+      </c>
+      <c r="I126" t="n">
+        <v>0.5008899999999999</v>
+      </c>
+      <c r="J126" t="n">
+        <v>0.39784</v>
+      </c>
+      <c r="K126" t="n">
+        <v>0.43939</v>
+      </c>
+      <c r="L126" t="n">
+        <v>0.48931</v>
+      </c>
+      <c r="M126" t="n">
+        <v>0.42972</v>
+      </c>
+      <c r="N126" t="n">
+        <v>0.41495</v>
+      </c>
+      <c r="O126" t="n">
+        <v>0.40452</v>
+      </c>
+      <c r="P126" t="n">
+        <v>0.40399</v>
+      </c>
+      <c r="Q126" t="n">
+        <v>0.4032</v>
+      </c>
+      <c r="R126" t="n">
+        <v>0.46035</v>
+      </c>
+      <c r="S126" t="n">
+        <v>0.40423</v>
+      </c>
+      <c r="T126" t="n">
+        <v>0.42473</v>
+      </c>
+      <c r="U126" t="n">
+        <v>0.38771</v>
+      </c>
+      <c r="V126" t="n">
+        <v>0.42539</v>
+      </c>
+      <c r="W126" t="n">
+        <v>0.38369</v>
+      </c>
+      <c r="X126" t="n">
+        <v>0.39803</v>
+      </c>
+      <c r="Y126" t="n">
+        <v>0.41567</v>
+      </c>
+      <c r="Z126" t="n">
+        <v>0.38778</v>
+      </c>
+      <c r="AA126" t="n">
+        <v>0.41564</v>
+      </c>
+      <c r="AB126" t="n">
+        <v>0.40351</v>
+      </c>
+      <c r="AC126" t="n">
+        <v>0.40426</v>
+      </c>
+      <c r="AD126" t="n">
+        <v>0.4068</v>
+      </c>
+      <c r="AE126" t="n">
+        <v>0.37638</v>
+      </c>
+      <c r="AF126" t="n">
+        <v>0.39226</v>
+      </c>
+      <c r="AG126" t="n">
+        <v>0.38996</v>
+      </c>
+      <c r="AH126" t="n">
+        <v>0.37744</v>
+      </c>
+      <c r="AI126" t="n">
+        <v>0.48603</v>
+      </c>
+      <c r="AJ126" t="n">
+        <v>0.35655</v>
+      </c>
+      <c r="AK126" t="n">
+        <v>0.30528</v>
+      </c>
+      <c r="AL126" t="n">
+        <v>0.28718</v>
+      </c>
+      <c r="AM126" t="n">
+        <v>0.34337</v>
+      </c>
+      <c r="AN126" t="n">
+        <v>0.35546</v>
+      </c>
+      <c r="AO126" t="n">
+        <v>0.30532</v>
+      </c>
+      <c r="AP126" t="n">
+        <v>0.33364</v>
+      </c>
+      <c r="AQ126" t="n">
+        <v>0.30418</v>
+      </c>
+      <c r="AR126" t="n">
+        <v>0.30749</v>
+      </c>
+      <c r="AS126" t="n">
+        <v>0.29888</v>
+      </c>
+      <c r="AT126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU126" t="n">
+        <v>0.52274</v>
+      </c>
+      <c r="AV126" t="n">
+        <v>0.35647</v>
+      </c>
+      <c r="AW126" t="n">
+        <v>0.22245</v>
+      </c>
+      <c r="AX126" t="n">
+        <v>0.24823</v>
+      </c>
+      <c r="AY126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ126" t="n">
+        <v>0.2998</v>
+      </c>
+      <c r="BA126" t="n">
+        <v>0.15557</v>
+      </c>
+      <c r="BB126" t="n">
+        <v>0.27398</v>
+      </c>
+      <c r="BC126" t="n">
+        <v>0.2754</v>
+      </c>
+      <c r="BD126" t="n">
+        <v>-0.00893</v>
+      </c>
+      <c r="BE126" t="n">
+        <v>0.33488</v>
+      </c>
+      <c r="BF126" t="n">
+        <v>0.30113</v>
+      </c>
+      <c r="BG126" t="n">
+        <v>0.25973</v>
+      </c>
+      <c r="BH126" t="n">
+        <v>0.25276</v>
+      </c>
+      <c r="BI126" t="n">
+        <v>0.30825</v>
+      </c>
+      <c r="BJ126" t="n">
+        <v>0.28166</v>
+      </c>
+      <c r="BK126" t="n">
+        <v>0.29179</v>
+      </c>
+      <c r="BL126" t="n">
+        <v>0.30496</v>
+      </c>
+      <c r="BM126" t="n">
+        <v>0.28898</v>
+      </c>
+      <c r="BN126" t="n">
+        <v>0.30418</v>
+      </c>
+      <c r="BO126" t="n">
+        <v>0.31051</v>
+      </c>
+      <c r="BP126" t="n">
+        <v>0.31842</v>
+      </c>
+      <c r="BQ126" t="n">
+        <v>0.31815</v>
+      </c>
+      <c r="BR126" t="n">
+        <v>0.31075</v>
+      </c>
+      <c r="BS126" t="n">
+        <v>0.32776</v>
+      </c>
+      <c r="BT126" t="n">
+        <v>0.32935</v>
+      </c>
+      <c r="BU126" t="n">
+        <v>0.38659</v>
+      </c>
+      <c r="BV126" t="n">
+        <v>0.38322</v>
+      </c>
+      <c r="BW126" t="n">
+        <v>0.34355</v>
+      </c>
+      <c r="BX126" t="n">
+        <v>0.35216</v>
+      </c>
+      <c r="BY126" t="n">
+        <v>0.3325</v>
+      </c>
+      <c r="BZ126" t="n">
+        <v>0.32074</v>
+      </c>
+      <c r="CA126" t="n">
+        <v>0.35941</v>
+      </c>
+      <c r="CB126" t="n">
+        <v>0.33419</v>
+      </c>
+      <c r="CC126" t="n">
+        <v>0.34362</v>
+      </c>
+      <c r="CD126" t="n">
+        <v>0.35399</v>
+      </c>
+      <c r="CE126" t="n">
+        <v>0.35393</v>
+      </c>
+      <c r="CF126" t="n">
+        <v>0.34088</v>
+      </c>
+      <c r="CG126" t="n">
+        <v>0.54088</v>
+      </c>
+      <c r="CH126" t="n">
+        <v>0.43115</v>
+      </c>
+      <c r="CI126" t="n">
+        <v>0.7827499999999999</v>
+      </c>
+      <c r="CJ126" t="n">
+        <v>0.43234</v>
+      </c>
+      <c r="CK126" t="n">
+        <v>0.43459</v>
+      </c>
+      <c r="CL126" t="n">
+        <v>0.36354</v>
+      </c>
+      <c r="CM126" t="n">
+        <v>0.43975</v>
+      </c>
+      <c r="CN126" t="n">
+        <v>0.36865</v>
+      </c>
+      <c r="CO126" t="n">
+        <v>0.35537</v>
+      </c>
+      <c r="CP126" t="n">
+        <v>0.32415</v>
+      </c>
+      <c r="CQ126" t="n">
+        <v>0.32312</v>
+      </c>
+      <c r="CR126" t="n">
+        <v>0.31968</v>
+      </c>
+      <c r="CS126" t="n">
+        <v>0.30644</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="n">
+        <v>46148</v>
+      </c>
+      <c r="B127" t="n">
+        <v>0.3183</v>
+      </c>
+      <c r="C127" t="n">
+        <v>0.38769</v>
+      </c>
+      <c r="D127" t="n">
+        <v>0.31871</v>
+      </c>
+      <c r="E127" t="n">
+        <v>1.32115</v>
+      </c>
+      <c r="F127" t="n">
+        <v>0.29839</v>
+      </c>
+      <c r="G127" t="n">
+        <v>0.32829</v>
+      </c>
+      <c r="H127" t="n">
+        <v>0.29373</v>
+      </c>
+      <c r="I127" t="n">
+        <v>0.29775</v>
+      </c>
+      <c r="J127" t="n">
+        <v>0.29223</v>
+      </c>
+      <c r="K127" t="n">
+        <v>0.29363</v>
+      </c>
+      <c r="L127" t="n">
+        <v>0.2847</v>
+      </c>
+      <c r="M127" t="n">
+        <v>0.29075</v>
+      </c>
+      <c r="N127" t="n">
+        <v>0.30885</v>
+      </c>
+      <c r="O127" t="n">
+        <v>0.30721</v>
+      </c>
+      <c r="P127" t="n">
+        <v>0.31074</v>
+      </c>
+      <c r="Q127" t="n">
+        <v>0.30683</v>
+      </c>
+      <c r="R127" t="n">
+        <v>0.2799</v>
+      </c>
+      <c r="S127" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="T127" t="n">
+        <v>0.29997</v>
+      </c>
+      <c r="U127" t="n">
+        <v>0.3147799999999999</v>
+      </c>
+      <c r="V127" t="n">
+        <v>0.30231</v>
+      </c>
+      <c r="W127" t="n">
+        <v>0.23946</v>
+      </c>
+      <c r="X127" t="n">
+        <v>0.28705</v>
+      </c>
+      <c r="Y127" t="n">
+        <v>0.34684</v>
+      </c>
+      <c r="Z127" t="n">
+        <v>0.24368</v>
+      </c>
+      <c r="AA127" t="n">
+        <v>0.31482</v>
+      </c>
+      <c r="AB127" t="n">
+        <v>0.35213</v>
+      </c>
+      <c r="AC127" t="n">
+        <v>0.33041</v>
+      </c>
+      <c r="AD127" t="n">
+        <v>0.32941</v>
+      </c>
+      <c r="AE127" t="n">
+        <v>0.32966</v>
+      </c>
+      <c r="AF127" t="n">
+        <v>0.32636</v>
+      </c>
+      <c r="AG127" t="n">
+        <v>0.31712</v>
+      </c>
+      <c r="AH127" t="n">
+        <v>0.2947</v>
+      </c>
+      <c r="AI127" t="n">
+        <v>0.31156</v>
+      </c>
+      <c r="AJ127" t="n">
+        <v>0.23759</v>
+      </c>
+      <c r="AK127" t="n">
+        <v>0.32212</v>
+      </c>
+      <c r="AL127" t="n">
+        <v>0.27304</v>
+      </c>
+      <c r="AM127" t="n">
+        <v>0.26305</v>
+      </c>
+      <c r="AN127" t="n">
+        <v>0.32019</v>
+      </c>
+      <c r="AO127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AP127" t="n">
+        <v>0.38376</v>
+      </c>
+      <c r="AQ127" t="n">
+        <v>0.22971</v>
+      </c>
+      <c r="AR127" t="n">
+        <v>0.26758</v>
+      </c>
+      <c r="AS127" t="n">
+        <v>0.38143</v>
+      </c>
+      <c r="AT127" t="n">
+        <v>0.34073</v>
+      </c>
+      <c r="AU127" t="n">
+        <v>0.42687</v>
+      </c>
+      <c r="AV127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX127" t="n">
+        <v>0.26264</v>
+      </c>
+      <c r="AY127" t="n">
+        <v>0.30823</v>
+      </c>
+      <c r="AZ127" t="n">
+        <v>0.33611</v>
+      </c>
+      <c r="BA127" t="n">
+        <v>0.3838</v>
+      </c>
+      <c r="BB127" t="n">
+        <v>0.29597</v>
+      </c>
+      <c r="BC127" t="n">
+        <v>0.34314</v>
+      </c>
+      <c r="BD127" t="n">
+        <v>0.32051</v>
+      </c>
+      <c r="BE127" t="n">
+        <v>0.31261</v>
+      </c>
+      <c r="BF127" t="n">
+        <v>0.2795299999999999</v>
+      </c>
+      <c r="BG127" t="n">
+        <v>0.27902</v>
+      </c>
+      <c r="BH127" t="n">
+        <v>0.34974</v>
+      </c>
+      <c r="BI127" t="n">
+        <v>0.39912</v>
+      </c>
+      <c r="BJ127" t="n">
+        <v>0.28745</v>
+      </c>
+      <c r="BK127" t="n">
+        <v>0.32545</v>
+      </c>
+      <c r="BL127" t="n">
+        <v>0.30657</v>
+      </c>
+      <c r="BM127" t="n">
+        <v>0.34228</v>
+      </c>
+      <c r="BN127" t="n">
+        <v>0.31144</v>
+      </c>
+      <c r="BO127" t="n">
+        <v>0.50129</v>
+      </c>
+      <c r="BP127" t="n">
+        <v>0.36335</v>
+      </c>
+      <c r="BQ127" t="n">
+        <v>0.42603</v>
+      </c>
+      <c r="BR127" t="n">
+        <v>0.31833</v>
+      </c>
+      <c r="BS127" t="n">
+        <v>0.37162</v>
+      </c>
+      <c r="BT127" t="n">
+        <v>0.36322</v>
+      </c>
+      <c r="BU127" t="n">
+        <v>0.45385</v>
+      </c>
+      <c r="BV127" t="n">
+        <v>0.33375</v>
+      </c>
+      <c r="BW127" t="n">
+        <v>0.36288</v>
+      </c>
+      <c r="BX127" t="n">
+        <v>0.33703</v>
+      </c>
+      <c r="BY127" t="n">
+        <v>0.37833</v>
+      </c>
+      <c r="BZ127" t="n">
+        <v>0.34545</v>
+      </c>
+      <c r="CA127" t="n">
+        <v>0.36461</v>
+      </c>
+      <c r="CB127" t="n">
+        <v>0.41531</v>
+      </c>
+      <c r="CC127" t="n">
+        <v>0.37625</v>
+      </c>
+      <c r="CD127" t="n">
+        <v>0.37001</v>
+      </c>
+      <c r="CE127" t="n">
+        <v>0.37751</v>
+      </c>
+      <c r="CF127" t="n">
+        <v>0.37524</v>
+      </c>
+      <c r="CG127" t="n">
+        <v>0.41944</v>
+      </c>
+      <c r="CH127" t="n">
+        <v>0.40716</v>
+      </c>
+      <c r="CI127" t="n">
+        <v>0.40766</v>
+      </c>
+      <c r="CJ127" t="n">
+        <v>0.41203</v>
+      </c>
+      <c r="CK127" t="n">
+        <v>0.43751</v>
+      </c>
+      <c r="CL127" t="n">
+        <v>0.39418</v>
+      </c>
+      <c r="CM127" t="n">
+        <v>0.38232</v>
+      </c>
+      <c r="CN127" t="n">
+        <v>0.39002</v>
+      </c>
+      <c r="CO127" t="n">
+        <v>0.38392</v>
+      </c>
+      <c r="CP127" t="n">
+        <v>0.34262</v>
+      </c>
+      <c r="CQ127" t="n">
+        <v>0.34357</v>
+      </c>
+      <c r="CR127" t="n">
+        <v>0.32578</v>
+      </c>
+      <c r="CS127" t="n">
+        <v>0.33382</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="n">
+        <v>46149</v>
+      </c>
+      <c r="B128" t="n">
+        <v>0.32807</v>
+      </c>
+      <c r="C128" t="n">
+        <v>0.48867</v>
+      </c>
+      <c r="D128" t="n">
+        <v>0.38215</v>
+      </c>
+      <c r="E128" t="n">
+        <v>0.43371</v>
+      </c>
+      <c r="F128" t="n">
+        <v>0.39817</v>
+      </c>
+      <c r="G128" t="n">
+        <v>0.39158</v>
+      </c>
+      <c r="H128" t="n">
+        <v>0.35449</v>
+      </c>
+      <c r="I128" t="n">
+        <v>0.36344</v>
+      </c>
+      <c r="J128" t="n">
+        <v>0.36229</v>
+      </c>
+      <c r="K128" t="n">
+        <v>0.37349</v>
+      </c>
+      <c r="L128" t="n">
+        <v>0.373</v>
+      </c>
+      <c r="M128" t="n">
+        <v>0.36354</v>
+      </c>
+      <c r="N128" t="n">
+        <v>0.3654</v>
+      </c>
+      <c r="O128" t="n">
+        <v>0.3486</v>
+      </c>
+      <c r="P128" t="n">
+        <v>0.37371</v>
+      </c>
+      <c r="Q128" t="n">
+        <v>0.35643</v>
+      </c>
+      <c r="R128" t="n">
+        <v>0.36232</v>
+      </c>
+      <c r="S128" t="n">
+        <v>0.3383</v>
+      </c>
+      <c r="T128" t="n">
+        <v>0.33591</v>
+      </c>
+      <c r="U128" t="n">
+        <v>0.34295</v>
+      </c>
+      <c r="V128" t="n">
+        <v>0.33389</v>
+      </c>
+      <c r="W128" t="n">
+        <v>0.33002</v>
+      </c>
+      <c r="X128" t="n">
+        <v>0.33427</v>
+      </c>
+      <c r="Y128" t="n">
+        <v>0.33001</v>
+      </c>
+      <c r="Z128" t="n">
+        <v>0.33921</v>
+      </c>
+      <c r="AA128" t="n">
+        <v>0.41747</v>
+      </c>
+      <c r="AB128" t="n">
+        <v>0.35391</v>
+      </c>
+      <c r="AC128" t="n">
+        <v>0.36292</v>
+      </c>
+      <c r="AD128" t="n">
+        <v>0.34695</v>
+      </c>
+      <c r="AE128" t="n">
+        <v>0.3316</v>
+      </c>
+      <c r="AF128" t="n">
+        <v>0.32951</v>
+      </c>
+      <c r="AG128" t="n">
+        <v>0.33179</v>
+      </c>
+      <c r="AH128" t="n">
+        <v>0.32064</v>
+      </c>
+      <c r="AI128" t="n">
+        <v>0.33305</v>
+      </c>
+      <c r="AJ128" t="n">
+        <v>0.33987</v>
+      </c>
+      <c r="AK128" t="n">
+        <v>0.35443</v>
+      </c>
+      <c r="AL128" t="n">
+        <v>0.29442</v>
+      </c>
+      <c r="AM128" t="n">
+        <v>0.31855</v>
+      </c>
+      <c r="AN128" t="n">
+        <v>0.33191</v>
+      </c>
+      <c r="AO128" t="n">
+        <v>0.32644</v>
+      </c>
+      <c r="AP128" t="n">
+        <v>0.29855</v>
+      </c>
+      <c r="AQ128" t="n">
+        <v>0.30899</v>
+      </c>
+      <c r="AR128" t="n">
+        <v>0.29418</v>
+      </c>
+      <c r="AS128" t="n">
+        <v>0.99482</v>
+      </c>
+      <c r="AT128" t="n">
+        <v>0.6859299999999999</v>
+      </c>
+      <c r="AU128" t="n">
+        <v>0.34509</v>
+      </c>
+      <c r="AV128" t="n">
+        <v>0.37056</v>
+      </c>
+      <c r="AW128" t="n">
+        <v>0.25296</v>
+      </c>
+      <c r="AX128" t="n">
+        <v>0.27976</v>
+      </c>
+      <c r="AY128" t="n">
+        <v>0.30088</v>
+      </c>
+      <c r="AZ128" t="n">
+        <v>0.30132</v>
+      </c>
+      <c r="BA128" t="n">
+        <v>0.31807</v>
+      </c>
+      <c r="BB128" t="n">
+        <v>0.31775</v>
+      </c>
+      <c r="BC128" t="n">
+        <v>0.31878</v>
+      </c>
+      <c r="BD128" t="n">
+        <v>0.36115</v>
+      </c>
+      <c r="BE128" t="n">
+        <v>0.31355</v>
+      </c>
+      <c r="BF128" t="n">
+        <v>0.32299</v>
+      </c>
+      <c r="BG128" t="n">
+        <v>0.29746</v>
+      </c>
+      <c r="BH128" t="n">
+        <v>0.23925</v>
+      </c>
+      <c r="BI128" t="n">
+        <v>0.3127</v>
+      </c>
+      <c r="BJ128" t="n">
+        <v>0.30312</v>
+      </c>
+      <c r="BK128" t="n">
+        <v>0.32012</v>
+      </c>
+      <c r="BL128" t="n">
+        <v>0.46465</v>
+      </c>
+      <c r="BM128" t="n">
+        <v>0.46619</v>
+      </c>
+      <c r="BN128" t="n">
+        <v>0.4216</v>
+      </c>
+      <c r="BO128" t="n">
+        <v>0.5134299999999999</v>
+      </c>
+      <c r="BP128" t="n">
+        <v>0.48856</v>
+      </c>
+      <c r="BQ128" t="n">
+        <v>0.39736</v>
+      </c>
+      <c r="BR128" t="n">
+        <v>0.33384</v>
+      </c>
+      <c r="BS128" t="n">
+        <v>0.68591</v>
+      </c>
+      <c r="BT128" t="n">
+        <v>0.7642899999999999</v>
+      </c>
+      <c r="BU128" t="n">
+        <v>0.3744</v>
+      </c>
+      <c r="BV128" t="n">
+        <v>0.39088</v>
+      </c>
+      <c r="BW128" t="n">
+        <v>0.34154</v>
+      </c>
+      <c r="BX128" t="n">
+        <v>0.38987</v>
+      </c>
+      <c r="BY128" t="n">
+        <v>0.71489</v>
+      </c>
+      <c r="BZ128" t="n">
+        <v>0.8789199999999999</v>
+      </c>
+      <c r="CA128" t="n">
+        <v>0.6462100000000001</v>
+      </c>
+      <c r="CB128" t="n">
+        <v>0.90962</v>
+      </c>
+      <c r="CC128" t="n">
+        <v>1.07241</v>
+      </c>
+      <c r="CD128" t="n">
+        <v>0.37779</v>
+      </c>
+      <c r="CE128" t="n">
+        <v>0.37169</v>
+      </c>
+      <c r="CF128" t="n">
+        <v>0.4059700000000001</v>
+      </c>
+      <c r="CG128" t="n">
+        <v>0.40467</v>
+      </c>
+      <c r="CH128" t="n">
+        <v>0.4001</v>
+      </c>
+      <c r="CI128" t="n">
+        <v>0.6223500000000001</v>
+      </c>
+      <c r="CJ128" t="n">
+        <v>0.3407</v>
+      </c>
+      <c r="CK128" t="n">
+        <v>0.34352</v>
+      </c>
+      <c r="CL128" t="n">
+        <v>0.44213</v>
+      </c>
+      <c r="CM128" t="n">
+        <v>0.35855</v>
+      </c>
+      <c r="CN128" t="n">
+        <v>0.40039</v>
+      </c>
+      <c r="CO128" t="n">
+        <v>0.35996</v>
+      </c>
+      <c r="CP128" t="n">
+        <v>0.36501</v>
+      </c>
+      <c r="CQ128" t="n">
+        <v>0.36893</v>
+      </c>
+      <c r="CR128" t="n">
+        <v>0.33997</v>
+      </c>
+      <c r="CS128" t="n">
+        <v>0.3481</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="n">
+        <v>46150</v>
+      </c>
+      <c r="B129" t="n">
+        <v>0.33547</v>
+      </c>
+      <c r="C129" t="n">
+        <v>0.35312</v>
+      </c>
+      <c r="D129" t="n">
+        <v>0.45863</v>
+      </c>
+      <c r="E129" t="n">
+        <v>0.36394</v>
+      </c>
+      <c r="F129" t="n">
+        <v>0.47133</v>
+      </c>
+      <c r="G129" t="n">
+        <v>0.3651</v>
+      </c>
+      <c r="H129" t="n">
+        <v>0.34186</v>
+      </c>
+      <c r="I129" t="n">
+        <v>0.35185</v>
+      </c>
+      <c r="J129" t="n">
+        <v>0.34508</v>
+      </c>
+      <c r="K129" t="n">
+        <v>0.33721</v>
+      </c>
+      <c r="L129" t="n">
+        <v>0.33051</v>
+      </c>
+      <c r="M129" t="n">
+        <v>0.33565</v>
+      </c>
+      <c r="N129" t="n">
+        <v>0.33495</v>
+      </c>
+      <c r="O129" t="n">
+        <v>0.3384</v>
+      </c>
+      <c r="P129" t="n">
+        <v>0.34003</v>
+      </c>
+      <c r="Q129" t="n">
+        <v>0.33726</v>
+      </c>
+      <c r="R129" t="n">
+        <v>0.33269</v>
+      </c>
+      <c r="S129" t="n">
+        <v>0.33139</v>
+      </c>
+      <c r="T129" t="n">
+        <v>0.33624</v>
+      </c>
+      <c r="U129" t="n">
+        <v>0.33169</v>
+      </c>
+      <c r="V129" t="n">
+        <v>0.32821</v>
+      </c>
+      <c r="W129" t="n">
+        <v>0.33302</v>
+      </c>
+      <c r="X129" t="n">
+        <v>0.32879</v>
+      </c>
+      <c r="Y129" t="n">
+        <v>0.33038</v>
+      </c>
+      <c r="Z129" t="n">
+        <v>0.33346</v>
+      </c>
+      <c r="AA129" t="n">
+        <v>0.33797</v>
+      </c>
+      <c r="AB129" t="n">
+        <v>0.36043</v>
+      </c>
+      <c r="AC129" t="n">
+        <v>0.37338</v>
+      </c>
+      <c r="AD129" t="n">
+        <v>0.36827</v>
+      </c>
+      <c r="AE129" t="n">
+        <v>0.3612</v>
+      </c>
+      <c r="AF129" t="n">
+        <v>0.43179</v>
+      </c>
+      <c r="AG129" t="n">
+        <v>0.33203</v>
+      </c>
+      <c r="AH129" t="n">
+        <v>0.8229099999999999</v>
+      </c>
+      <c r="AI129" t="n">
+        <v>0.94713</v>
+      </c>
+      <c r="AJ129" t="n">
+        <v>0.9391699999999999</v>
+      </c>
+      <c r="AK129" t="n">
+        <v>1.43729</v>
+      </c>
+      <c r="AL129" t="n">
+        <v>0.86805</v>
+      </c>
+      <c r="AM129" t="n">
+        <v>1.50872</v>
+      </c>
+      <c r="AN129" t="n">
+        <v>1.19077</v>
+      </c>
+      <c r="AO129" t="n">
+        <v>0.94997</v>
+      </c>
+      <c r="AP129" t="n">
+        <v>0.9342699999999999</v>
+      </c>
+      <c r="AQ129" t="n">
+        <v>1.16004</v>
+      </c>
+      <c r="AR129" t="n">
+        <v>0.90538</v>
+      </c>
+      <c r="AS129" t="n">
+        <v>1.35021</v>
+      </c>
+      <c r="AT129" t="n">
+        <v>1.21928</v>
+      </c>
+      <c r="AU129" t="n">
+        <v>1.25299</v>
+      </c>
+      <c r="AV129" t="n">
+        <v>0.85729</v>
+      </c>
+      <c r="AW129" t="n">
+        <v>1.36964</v>
+      </c>
+      <c r="AX129" t="n">
+        <v>0.45277</v>
+      </c>
+      <c r="AY129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AZ129" t="n">
+        <v>1.55262</v>
+      </c>
+      <c r="BA129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BB129" t="n">
+        <v>0.60211</v>
+      </c>
+      <c r="BC129" t="n">
+        <v>1.3214</v>
+      </c>
+      <c r="BD129" t="n">
+        <v>1.29718</v>
+      </c>
+      <c r="BE129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BF129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BG129" t="n">
+        <v>1.45341</v>
+      </c>
+      <c r="BH129" t="n">
+        <v>1.71652</v>
+      </c>
+      <c r="BI129" t="n">
+        <v>1.57525</v>
+      </c>
+      <c r="BJ129" t="n">
+        <v>1.46123</v>
+      </c>
+      <c r="BK129" t="n">
+        <v>1.59168</v>
+      </c>
+      <c r="BL129" t="n">
+        <v>1.26513</v>
+      </c>
+      <c r="BM129" t="n">
+        <v>1.53167</v>
+      </c>
+      <c r="BN129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BO129" t="n">
+        <v>0.88326</v>
+      </c>
+      <c r="BP129" t="n">
+        <v>1.69326</v>
+      </c>
+      <c r="BQ129" t="n">
+        <v>0.6686299999999999</v>
+      </c>
+      <c r="BR129" t="n">
+        <v>1.17776</v>
+      </c>
+      <c r="BS129" t="n">
+        <v>0.67587</v>
+      </c>
+      <c r="BT129" t="n">
+        <v>0.6431399999999999</v>
+      </c>
+      <c r="BU129" t="n">
+        <v>0.7316699999999999</v>
+      </c>
+      <c r="BV129" t="n">
+        <v>0.6596900000000001</v>
+      </c>
+      <c r="BW129" t="n">
+        <v>0.65413</v>
+      </c>
+      <c r="BX129" t="n">
+        <v>1.16291</v>
+      </c>
+      <c r="BY129" t="n">
+        <v>0.78051</v>
+      </c>
+      <c r="BZ129" t="n">
+        <v>1.44632</v>
+      </c>
+      <c r="CA129" t="n">
+        <v>0.76012</v>
+      </c>
+      <c r="CB129" t="n">
+        <v>0.74205</v>
+      </c>
+      <c r="CC129" t="n">
+        <v>1.01703</v>
+      </c>
+      <c r="CD129" t="n">
+        <v>1.51244</v>
+      </c>
+      <c r="CE129" t="n">
+        <v>0.64977</v>
+      </c>
+      <c r="CF129" t="n">
+        <v>1.32977</v>
+      </c>
+      <c r="CG129" t="n">
+        <v>0.5151399999999999</v>
+      </c>
+      <c r="CH129" t="n">
+        <v>1.16468</v>
+      </c>
+      <c r="CI129" t="n">
+        <v>1.50298</v>
+      </c>
+      <c r="CJ129" t="n">
+        <v>0.24002</v>
+      </c>
+      <c r="CK129" t="n">
+        <v>1.3688</v>
+      </c>
+      <c r="CL129" t="n">
+        <v>1.35158</v>
+      </c>
+      <c r="CM129" t="n">
+        <v>0.32906</v>
+      </c>
+      <c r="CN129" t="n">
+        <v>0.34456</v>
+      </c>
+      <c r="CO129" t="n">
+        <v>0.33435</v>
+      </c>
+      <c r="CP129" t="n">
+        <v>0.3127</v>
+      </c>
+      <c r="CQ129" t="n">
+        <v>0.33876</v>
+      </c>
+      <c r="CR129" t="n">
+        <v>0.93712</v>
+      </c>
+      <c r="CS129" t="n">
+        <v>0.30878</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="n">
+        <v>46151</v>
+      </c>
+      <c r="B130" t="n">
+        <v>0.32001</v>
+      </c>
+      <c r="C130" t="n">
+        <v>0.64479</v>
+      </c>
+      <c r="D130" t="n">
+        <v>0.39616</v>
+      </c>
+      <c r="E130" t="n">
+        <v>0.41355</v>
+      </c>
+      <c r="F130" t="n">
+        <v>0.33681</v>
+      </c>
+      <c r="G130" t="n">
+        <v>0.32168</v>
+      </c>
+      <c r="H130" t="n">
+        <v>0.33374</v>
+      </c>
+      <c r="I130" t="n">
+        <v>0.35063</v>
+      </c>
+      <c r="J130" t="n">
+        <v>0.31215</v>
+      </c>
+      <c r="K130" t="n">
+        <v>0.38008</v>
+      </c>
+      <c r="L130" t="n">
+        <v>0.35757</v>
+      </c>
+      <c r="M130" t="n">
+        <v>0.32869</v>
+      </c>
+      <c r="N130" t="n">
+        <v>0.32275</v>
+      </c>
+      <c r="O130" t="n">
+        <v>0.32228</v>
+      </c>
+      <c r="P130" t="n">
+        <v>0.31674</v>
+      </c>
+      <c r="Q130" t="n">
+        <v>0.31458</v>
+      </c>
+      <c r="R130" t="n">
+        <v>0.36795</v>
+      </c>
+      <c r="S130" t="n">
+        <v>0.32498</v>
+      </c>
+      <c r="T130" t="n">
+        <v>0.29824</v>
+      </c>
+      <c r="U130" t="n">
+        <v>0.28543</v>
+      </c>
+      <c r="V130" t="n">
+        <v>0.30082</v>
+      </c>
+      <c r="W130" t="n">
+        <v>0.31295</v>
+      </c>
+      <c r="X130" t="n">
+        <v>0.31612</v>
+      </c>
+      <c r="Y130" t="n">
+        <v>0.31151</v>
+      </c>
+      <c r="Z130" t="n">
+        <v>0.29797</v>
+      </c>
+      <c r="AA130" t="n">
+        <v>0.30282</v>
+      </c>
+      <c r="AB130" t="n">
+        <v>0.31384</v>
+      </c>
+      <c r="AC130" t="n">
+        <v>0.31614</v>
+      </c>
+      <c r="AD130" t="n">
+        <v>0.30796</v>
+      </c>
+      <c r="AE130" t="n">
+        <v>0.29399</v>
+      </c>
+      <c r="AF130" t="n">
+        <v>0.31846</v>
+      </c>
+      <c r="AG130" t="n">
+        <v>0.30918</v>
+      </c>
+      <c r="AH130" t="n">
+        <v>0.32968</v>
+      </c>
+      <c r="AI130" t="n">
+        <v>0.3488</v>
+      </c>
+      <c r="AJ130" t="n">
+        <v>0.37236</v>
+      </c>
+      <c r="AK130" t="n">
+        <v>0.37092</v>
+      </c>
+      <c r="AL130" t="n">
+        <v>0.32744</v>
+      </c>
+      <c r="AM130" t="n">
+        <v>0.95052</v>
+      </c>
+      <c r="AN130" t="n">
+        <v>0.36292</v>
+      </c>
+      <c r="AO130" t="n">
+        <v>0.34183</v>
+      </c>
+      <c r="AP130" t="n">
+        <v>0.45369</v>
+      </c>
+      <c r="AQ130" t="n">
+        <v>0.34238</v>
+      </c>
+      <c r="AR130" t="n">
+        <v>0.3308</v>
+      </c>
+      <c r="AS130" t="n">
+        <v>0.31515</v>
+      </c>
+      <c r="AT130" t="n">
+        <v>0.33275</v>
+      </c>
+      <c r="AU130" t="n">
+        <v>0.33261</v>
+      </c>
+      <c r="AV130" t="n">
+        <v>0.3093</v>
+      </c>
+      <c r="AW130" t="n">
+        <v>0.32563</v>
+      </c>
+      <c r="AX130" t="n">
+        <v>0.2764</v>
+      </c>
+      <c r="AY130" t="n">
+        <v>0.32426</v>
+      </c>
+      <c r="AZ130" t="n">
+        <v>0.33317</v>
+      </c>
+      <c r="BA130" t="n">
+        <v>0.31225</v>
+      </c>
+      <c r="BB130" t="n">
+        <v>0.31828</v>
+      </c>
+      <c r="BC130" t="n">
+        <v>0.3206</v>
+      </c>
+      <c r="BD130" t="n">
+        <v>0.32724</v>
+      </c>
+      <c r="BE130" t="n">
+        <v>0.33304</v>
+      </c>
+      <c r="BF130" t="n">
+        <v>0.32789</v>
+      </c>
+      <c r="BG130" t="n">
+        <v>0.3166</v>
+      </c>
+      <c r="BH130" t="n">
+        <v>0.30594</v>
+      </c>
+      <c r="BI130" t="n">
+        <v>0.30923</v>
+      </c>
+      <c r="BJ130" t="n">
+        <v>0.3108399999999999</v>
+      </c>
+      <c r="BK130" t="n">
+        <v>0.75467</v>
+      </c>
+      <c r="BL130" t="n">
+        <v>0.33667</v>
+      </c>
+      <c r="BM130" t="n">
+        <v>1.04667</v>
+      </c>
+      <c r="BN130" t="n">
+        <v>1.3039</v>
+      </c>
+      <c r="BO130" t="n">
+        <v>0.97797</v>
+      </c>
+      <c r="BP130" t="n">
+        <v>0.49142</v>
+      </c>
+      <c r="BQ130" t="n">
+        <v>0.33041</v>
+      </c>
+      <c r="BR130" t="n">
+        <v>0.35313</v>
+      </c>
+      <c r="BS130" t="n">
+        <v>0.36441</v>
+      </c>
+      <c r="BT130" t="n">
+        <v>0.34154</v>
+      </c>
+      <c r="BU130" t="n">
+        <v>0.33905</v>
+      </c>
+      <c r="BV130" t="n">
+        <v>0.3384</v>
+      </c>
+      <c r="BW130" t="n">
+        <v>0.75706</v>
+      </c>
+      <c r="BX130" t="n">
+        <v>0.3671</v>
+      </c>
+      <c r="BY130" t="n">
+        <v>0.75085</v>
+      </c>
+      <c r="BZ130" t="n">
+        <v>0.33815</v>
+      </c>
+      <c r="CA130" t="n">
+        <v>0.35106</v>
+      </c>
+      <c r="CB130" t="n">
+        <v>0.35695</v>
+      </c>
+      <c r="CC130" t="n">
+        <v>0.34886</v>
+      </c>
+      <c r="CD130" t="n">
+        <v>0.34104</v>
+      </c>
+      <c r="CE130" t="n">
+        <v>0.35004</v>
+      </c>
+      <c r="CF130" t="n">
+        <v>0.34803</v>
+      </c>
+      <c r="CG130" t="n">
+        <v>0.35301</v>
+      </c>
+      <c r="CH130" t="n">
+        <v>0.35909</v>
+      </c>
+      <c r="CI130" t="n">
+        <v>0.36336</v>
+      </c>
+      <c r="CJ130" t="n">
+        <v>0.36448</v>
+      </c>
+      <c r="CK130" t="n">
+        <v>0.36108</v>
+      </c>
+      <c r="CL130" t="n">
+        <v>0.34766</v>
+      </c>
+      <c r="CM130" t="n">
+        <v>0.35629</v>
+      </c>
+      <c r="CN130" t="n">
+        <v>0.35765</v>
+      </c>
+      <c r="CO130" t="n">
+        <v>0.32413</v>
+      </c>
+      <c r="CP130" t="n">
+        <v>0.30613</v>
+      </c>
+      <c r="CQ130" t="n">
+        <v>0.34307</v>
+      </c>
+      <c r="CR130" t="n">
+        <v>0.32271</v>
+      </c>
+      <c r="CS130" t="n">
+        <v>0.34267</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="n">
+        <v>46152</v>
+      </c>
+      <c r="B131" t="n">
+        <v>0.32867</v>
+      </c>
+      <c r="C131" t="n">
+        <v>0.34346</v>
+      </c>
+      <c r="D131" t="n">
+        <v>0.34245</v>
+      </c>
+      <c r="E131" t="n">
+        <v>0.3434700000000001</v>
+      </c>
+      <c r="F131" t="n">
+        <v>0.34443</v>
+      </c>
+      <c r="G131" t="n">
+        <v>0.3439</v>
+      </c>
+      <c r="H131" t="n">
+        <v>0.3431</v>
+      </c>
+      <c r="I131" t="n">
+        <v>0.33352</v>
+      </c>
+      <c r="J131" t="n">
+        <v>0.34246</v>
+      </c>
+      <c r="K131" t="n">
+        <v>0.33931</v>
+      </c>
+      <c r="L131" t="n">
+        <v>0.27257</v>
+      </c>
+      <c r="M131" t="n">
+        <v>0.3401</v>
+      </c>
+      <c r="N131" t="n">
+        <v>0.33419</v>
+      </c>
+      <c r="O131" t="n">
+        <v>0.33464</v>
+      </c>
+      <c r="P131" t="n">
+        <v>0.32234</v>
+      </c>
+      <c r="Q131" t="n">
+        <v>0.33264</v>
+      </c>
+      <c r="R131" t="n">
+        <v>0.3331</v>
+      </c>
+      <c r="S131" t="n">
+        <v>0.32709</v>
+      </c>
+      <c r="T131" t="n">
+        <v>0.34932</v>
+      </c>
+      <c r="U131" t="n">
+        <v>0.31744</v>
+      </c>
+      <c r="V131" t="n">
+        <v>0.32549</v>
+      </c>
+      <c r="W131" t="n">
+        <v>0.33253</v>
+      </c>
+      <c r="X131" t="n">
+        <v>0.33421</v>
+      </c>
+      <c r="Y131" t="n">
+        <v>0.32476</v>
+      </c>
+      <c r="Z131" t="n">
+        <v>0.32419</v>
+      </c>
+      <c r="AA131" t="n">
+        <v>0.3381</v>
+      </c>
+      <c r="AB131" t="n">
+        <v>0.3239</v>
+      </c>
+      <c r="AC131" t="n">
+        <v>0.33562</v>
+      </c>
+      <c r="AD131" t="n">
+        <v>0.3355</v>
+      </c>
+      <c r="AE131" t="n">
+        <v>0.32937</v>
+      </c>
+      <c r="AF131" t="n">
+        <v>0.32628</v>
+      </c>
+      <c r="AG131" t="n">
+        <v>0.31575</v>
+      </c>
+      <c r="AH131" t="n">
+        <v>0.3336</v>
+      </c>
+      <c r="AI131" t="n">
+        <v>0.32942</v>
+      </c>
+      <c r="AJ131" t="n">
+        <v>0.31837</v>
+      </c>
+      <c r="AK131" t="n">
+        <v>0.32457</v>
+      </c>
+      <c r="AL131" t="n">
+        <v>0.29984</v>
+      </c>
+      <c r="AM131" t="n">
+        <v>0.3183</v>
+      </c>
+      <c r="AN131" t="n">
+        <v>0.3217</v>
+      </c>
+      <c r="AO131" t="n">
+        <v>0.32427</v>
+      </c>
+      <c r="AP131" t="n">
+        <v>0.32292</v>
+      </c>
+      <c r="AQ131" t="n">
+        <v>0.31442</v>
+      </c>
+      <c r="AR131" t="n">
+        <v>0.32323</v>
+      </c>
+      <c r="AS131" t="n">
+        <v>0.31464</v>
+      </c>
+      <c r="AT131" t="n">
+        <v>0.3156</v>
+      </c>
+      <c r="AU131" t="n">
+        <v>0.32342</v>
+      </c>
+      <c r="AV131" t="n">
+        <v>0.32076</v>
+      </c>
+      <c r="AW131" t="n">
+        <v>0.32853</v>
+      </c>
+      <c r="AX131" t="n">
+        <v>0.31747</v>
+      </c>
+      <c r="AY131" t="n">
+        <v>0.36962</v>
+      </c>
+      <c r="AZ131" t="n">
+        <v>0.33574</v>
+      </c>
+      <c r="BA131" t="n">
+        <v>0.31915</v>
+      </c>
+      <c r="BB131" t="n">
+        <v>0.68733</v>
+      </c>
+      <c r="BC131" t="n">
+        <v>1.17756</v>
+      </c>
+      <c r="BD131" t="n">
+        <v>0.40685</v>
+      </c>
+      <c r="BE131" t="n">
+        <v>0.5173099999999999</v>
+      </c>
+      <c r="BF131" t="n">
+        <v>0.41142</v>
+      </c>
+      <c r="BG131" t="n">
+        <v>0.37882</v>
+      </c>
+      <c r="BH131" t="n">
+        <v>0.40276</v>
+      </c>
+      <c r="BI131" t="n">
+        <v>0.47282</v>
+      </c>
+      <c r="BJ131" t="n">
+        <v>0.34107</v>
+      </c>
+      <c r="BK131" t="n">
+        <v>0.35968</v>
+      </c>
+      <c r="BL131" t="n">
+        <v>0.33329</v>
+      </c>
+      <c r="BM131" t="n">
+        <v>0.34883</v>
+      </c>
+      <c r="BN131" t="n">
+        <v>0.35005</v>
+      </c>
+      <c r="BO131" t="n">
+        <v>0.55399</v>
+      </c>
+      <c r="BP131" t="n">
+        <v>0.3776600000000001</v>
+      </c>
+      <c r="BQ131" t="n">
+        <v>0.3468</v>
+      </c>
+      <c r="BR131" t="n">
+        <v>0.35268</v>
+      </c>
+      <c r="BS131" t="n">
+        <v>0.4064</v>
+      </c>
+      <c r="BT131" t="n">
+        <v>0.3442</v>
+      </c>
+      <c r="BU131" t="n">
+        <v>0.37858</v>
+      </c>
+      <c r="BV131" t="n">
+        <v>0.4228</v>
+      </c>
+      <c r="BW131" t="n">
+        <v>0.34876</v>
+      </c>
+      <c r="BX131" t="n">
+        <v>0.35182</v>
+      </c>
+      <c r="BY131" t="n">
+        <v>0.39534</v>
+      </c>
+      <c r="BZ131" t="n">
+        <v>0.34177</v>
+      </c>
+      <c r="CA131" t="n">
+        <v>0.36961</v>
+      </c>
+      <c r="CB131" t="n">
+        <v>0.47069</v>
+      </c>
+      <c r="CC131" t="n">
+        <v>0.41116</v>
+      </c>
+      <c r="CD131" t="n">
+        <v>0.37069</v>
+      </c>
+      <c r="CE131" t="n">
+        <v>0.40381</v>
+      </c>
+      <c r="CF131" t="n">
+        <v>0.57686</v>
+      </c>
+      <c r="CG131" t="n">
+        <v>0.37242</v>
+      </c>
+      <c r="CH131" t="n">
+        <v>0.36886</v>
+      </c>
+      <c r="CI131" t="n">
+        <v>0.6502899999999999</v>
+      </c>
+      <c r="CJ131" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CK131" t="n">
+        <v>0.4265</v>
+      </c>
+      <c r="CL131" t="n">
+        <v>0.58716</v>
+      </c>
+      <c r="CM131" t="n">
+        <v>0.57464</v>
+      </c>
+      <c r="CN131" t="n">
+        <v>0.8150599999999999</v>
+      </c>
+      <c r="CO131" t="n">
+        <v>0.34343</v>
+      </c>
+      <c r="CP131" t="n">
+        <v>0.6638099999999999</v>
+      </c>
+      <c r="CQ131" t="n">
+        <v>0.35231</v>
+      </c>
+      <c r="CR131" t="n">
+        <v>0.33273</v>
+      </c>
+      <c r="CS131" t="n">
+        <v>0.33346</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="B132" t="n">
+        <v>0.32209</v>
+      </c>
+      <c r="C132" t="n">
+        <v>0.40413</v>
+      </c>
+      <c r="D132" t="n">
+        <v>0.36927</v>
+      </c>
+      <c r="E132" t="n">
+        <v>0.35966</v>
+      </c>
+      <c r="F132" t="n">
+        <v>0.35502</v>
+      </c>
+      <c r="G132" t="n">
+        <v>0.35217</v>
+      </c>
+      <c r="H132" t="n">
+        <v>0.35183</v>
+      </c>
+      <c r="I132" t="n">
+        <v>0.355</v>
+      </c>
+      <c r="J132" t="n">
+        <v>0.3511</v>
+      </c>
+      <c r="K132" t="n">
+        <v>0.34974</v>
+      </c>
+      <c r="L132" t="n">
+        <v>0.35195</v>
+      </c>
+      <c r="M132" t="n">
+        <v>0.34581</v>
+      </c>
+      <c r="N132" t="n">
+        <v>0.35296</v>
+      </c>
+      <c r="O132" t="n">
+        <v>0.34907</v>
+      </c>
+      <c r="P132" t="n">
+        <v>0.3491</v>
+      </c>
+      <c r="Q132" t="n">
+        <v>0.34506</v>
+      </c>
+      <c r="R132" t="n">
+        <v>0.34804</v>
+      </c>
+      <c r="S132" t="n">
+        <v>0.35246</v>
+      </c>
+      <c r="T132" t="n">
+        <v>0.35278</v>
+      </c>
+      <c r="U132" t="n">
+        <v>0.34067</v>
+      </c>
+      <c r="V132" t="n">
+        <v>0.35044</v>
+      </c>
+      <c r="W132" t="n">
+        <v>0.35175</v>
+      </c>
+      <c r="X132" t="n">
+        <v>0.34949</v>
+      </c>
+      <c r="Y132" t="n">
+        <v>0.35305</v>
+      </c>
+      <c r="Z132" t="n">
+        <v>0.35305</v>
+      </c>
+      <c r="AA132" t="n">
+        <v>0.36258</v>
+      </c>
+      <c r="AB132" t="n">
+        <v>0.35886</v>
+      </c>
+      <c r="AC132" t="n">
+        <v>0.37286</v>
+      </c>
+      <c r="AD132" t="n">
+        <v>0.34954</v>
+      </c>
+      <c r="AE132" t="n">
+        <v>0.34946</v>
+      </c>
+      <c r="AF132" t="n">
+        <v>0.34416</v>
+      </c>
+      <c r="AG132" t="n">
+        <v>0.34485</v>
+      </c>
+      <c r="AH132" t="n">
+        <v>0.3509</v>
+      </c>
+      <c r="AI132" t="n">
+        <v>0.34236</v>
+      </c>
+      <c r="AJ132" t="n">
+        <v>0.32483</v>
+      </c>
+      <c r="AK132" t="n">
+        <v>1.17591</v>
+      </c>
+      <c r="AL132" t="n">
+        <v>0.4416600000000001</v>
+      </c>
+      <c r="AM132" t="n">
+        <v>0.73494</v>
+      </c>
+      <c r="AN132" t="n">
+        <v>0.50445</v>
+      </c>
+      <c r="AO132" t="n">
+        <v>0.74978</v>
+      </c>
+      <c r="AP132" t="n">
+        <v>0.43213</v>
+      </c>
+      <c r="AQ132" t="n">
+        <v>0.58688</v>
+      </c>
+      <c r="AR132" t="n">
+        <v>0.3325</v>
+      </c>
+      <c r="AS132" t="n">
+        <v>0.31315</v>
+      </c>
+      <c r="AT132" t="n">
+        <v>0.82029</v>
+      </c>
+      <c r="AU132" t="n">
+        <v>0.35912</v>
+      </c>
+      <c r="AV132" t="n">
+        <v>0.37718</v>
+      </c>
+      <c r="AW132" t="n">
+        <v>0.29819</v>
+      </c>
+      <c r="AX132" t="n">
+        <v>0.28156</v>
+      </c>
+      <c r="AY132" t="n">
+        <v>0.31931</v>
+      </c>
+      <c r="AZ132" t="n">
+        <v>0.29403</v>
+      </c>
+      <c r="BA132" t="n">
+        <v>0.28706</v>
+      </c>
+      <c r="BB132" t="n">
+        <v>0.30524</v>
+      </c>
+      <c r="BC132" t="n">
+        <v>0.33284</v>
+      </c>
+      <c r="BD132" t="n">
+        <v>0.34277</v>
+      </c>
+      <c r="BE132" t="n">
+        <v>0.60842</v>
+      </c>
+      <c r="BF132" t="n">
+        <v>0.37087</v>
+      </c>
+      <c r="BG132" t="n">
+        <v>0.3409700000000001</v>
+      </c>
+      <c r="BH132" t="n">
+        <v>0.33653</v>
+      </c>
+      <c r="BI132" t="n">
+        <v>0.40495</v>
+      </c>
+      <c r="BJ132" t="n">
+        <v>0.34118</v>
+      </c>
+      <c r="BK132" t="n">
+        <v>0.64739</v>
+      </c>
+      <c r="BL132" t="n">
+        <v>0.51449</v>
+      </c>
+      <c r="BM132" t="n">
+        <v>0.76998</v>
+      </c>
+      <c r="BN132" t="n">
+        <v>0.6721699999999999</v>
+      </c>
+      <c r="BO132" t="n">
+        <v>1.10437</v>
+      </c>
+      <c r="BP132" t="n">
+        <v>0.63528</v>
+      </c>
+      <c r="BQ132" t="n">
+        <v>0.61276</v>
+      </c>
+      <c r="BR132" t="n">
+        <v>0.34466</v>
+      </c>
+      <c r="BS132" t="n">
+        <v>0.8269299999999999</v>
+      </c>
+      <c r="BT132" t="n">
+        <v>0.64203</v>
+      </c>
+      <c r="BU132" t="n">
+        <v>0.81636</v>
+      </c>
+      <c r="BV132" t="n">
+        <v>0.35338</v>
+      </c>
+      <c r="BW132" t="n">
+        <v>1.15169</v>
+      </c>
+      <c r="BX132" t="n">
+        <v>1.14892</v>
+      </c>
+      <c r="BY132" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BZ132" t="n">
+        <v>1.18038</v>
+      </c>
+      <c r="CA132" t="n">
+        <v>0.94372</v>
+      </c>
+      <c r="CB132" t="n">
+        <v>0.9015599999999999</v>
+      </c>
+      <c r="CC132" t="n">
+        <v>1.22168</v>
+      </c>
+      <c r="CD132" t="n">
+        <v>0.79159</v>
+      </c>
+      <c r="CE132" t="n">
+        <v>1.03075</v>
+      </c>
+      <c r="CF132" t="n">
+        <v>0.80133</v>
+      </c>
+      <c r="CG132" t="n">
+        <v>1.59872</v>
+      </c>
+      <c r="CH132" t="n">
+        <v>1.76351</v>
+      </c>
+      <c r="CI132" t="n">
+        <v>0.78838</v>
+      </c>
+      <c r="CJ132" t="n">
+        <v>0.69965</v>
+      </c>
+      <c r="CK132" t="n">
+        <v>1.20029</v>
+      </c>
+      <c r="CL132" t="n">
+        <v>1.37415</v>
+      </c>
+      <c r="CM132" t="n">
+        <v>0.6809500000000001</v>
+      </c>
+      <c r="CN132" t="n">
+        <v>0.40469</v>
+      </c>
+      <c r="CO132" t="n">
+        <v>0.39582</v>
+      </c>
+      <c r="CP132" t="n">
+        <v>0.36528</v>
+      </c>
+      <c r="CQ132" t="n">
+        <v>0.36801</v>
+      </c>
+      <c r="CR132" t="n">
+        <v>0.35574</v>
+      </c>
+      <c r="CS132" t="n">
+        <v>0.34966</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="n">
+        <v>46156</v>
+      </c>
+      <c r="B133" t="n">
+        <v>0.34577</v>
+      </c>
+      <c r="C133" t="n">
+        <v>0.45227</v>
+      </c>
+      <c r="D133" t="n">
+        <v>0.52373</v>
+      </c>
+      <c r="E133" t="n">
+        <v>0.47145</v>
+      </c>
+      <c r="F133" t="n">
+        <v>0.6111799999999999</v>
+      </c>
+      <c r="G133" t="n">
+        <v>0.39428</v>
+      </c>
+      <c r="H133" t="n">
+        <v>0.39438</v>
+      </c>
+      <c r="I133" t="n">
+        <v>0.38344</v>
+      </c>
+      <c r="J133" t="n">
+        <v>0.38815</v>
+      </c>
+      <c r="K133" t="n">
+        <v>0.38775</v>
+      </c>
+      <c r="L133" t="n">
+        <v>0.39372</v>
+      </c>
+      <c r="M133" t="n">
+        <v>0.38059</v>
+      </c>
+      <c r="N133" t="n">
+        <v>0.38763</v>
+      </c>
+      <c r="O133" t="n">
+        <v>0.39251</v>
+      </c>
+      <c r="P133" t="n">
+        <v>0.39073</v>
+      </c>
+      <c r="Q133" t="n">
+        <v>0.37861</v>
+      </c>
+      <c r="R133" t="n">
+        <v>0.38093</v>
+      </c>
+      <c r="S133" t="n">
+        <v>1.39366</v>
+      </c>
+      <c r="T133" t="n">
+        <v>0.36968</v>
+      </c>
+      <c r="U133" t="n">
+        <v>0.39205</v>
+      </c>
+      <c r="V133" t="n">
+        <v>0.37153</v>
+      </c>
+      <c r="W133" t="n">
+        <v>0.37385</v>
+      </c>
+      <c r="X133" t="n">
+        <v>0.37757</v>
+      </c>
+      <c r="Y133" t="n">
+        <v>0.38893</v>
+      </c>
+      <c r="Z133" t="n">
+        <v>0.37538</v>
+      </c>
+      <c r="AA133" t="n">
+        <v>0.41134</v>
+      </c>
+      <c r="AB133" t="n">
+        <v>0.41379</v>
+      </c>
+      <c r="AC133" t="n">
+        <v>0.49893</v>
+      </c>
+      <c r="AD133" t="n">
+        <v>0.4561</v>
+      </c>
+      <c r="AE133" t="n">
+        <v>0.41836</v>
+      </c>
+      <c r="AF133" t="n">
+        <v>0.45352</v>
+      </c>
+      <c r="AG133" t="n">
+        <v>0.41694</v>
+      </c>
+      <c r="AH133" t="n">
+        <v>0.57236</v>
+      </c>
+      <c r="AI133" t="n">
+        <v>1.13409</v>
+      </c>
+      <c r="AJ133" t="n">
+        <v>0.82735</v>
+      </c>
+      <c r="AK133" t="n">
+        <v>1.18133</v>
+      </c>
+      <c r="AL133" t="n">
+        <v>1.21795</v>
+      </c>
+      <c r="AM133" t="n">
+        <v>1.5452</v>
+      </c>
+      <c r="AN133" t="n">
+        <v>1.29757</v>
+      </c>
+      <c r="AO133" t="n">
+        <v>0.42748</v>
+      </c>
+      <c r="AP133" t="n">
+        <v>0.36395</v>
+      </c>
+      <c r="AQ133" t="n">
+        <v>0.3479100000000001</v>
+      </c>
+      <c r="AR133" t="n">
+        <v>0.35575</v>
+      </c>
+      <c r="AS133" t="n">
+        <v>0.6526799999999999</v>
+      </c>
+      <c r="AT133" t="n">
+        <v>0.6547200000000001</v>
+      </c>
+      <c r="AU133" t="n">
+        <v>0.67749</v>
+      </c>
+      <c r="AV133" t="n">
+        <v>1.02431</v>
+      </c>
+      <c r="AW133" t="n">
+        <v>0.7877000000000001</v>
+      </c>
+      <c r="AX133" t="n">
+        <v>0.56831</v>
+      </c>
+      <c r="AY133" t="n">
+        <v>0.59966</v>
+      </c>
+      <c r="AZ133" t="n">
+        <v>0.59078</v>
+      </c>
+      <c r="BA133" t="n">
+        <v>0.6701699999999999</v>
+      </c>
+      <c r="BB133" t="n">
+        <v>0.9192</v>
+      </c>
+      <c r="BC133" t="n">
+        <v>0.9302</v>
+      </c>
+      <c r="BD133" t="n">
+        <v>1.26235</v>
+      </c>
+      <c r="BE133" t="n">
+        <v>0.64362</v>
+      </c>
+      <c r="BF133" t="n">
+        <v>0.6484099999999999</v>
+      </c>
+      <c r="BG133" t="n">
+        <v>0.6372599999999999</v>
+      </c>
+      <c r="BH133" t="n">
+        <v>0.6341100000000001</v>
+      </c>
+      <c r="BI133" t="n">
+        <v>1.13907</v>
+      </c>
+      <c r="BJ133" t="n">
+        <v>0.33923</v>
+      </c>
+      <c r="BK133" t="n">
+        <v>0.3154</v>
+      </c>
+      <c r="BL133" t="n">
+        <v>0.33419</v>
+      </c>
+      <c r="BM133" t="n">
+        <v>0.34931</v>
+      </c>
+      <c r="BN133" t="n">
+        <v>0.3375</v>
+      </c>
+      <c r="BO133" t="n">
+        <v>0.3565</v>
+      </c>
+      <c r="BP133" t="n">
+        <v>0.35159</v>
+      </c>
+      <c r="BQ133" t="n">
+        <v>0.3541</v>
+      </c>
+      <c r="BR133" t="n">
+        <v>0.35931</v>
+      </c>
+      <c r="BS133" t="n">
+        <v>0.37005</v>
+      </c>
+      <c r="BT133" t="n">
+        <v>0.34461</v>
+      </c>
+      <c r="BU133" t="n">
+        <v>0.36311</v>
+      </c>
+      <c r="BV133" t="n">
+        <v>0.33162</v>
+      </c>
+      <c r="BW133" t="n">
+        <v>0.39119</v>
+      </c>
+      <c r="BX133" t="n">
+        <v>0.4107</v>
+      </c>
+      <c r="BY133" t="n">
+        <v>0.45489</v>
+      </c>
+      <c r="BZ133" t="n">
+        <v>0.41769</v>
+      </c>
+      <c r="CA133" t="n">
+        <v>0.4680299999999999</v>
+      </c>
+      <c r="CB133" t="n">
+        <v>0.46822</v>
+      </c>
+      <c r="CC133" t="n">
+        <v>0.50031</v>
+      </c>
+      <c r="CD133" t="n">
+        <v>0.61448</v>
+      </c>
+      <c r="CE133" t="n">
+        <v>0.71938</v>
+      </c>
+      <c r="CF133" t="n">
+        <v>0.80721</v>
+      </c>
+      <c r="CG133" t="n">
+        <v>0.57868</v>
+      </c>
+      <c r="CH133" t="n">
+        <v>0.7028300000000001</v>
+      </c>
+      <c r="CI133" t="n">
+        <v>0.85903</v>
+      </c>
+      <c r="CJ133" t="n">
+        <v>0.96924</v>
+      </c>
+      <c r="CK133" t="n">
+        <v>0.7227899999999999</v>
+      </c>
+      <c r="CL133" t="n">
+        <v>0.76461</v>
+      </c>
+      <c r="CM133" t="n">
+        <v>0.61733</v>
+      </c>
+      <c r="CN133" t="n">
+        <v>0.6656</v>
+      </c>
+      <c r="CO133" t="n">
+        <v>1.04436</v>
+      </c>
+      <c r="CP133" t="n">
+        <v>0.73961</v>
+      </c>
+      <c r="CQ133" t="n">
+        <v>0.44487</v>
+      </c>
+      <c r="CR133" t="n">
+        <v>0.44141</v>
+      </c>
+      <c r="CS133" t="n">
+        <v>0.43461</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="n">
+        <v>46157</v>
+      </c>
+      <c r="B134" t="n">
+        <v>0.3955</v>
+      </c>
+      <c r="C134" t="n">
+        <v>0.50114</v>
+      </c>
+      <c r="D134" t="n">
+        <v>0.40357</v>
+      </c>
+      <c r="E134" t="n">
+        <v>0.41415</v>
+      </c>
+      <c r="F134" t="n">
+        <v>0.42433</v>
+      </c>
+      <c r="G134" t="n">
+        <v>0.42752</v>
+      </c>
+      <c r="H134" t="n">
+        <v>0.41744</v>
+      </c>
+      <c r="I134" t="n">
+        <v>0.41588</v>
+      </c>
+      <c r="J134" t="n">
+        <v>0.40918</v>
+      </c>
+      <c r="K134" t="n">
+        <v>0.37968</v>
+      </c>
+      <c r="L134" t="n">
+        <v>0.41262</v>
+      </c>
+      <c r="M134" t="n">
+        <v>0.37264</v>
+      </c>
+      <c r="N134" t="n">
+        <v>0.37908</v>
+      </c>
+      <c r="O134" t="n">
+        <v>0.45806</v>
+      </c>
+      <c r="P134" t="n">
+        <v>0.36815</v>
+      </c>
+      <c r="Q134" t="n">
+        <v>0.36321</v>
+      </c>
+      <c r="R134" t="n">
+        <v>0.35736</v>
+      </c>
+      <c r="S134" t="n">
+        <v>0.35321</v>
+      </c>
+      <c r="T134" t="n">
+        <v>0.35001</v>
+      </c>
+      <c r="U134" t="n">
+        <v>0.35899</v>
+      </c>
+      <c r="V134" t="n">
+        <v>0.28941</v>
+      </c>
+      <c r="W134" t="n">
+        <v>0.34923</v>
+      </c>
+      <c r="X134" t="n">
+        <v>0.3426</v>
+      </c>
+      <c r="Y134" t="n">
+        <v>0.35288</v>
+      </c>
+      <c r="Z134" t="n">
+        <v>0.35899</v>
+      </c>
+      <c r="AA134" t="n">
+        <v>0.36093</v>
+      </c>
+      <c r="AB134" t="n">
+        <v>0.36556</v>
+      </c>
+      <c r="AC134" t="n">
+        <v>0.37256</v>
+      </c>
+      <c r="AD134" t="n">
+        <v>0.3491</v>
+      </c>
+      <c r="AE134" t="n">
+        <v>0.35442</v>
+      </c>
+      <c r="AF134" t="n">
+        <v>0.34818</v>
+      </c>
+      <c r="AG134" t="n">
+        <v>0.37251</v>
+      </c>
+      <c r="AH134" t="n">
+        <v>0.39499</v>
+      </c>
+      <c r="AI134" t="n">
+        <v>0.35803</v>
+      </c>
+      <c r="AJ134" t="n">
+        <v>0.38102</v>
+      </c>
+      <c r="AK134" t="n">
+        <v>0.3923</v>
+      </c>
+      <c r="AL134" t="n">
+        <v>0.37837</v>
+      </c>
+      <c r="AM134" t="n">
+        <v>0.37963</v>
+      </c>
+      <c r="AN134" t="n">
+        <v>0.35138</v>
+      </c>
+      <c r="AO134" t="n">
+        <v>0.35934</v>
+      </c>
+      <c r="AP134" t="n">
+        <v>0.33925</v>
+      </c>
+      <c r="AQ134" t="n">
+        <v>0.33411</v>
+      </c>
+      <c r="AR134" t="n">
+        <v>0.34133</v>
+      </c>
+      <c r="AS134" t="n">
+        <v>0.36888</v>
+      </c>
+      <c r="AT134" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AU134" t="n">
+        <v>0.64938</v>
+      </c>
+      <c r="AV134" t="n">
+        <v>0.62094</v>
+      </c>
+      <c r="AW134" t="n">
+        <v>0.6156699999999999</v>
+      </c>
+      <c r="AX134" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AY134" t="n">
+        <v>0.63703</v>
+      </c>
+      <c r="AZ134" t="n">
+        <v>0.62609</v>
+      </c>
+      <c r="BA134" t="n">
+        <v>0.91249</v>
+      </c>
+      <c r="BB134" t="n">
+        <v>0.6380399999999999</v>
+      </c>
+      <c r="BC134" t="n">
+        <v>0.7152000000000001</v>
+      </c>
+      <c r="BD134" t="n">
+        <v>0.67464</v>
+      </c>
+      <c r="BE134" t="n">
+        <v>0.72525</v>
+      </c>
+      <c r="BF134" t="n">
+        <v>1.67955</v>
+      </c>
+      <c r="BG134" t="n">
+        <v>0.3655</v>
+      </c>
+      <c r="BH134" t="n">
+        <v>0.1586</v>
+      </c>
+      <c r="BI134" t="n">
+        <v>0.22127</v>
+      </c>
+      <c r="BJ134" t="n">
+        <v>0.30182</v>
+      </c>
+      <c r="BK134" t="n">
+        <v>0.29949</v>
+      </c>
+      <c r="BL134" t="n">
+        <v>0.32198</v>
+      </c>
+      <c r="BM134" t="n">
+        <v>0.34348</v>
+      </c>
+      <c r="BN134" t="n">
+        <v>0.33574</v>
+      </c>
+      <c r="BO134" t="n">
+        <v>0.33798</v>
+      </c>
+      <c r="BP134" t="n">
+        <v>0.3387</v>
+      </c>
+      <c r="BQ134" t="n">
+        <v>0.35669</v>
+      </c>
+      <c r="BR134" t="n">
+        <v>0.37789</v>
+      </c>
+      <c r="BS134" t="n">
+        <v>0.37771</v>
+      </c>
+      <c r="BT134" t="n">
+        <v>0.64622</v>
+      </c>
+      <c r="BU134" t="n">
+        <v>0.4712</v>
+      </c>
+      <c r="BV134" t="n">
+        <v>0.33462</v>
+      </c>
+      <c r="BW134" t="n">
+        <v>0.42398</v>
+      </c>
+      <c r="BX134" t="n">
+        <v>0.4105</v>
+      </c>
+      <c r="BY134" t="n">
+        <v>0.42249</v>
+      </c>
+      <c r="BZ134" t="n">
+        <v>0.40115</v>
+      </c>
+      <c r="CA134" t="n">
+        <v>0.39151</v>
+      </c>
+      <c r="CB134" t="n">
+        <v>0.34706</v>
+      </c>
+      <c r="CC134" t="n">
+        <v>0.35027</v>
+      </c>
+      <c r="CD134" t="n">
+        <v>0.36894</v>
+      </c>
+      <c r="CE134" t="n">
+        <v>0.37743</v>
+      </c>
+      <c r="CF134" t="n">
+        <v>0.32491</v>
+      </c>
+      <c r="CG134" t="n">
+        <v>0.3371</v>
+      </c>
+      <c r="CH134" t="n">
+        <v>0.36868</v>
+      </c>
+      <c r="CI134" t="n">
+        <v>0.36804</v>
+      </c>
+      <c r="CJ134" t="n">
+        <v>0.35319</v>
+      </c>
+      <c r="CK134" t="n">
+        <v>0.3594</v>
+      </c>
+      <c r="CL134" t="n">
+        <v>0.35477</v>
+      </c>
+      <c r="CM134" t="n">
+        <v>0.37355</v>
+      </c>
+      <c r="CN134" t="n">
+        <v>0.33439</v>
+      </c>
+      <c r="CO134" t="n">
+        <v>0.35625</v>
+      </c>
+      <c r="CP134" t="n">
+        <v>0.31393</v>
+      </c>
+      <c r="CQ134" t="n">
+        <v>0.3476</v>
+      </c>
+      <c r="CR134" t="n">
+        <v>0.33431</v>
+      </c>
+      <c r="CS134" t="n">
+        <v>0.32889</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="n">
+        <v>46158</v>
+      </c>
+      <c r="B135" t="n">
+        <v>0.29641</v>
+      </c>
+      <c r="C135" t="n">
+        <v>0.45594</v>
+      </c>
+      <c r="D135" t="n">
+        <v>1.12652</v>
+      </c>
+      <c r="E135" t="n">
+        <v>0.37204</v>
+      </c>
+      <c r="F135" t="n">
+        <v>0.35577</v>
+      </c>
+      <c r="G135" t="n">
+        <v>0.9264199999999999</v>
+      </c>
+      <c r="H135" t="n">
+        <v>0.34236</v>
+      </c>
+      <c r="I135" t="n">
+        <v>0.30818</v>
+      </c>
+      <c r="J135" t="n">
+        <v>0.29086</v>
+      </c>
+      <c r="K135" t="n">
+        <v>0.33449</v>
+      </c>
+      <c r="L135" t="n">
+        <v>0.27489</v>
+      </c>
+      <c r="M135" t="n">
+        <v>0.27238</v>
+      </c>
+      <c r="N135" t="n">
+        <v>0.30812</v>
+      </c>
+      <c r="O135" t="n">
+        <v>0.27273</v>
+      </c>
+      <c r="P135" t="n">
+        <v>0.31258</v>
+      </c>
+      <c r="Q135" t="n">
+        <v>0.34448</v>
+      </c>
+      <c r="R135" t="n">
+        <v>0.3072</v>
+      </c>
+      <c r="S135" t="n">
+        <v>0.26034</v>
+      </c>
+      <c r="T135" t="n">
+        <v>0.29109</v>
+      </c>
+      <c r="U135" t="n">
+        <v>0.2988</v>
+      </c>
+      <c r="V135" t="n">
+        <v>0.30706</v>
+      </c>
+      <c r="W135" t="n">
+        <v>0.29467</v>
+      </c>
+      <c r="X135" t="n">
+        <v>0.29915</v>
+      </c>
+      <c r="Y135" t="n">
+        <v>0.30362</v>
+      </c>
+      <c r="Z135" t="n">
+        <v>0.25288</v>
+      </c>
+      <c r="AA135" t="n">
+        <v>0.3081</v>
+      </c>
+      <c r="AB135" t="n">
+        <v>0.25196</v>
+      </c>
+      <c r="AC135" t="n">
+        <v>0.24622</v>
+      </c>
+      <c r="AD135" t="n">
+        <v>0.32603</v>
+      </c>
+      <c r="AE135" t="n">
+        <v>0.28659</v>
+      </c>
+      <c r="AF135" t="n">
+        <v>0.27913</v>
+      </c>
+      <c r="AG135" t="n">
+        <v>0.30738</v>
+      </c>
+      <c r="AH135" t="n">
+        <v>0.24144</v>
+      </c>
+      <c r="AI135" t="n">
+        <v>0.34284</v>
+      </c>
+      <c r="AJ135" t="n">
+        <v>0.30817</v>
+      </c>
+      <c r="AK135" t="n">
+        <v>0.30681</v>
+      </c>
+      <c r="AL135" t="n">
+        <v>0.30207</v>
+      </c>
+      <c r="AM135" t="n">
+        <v>0.18457</v>
+      </c>
+      <c r="AN135" t="n">
+        <v>0.28221</v>
+      </c>
+      <c r="AO135" t="n">
+        <v>0.24718</v>
+      </c>
+      <c r="AP135" t="n">
+        <v>0.27162</v>
+      </c>
+      <c r="AQ135" t="n">
+        <v>0.26351</v>
+      </c>
+      <c r="AR135" t="n">
+        <v>0.25961</v>
+      </c>
+      <c r="AS135" t="n">
+        <v>0.09356999999999999</v>
+      </c>
+      <c r="AT135" t="n">
+        <v>0.31697</v>
+      </c>
+      <c r="AU135" t="n">
+        <v>0.30806</v>
+      </c>
+      <c r="AV135" t="n">
+        <v>0.2702</v>
+      </c>
+      <c r="AW135" t="n">
+        <v>0.258</v>
+      </c>
+      <c r="AX135" t="n">
+        <v>0.03348</v>
+      </c>
+      <c r="AY135" t="n">
+        <v>0.2894</v>
+      </c>
+      <c r="AZ135" t="n">
+        <v>0.28192</v>
+      </c>
+      <c r="BA135" t="n">
+        <v>0.19759</v>
+      </c>
+      <c r="BB135" t="n">
+        <v>0.31346</v>
+      </c>
+      <c r="BC135" t="n">
+        <v>0.31097</v>
+      </c>
+      <c r="BD135" t="n">
+        <v>0.31273</v>
+      </c>
+      <c r="BE135" t="n">
+        <v>0.30748</v>
+      </c>
+      <c r="BF135" t="n">
+        <v>0.25102</v>
+      </c>
+      <c r="BG135" t="n">
+        <v>0.27002</v>
+      </c>
+      <c r="BH135" t="n">
+        <v>0.25795</v>
+      </c>
+      <c r="BI135" t="n">
+        <v>0.24106</v>
+      </c>
+      <c r="BJ135" t="n">
+        <v>0.27628</v>
+      </c>
+      <c r="BK135" t="n">
+        <v>0.28492</v>
+      </c>
+      <c r="BL135" t="n">
+        <v>0.27446</v>
+      </c>
+      <c r="BM135" t="n">
+        <v>0.32175</v>
+      </c>
+      <c r="BN135" t="n">
+        <v>0.3235</v>
+      </c>
+      <c r="BO135" t="n">
+        <v>0.31642</v>
+      </c>
+      <c r="BP135" t="n">
+        <v>0.33898</v>
+      </c>
+      <c r="BQ135" t="n">
+        <v>0.33628</v>
+      </c>
+      <c r="BR135" t="n">
+        <v>0.34566</v>
+      </c>
+      <c r="BS135" t="n">
+        <v>0.36222</v>
+      </c>
+      <c r="BT135" t="n">
+        <v>0.34121</v>
+      </c>
+      <c r="BU135" t="n">
+        <v>0.37331</v>
+      </c>
+      <c r="BV135" t="n">
+        <v>0.38175</v>
+      </c>
+      <c r="BW135" t="n">
+        <v>0.39957</v>
+      </c>
+      <c r="BX135" t="n">
+        <v>0.3771</v>
+      </c>
+      <c r="BY135" t="n">
+        <v>0.51028</v>
+      </c>
+      <c r="BZ135" t="n">
+        <v>0.30226</v>
+      </c>
+      <c r="CA135" t="n">
+        <v>0.35045</v>
+      </c>
+      <c r="CB135" t="n">
+        <v>0.33848</v>
+      </c>
+      <c r="CC135" t="n">
+        <v>0.35277</v>
+      </c>
+      <c r="CD135" t="n">
+        <v>0.33171</v>
+      </c>
+      <c r="CE135" t="n">
+        <v>0.33903</v>
+      </c>
+      <c r="CF135" t="n">
+        <v>0.35788</v>
+      </c>
+      <c r="CG135" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="CH135" t="n">
+        <v>0.5013</v>
+      </c>
+      <c r="CI135" t="n">
+        <v>0.38621</v>
+      </c>
+      <c r="CJ135" t="n">
+        <v>0.43346</v>
+      </c>
+      <c r="CK135" t="n">
+        <v>0.34736</v>
+      </c>
+      <c r="CL135" t="n">
+        <v>0.33741</v>
+      </c>
+      <c r="CM135" t="n">
+        <v>0.32356</v>
+      </c>
+      <c r="CN135" t="n">
+        <v>0.33456</v>
+      </c>
+      <c r="CO135" t="n">
+        <v>0.32636</v>
+      </c>
+      <c r="CP135" t="n">
+        <v>0.3052</v>
+      </c>
+      <c r="CQ135" t="n">
+        <v>0.33102</v>
+      </c>
+      <c r="CR135" t="n">
+        <v>0.305</v>
+      </c>
+      <c r="CS135" t="n">
+        <v>0.32128</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="n">
+        <v>46159</v>
+      </c>
+      <c r="B136" t="n">
+        <v>0.30007</v>
+      </c>
+      <c r="C136" t="n">
+        <v>0.7486699999999999</v>
+      </c>
+      <c r="D136" t="n">
+        <v>0.32688</v>
+      </c>
+      <c r="E136" t="n">
+        <v>0.3267</v>
+      </c>
+      <c r="F136" t="n">
+        <v>0.32948</v>
+      </c>
+      <c r="G136" t="n">
+        <v>0.33088</v>
+      </c>
+      <c r="H136" t="n">
+        <v>0.26662</v>
+      </c>
+      <c r="I136" t="n">
+        <v>0.29143</v>
+      </c>
+      <c r="J136" t="n">
+        <v>0.28701</v>
+      </c>
+      <c r="K136" t="n">
+        <v>0.30579</v>
+      </c>
+      <c r="L136" t="n">
+        <v>0.23491</v>
+      </c>
+      <c r="M136" t="n">
+        <v>0.28487</v>
+      </c>
+      <c r="N136" t="n">
+        <v>0.29271</v>
+      </c>
+      <c r="O136" t="n">
+        <v>0.28866</v>
+      </c>
+      <c r="P136" t="n">
+        <v>0.24551</v>
+      </c>
+      <c r="Q136" t="n">
+        <v>0.23397</v>
+      </c>
+      <c r="R136" t="n">
+        <v>0.23703</v>
+      </c>
+      <c r="S136" t="n">
+        <v>0.23701</v>
+      </c>
+      <c r="T136" t="n">
+        <v>0.23383</v>
+      </c>
+      <c r="U136" t="n">
+        <v>0.23383</v>
+      </c>
+      <c r="V136" t="n">
+        <v>0.23574</v>
+      </c>
+      <c r="W136" t="n">
+        <v>0.28041</v>
+      </c>
+      <c r="X136" t="n">
+        <v>0.23019</v>
+      </c>
+      <c r="Y136" t="n">
+        <v>0.23383</v>
+      </c>
+      <c r="Z136" t="n">
+        <v>0.23414</v>
+      </c>
+      <c r="AA136" t="n">
+        <v>0.27954</v>
+      </c>
+      <c r="AB136" t="n">
+        <v>0.23412</v>
+      </c>
+      <c r="AC136" t="n">
+        <v>0.23391</v>
+      </c>
+      <c r="AD136" t="n">
+        <v>0.32598</v>
+      </c>
+      <c r="AE136" t="n">
+        <v>0.24087</v>
+      </c>
+      <c r="AF136" t="n">
+        <v>0.16039</v>
+      </c>
+      <c r="AG136" t="n">
+        <v>0.26608</v>
+      </c>
+      <c r="AH136" t="n">
+        <v>0.20736</v>
+      </c>
+      <c r="AI136" t="n">
+        <v>0.01222</v>
+      </c>
+      <c r="AJ136" t="n">
+        <v>0.00044</v>
+      </c>
+      <c r="AK136" t="n">
+        <v>-0.00032</v>
+      </c>
+      <c r="AL136" t="n">
+        <v>-0.04957</v>
+      </c>
+      <c r="AM136" t="n">
+        <v>0.1455</v>
+      </c>
+      <c r="AN136" t="n">
+        <v>0.02115</v>
+      </c>
+      <c r="AO136" t="n">
+        <v>-0.03957</v>
+      </c>
+      <c r="AP136" t="n">
+        <v>-0.04959</v>
+      </c>
+      <c r="AQ136" t="n">
+        <v>-0.01539</v>
+      </c>
+      <c r="AR136" t="n">
+        <v>-0.04284</v>
+      </c>
+      <c r="AS136" t="n">
+        <v>-0.04073</v>
+      </c>
+      <c r="AT136" t="n">
+        <v>-0.04858</v>
+      </c>
+      <c r="AU136" t="n">
+        <v>-0.04823</v>
+      </c>
+      <c r="AV136" t="n">
+        <v>-0.02446</v>
+      </c>
+      <c r="AW136" t="n">
+        <v>-0.02922</v>
+      </c>
+      <c r="AX136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY136" t="n">
+        <v>-0.04961</v>
+      </c>
+      <c r="AZ136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BA136" t="n">
+        <v>-0.04959</v>
+      </c>
+      <c r="BB136" t="n">
+        <v>-0.0496</v>
+      </c>
+      <c r="BC136" t="n">
+        <v>-0.0494</v>
+      </c>
+      <c r="BD136" t="n">
+        <v>0.00013</v>
+      </c>
+      <c r="BE136" t="n">
+        <v>0.27413</v>
+      </c>
+      <c r="BF136" t="n">
+        <v>-0.04964</v>
+      </c>
+      <c r="BG136" t="n">
+        <v>-0.0493</v>
+      </c>
+      <c r="BH136" t="n">
+        <v>-0.0496</v>
+      </c>
+      <c r="BI136" t="n">
+        <v>-0.03838</v>
+      </c>
+      <c r="BJ136" t="n">
+        <v>-0.01913</v>
+      </c>
+      <c r="BK136" t="n">
+        <v>-0.04958</v>
+      </c>
+      <c r="BL136" t="n">
+        <v>-0.04963</v>
+      </c>
+      <c r="BM136" t="n">
+        <v>-0.03618</v>
+      </c>
+      <c r="BN136" t="n">
+        <v>0.20122</v>
+      </c>
+      <c r="BO136" t="n">
+        <v>0.26456</v>
+      </c>
+      <c r="BP136" t="n">
+        <v>0.28811</v>
+      </c>
+      <c r="BQ136" t="n">
+        <v>0.27911</v>
+      </c>
+      <c r="BR136" t="n">
+        <v>0.30367</v>
+      </c>
+      <c r="BS136" t="n">
+        <v>0.30763</v>
+      </c>
+      <c r="BT136" t="n">
+        <v>0.23815</v>
+      </c>
+      <c r="BU136" t="n">
+        <v>0.31014</v>
+      </c>
+      <c r="BV136" t="n">
+        <v>0.32778</v>
+      </c>
+      <c r="BW136" t="n">
+        <v>0.34314</v>
+      </c>
+      <c r="BX136" t="n">
+        <v>0.33608</v>
+      </c>
+      <c r="BY136" t="n">
+        <v>0.33944</v>
+      </c>
+      <c r="BZ136" t="n">
+        <v>0.3093</v>
+      </c>
+      <c r="CA136" t="n">
+        <v>0.31447</v>
+      </c>
+      <c r="CB136" t="n">
+        <v>0.34886</v>
+      </c>
+      <c r="CC136" t="n">
+        <v>0.33758</v>
+      </c>
+      <c r="CD136" t="n">
+        <v>0.34177</v>
+      </c>
+      <c r="CE136" t="n">
+        <v>0.33956</v>
+      </c>
+      <c r="CF136" t="n">
+        <v>0.33786</v>
+      </c>
+      <c r="CG136" t="n">
+        <v>0.34321</v>
+      </c>
+      <c r="CH136" t="n">
+        <v>0.33735</v>
+      </c>
+      <c r="CI136" t="n">
+        <v>0.36384</v>
+      </c>
+      <c r="CJ136" t="n">
+        <v>0.41685</v>
+      </c>
+      <c r="CK136" t="n">
+        <v>0.35211</v>
+      </c>
+      <c r="CL136" t="n">
+        <v>0.36593</v>
+      </c>
+      <c r="CM136" t="n">
+        <v>0.34752</v>
+      </c>
+      <c r="CN136" t="n">
+        <v>0.34293</v>
+      </c>
+      <c r="CO136" t="n">
+        <v>0.34239</v>
+      </c>
+      <c r="CP136" t="n">
+        <v>0.33445</v>
+      </c>
+      <c r="CQ136" t="n">
+        <v>0.34446</v>
+      </c>
+      <c r="CR136" t="n">
+        <v>0.3116</v>
+      </c>
+      <c r="CS136" t="n">
+        <v>0.32904</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="n">
+        <v>46160</v>
+      </c>
+      <c r="B137" t="n">
+        <v>0.29801</v>
+      </c>
+      <c r="C137" t="n">
+        <v>0.72157</v>
+      </c>
+      <c r="D137" t="n">
+        <v>0.61988</v>
+      </c>
+      <c r="E137" t="n">
+        <v>0.38323</v>
+      </c>
+      <c r="F137" t="n">
+        <v>0.41547</v>
+      </c>
+      <c r="G137" t="n">
+        <v>0.38986</v>
+      </c>
+      <c r="H137" t="n">
+        <v>0.41115</v>
+      </c>
+      <c r="I137" t="n">
+        <v>0.41844</v>
+      </c>
+      <c r="J137" t="n">
+        <v>0.35812</v>
+      </c>
+      <c r="K137" t="n">
+        <v>0.29386</v>
+      </c>
+      <c r="L137" t="n">
+        <v>0.33804</v>
+      </c>
+      <c r="M137" t="n">
+        <v>0.30545</v>
+      </c>
+      <c r="N137" t="n">
+        <v>0.30391</v>
+      </c>
+      <c r="O137" t="n">
+        <v>0.29932</v>
+      </c>
+      <c r="P137" t="n">
+        <v>0.25659</v>
+      </c>
+      <c r="Q137" t="n">
+        <v>0.29958</v>
+      </c>
+      <c r="R137" t="n">
+        <v>0.2833</v>
+      </c>
+      <c r="S137" t="n">
+        <v>0.25615</v>
+      </c>
+      <c r="T137" t="n">
+        <v>0.23367</v>
+      </c>
+      <c r="U137" t="n">
+        <v>0.26803</v>
+      </c>
+      <c r="V137" t="n">
+        <v>0.25842</v>
+      </c>
+      <c r="W137" t="n">
+        <v>0.28723</v>
+      </c>
+      <c r="X137" t="n">
+        <v>0.25359</v>
+      </c>
+      <c r="Y137" t="n">
+        <v>0.27906</v>
+      </c>
+      <c r="Z137" t="n">
+        <v>0.2907</v>
+      </c>
+      <c r="AA137" t="n">
+        <v>0.31335</v>
+      </c>
+      <c r="AB137" t="n">
+        <v>0.43575</v>
+      </c>
+      <c r="AC137" t="n">
+        <v>0.35405</v>
+      </c>
+      <c r="AD137" t="n">
+        <v>0.33936</v>
+      </c>
+      <c r="AE137" t="n">
+        <v>0.34538</v>
+      </c>
+      <c r="AF137" t="n">
+        <v>0.25846</v>
+      </c>
+      <c r="AG137" t="n">
+        <v>0.36354</v>
+      </c>
+      <c r="AH137" t="n">
+        <v>0.65467</v>
+      </c>
+      <c r="AI137" t="n">
+        <v>0.8213200000000001</v>
+      </c>
+      <c r="AJ137" t="n">
+        <v>0.87561</v>
+      </c>
+      <c r="AK137" t="n">
+        <v>0.84922</v>
+      </c>
+      <c r="AL137" t="n">
+        <v>0.32525</v>
+      </c>
+      <c r="AM137" t="n">
+        <v>0.38096</v>
+      </c>
+      <c r="AN137" t="n">
+        <v>0.12336</v>
+      </c>
+      <c r="AO137" t="n">
+        <v>0.21427</v>
+      </c>
+      <c r="AP137" t="n">
+        <v>0.29847</v>
+      </c>
+      <c r="AQ137" t="n">
+        <v>0.31249</v>
+      </c>
+      <c r="AR137" t="n">
+        <v>0.29644</v>
+      </c>
+      <c r="AS137" t="n">
+        <v>0.29858</v>
+      </c>
+      <c r="AT137" t="n">
+        <v>0.26621</v>
+      </c>
+      <c r="AU137" t="n">
+        <v>0.30027</v>
+      </c>
+      <c r="AV137" t="n">
+        <v>0.34444</v>
+      </c>
+      <c r="AW137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY137" t="n">
+        <v>0.25766</v>
+      </c>
+      <c r="AZ137" t="n">
+        <v>0.2714</v>
+      </c>
+      <c r="BA137" t="n">
+        <v>0.01566</v>
+      </c>
+      <c r="BB137" t="n">
+        <v>0.27356</v>
+      </c>
+      <c r="BC137" t="n">
+        <v>0.00575</v>
+      </c>
+      <c r="BD137" t="n">
+        <v>0.31171</v>
+      </c>
+      <c r="BE137" t="n">
+        <v>0.31558</v>
+      </c>
+      <c r="BF137" t="n">
+        <v>0.29109</v>
+      </c>
+      <c r="BG137" t="n">
+        <v>0.06376</v>
+      </c>
+      <c r="BH137" t="n">
+        <v>0.28583</v>
+      </c>
+      <c r="BI137" t="n">
+        <v>0.30014</v>
+      </c>
+      <c r="BJ137" t="n">
+        <v>0.28881</v>
+      </c>
+      <c r="BK137" t="n">
+        <v>0.30319</v>
+      </c>
+      <c r="BL137" t="n">
+        <v>0.25735</v>
+      </c>
+      <c r="BM137" t="n">
+        <v>0.29383</v>
+      </c>
+      <c r="BN137" t="n">
+        <v>0.4710299999999999</v>
+      </c>
+      <c r="BO137" t="n">
+        <v>0.33117</v>
+      </c>
+      <c r="BP137" t="n">
+        <v>0.32478</v>
+      </c>
+      <c r="BQ137" t="n">
+        <v>0.35517</v>
+      </c>
+      <c r="BR137" t="n">
+        <v>0.38465</v>
+      </c>
+      <c r="BS137" t="n">
+        <v>0.39642</v>
+      </c>
+      <c r="BT137" t="n">
+        <v>0.35389</v>
+      </c>
+      <c r="BU137" t="n">
+        <v>0.37805</v>
+      </c>
+      <c r="BV137" t="n">
+        <v>0.36826</v>
+      </c>
+      <c r="BW137" t="n">
+        <v>0.39804</v>
+      </c>
+      <c r="BX137" t="n">
+        <v>1.48919</v>
+      </c>
+      <c r="BY137" t="n">
+        <v>0.79162</v>
+      </c>
+      <c r="BZ137" t="n">
+        <v>0.75225</v>
+      </c>
+      <c r="CA137" t="n">
+        <v>0.7750199999999999</v>
+      </c>
+      <c r="CB137" t="n">
+        <v>1.34031</v>
+      </c>
+      <c r="CC137" t="n">
+        <v>0.99595</v>
+      </c>
+      <c r="CD137" t="n">
+        <v>0.75782</v>
+      </c>
+      <c r="CE137" t="n">
+        <v>0.83611</v>
+      </c>
+      <c r="CF137" t="n">
+        <v>0.78216</v>
+      </c>
+      <c r="CG137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CH137" t="n">
+        <v>0.8397</v>
+      </c>
+      <c r="CI137" t="n">
+        <v>0.83789</v>
+      </c>
+      <c r="CJ137" t="n">
+        <v>0.84221</v>
+      </c>
+      <c r="CK137" t="n">
+        <v>0.93943</v>
+      </c>
+      <c r="CL137" t="n">
+        <v>0.74124</v>
+      </c>
+      <c r="CM137" t="n">
+        <v>0.77811</v>
+      </c>
+      <c r="CN137" t="n">
+        <v>0.74453</v>
+      </c>
+      <c r="CO137" t="n">
+        <v>0.3801</v>
+      </c>
+      <c r="CP137" t="n">
+        <v>0.35461</v>
+      </c>
+      <c r="CQ137" t="n">
+        <v>0.37157</v>
+      </c>
+      <c r="CR137" t="n">
+        <v>0.3622</v>
+      </c>
+      <c r="CS137" t="n">
+        <v>0.36204</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="n">
+        <v>46161</v>
+      </c>
+      <c r="B138" t="n">
+        <v>0.33007</v>
+      </c>
+      <c r="C138" t="n">
+        <v>0.46252</v>
+      </c>
+      <c r="D138" t="n">
+        <v>0.6020700000000001</v>
+      </c>
+      <c r="E138" t="n">
+        <v>0.63251</v>
+      </c>
+      <c r="F138" t="n">
+        <v>0.5642999999999999</v>
+      </c>
+      <c r="G138" t="n">
+        <v>0.49288</v>
+      </c>
+      <c r="H138" t="n">
+        <v>0.45708</v>
+      </c>
+      <c r="I138" t="n">
+        <v>0.39918</v>
+      </c>
+      <c r="J138" t="n">
+        <v>0.38877</v>
+      </c>
+      <c r="K138" t="n">
+        <v>0.38016</v>
+      </c>
+      <c r="L138" t="n">
+        <v>0.36985</v>
+      </c>
+      <c r="M138" t="n">
+        <v>0.35215</v>
+      </c>
+      <c r="N138" t="n">
+        <v>0.33074</v>
+      </c>
+      <c r="O138" t="n">
+        <v>0.33496</v>
+      </c>
+      <c r="P138" t="n">
+        <v>0.32439</v>
+      </c>
+      <c r="Q138" t="n">
+        <v>0.31669</v>
+      </c>
+      <c r="R138" t="n">
+        <v>0.47126</v>
+      </c>
+      <c r="S138" t="n">
+        <v>0.31835</v>
+      </c>
+      <c r="T138" t="n">
+        <v>0.31233</v>
+      </c>
+      <c r="U138" t="n">
+        <v>0.31241</v>
+      </c>
+      <c r="V138" t="n">
+        <v>0.30319</v>
+      </c>
+      <c r="W138" t="n">
+        <v>0.30765</v>
+      </c>
+      <c r="X138" t="n">
+        <v>0.27421</v>
+      </c>
+      <c r="Y138" t="n">
+        <v>0.33892</v>
+      </c>
+      <c r="Z138" t="n">
+        <v>0.33676</v>
+      </c>
+      <c r="AA138" t="n">
+        <v>0.3627</v>
+      </c>
+      <c r="AB138" t="n">
+        <v>0.45777</v>
+      </c>
+      <c r="AC138" t="n">
+        <v>0.46795</v>
+      </c>
+      <c r="AD138" t="n">
+        <v>0.36368</v>
+      </c>
+      <c r="AE138" t="n">
+        <v>0.38065</v>
+      </c>
+      <c r="AF138" t="n">
+        <v>0.32133</v>
+      </c>
+      <c r="AG138" t="n">
+        <v>0.32165</v>
+      </c>
+      <c r="AH138" t="n">
+        <v>0.33067</v>
+      </c>
+      <c r="AI138" t="n">
+        <v>0.42047</v>
+      </c>
+      <c r="AJ138" t="n">
+        <v>0.37463</v>
+      </c>
+      <c r="AK138" t="n">
+        <v>0.44716</v>
+      </c>
+      <c r="AL138" t="n">
+        <v>0.37838</v>
+      </c>
+      <c r="AM138" t="n">
+        <v>0.42029</v>
+      </c>
+      <c r="AN138" t="n">
+        <v>0.39859</v>
+      </c>
+      <c r="AO138" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="AP138" t="n">
+        <v>0.35906</v>
+      </c>
+      <c r="AQ138" t="n">
+        <v>0.34595</v>
+      </c>
+      <c r="AR138" t="n">
+        <v>0.39854</v>
+      </c>
+      <c r="AS138" t="n">
+        <v>0.35349</v>
+      </c>
+      <c r="AT138" t="n">
+        <v>0.32533</v>
+      </c>
+      <c r="AU138" t="n">
+        <v>0.32539</v>
+      </c>
+      <c r="AV138" t="n">
+        <v>0.34278</v>
+      </c>
+      <c r="AW138" t="n">
+        <v>0.32296</v>
+      </c>
+      <c r="AX138" t="n">
+        <v>0.27575</v>
+      </c>
+      <c r="AY138" t="n">
+        <v>0.32565</v>
+      </c>
+      <c r="AZ138" t="n">
+        <v>0.31676</v>
+      </c>
+      <c r="BA138" t="n">
+        <v>0.31828</v>
+      </c>
+      <c r="BB138" t="n">
+        <v>0.32754</v>
+      </c>
+      <c r="BC138" t="n">
+        <v>0.338</v>
+      </c>
+      <c r="BD138" t="n">
+        <v>0.33558</v>
+      </c>
+      <c r="BE138" t="n">
+        <v>0.36673</v>
+      </c>
+      <c r="BF138" t="n">
+        <v>0.33208</v>
+      </c>
+      <c r="BG138" t="n">
+        <v>0.32843</v>
+      </c>
+      <c r="BH138" t="n">
+        <v>0.31596</v>
+      </c>
+      <c r="BI138" t="n">
+        <v>0.31709</v>
+      </c>
+      <c r="BJ138" t="n">
+        <v>0.32244</v>
+      </c>
+      <c r="BK138" t="n">
+        <v>0.33465</v>
+      </c>
+      <c r="BL138" t="n">
+        <v>0.33815</v>
+      </c>
+      <c r="BM138" t="n">
+        <v>0.33611</v>
+      </c>
+      <c r="BN138" t="n">
+        <v>0.34211</v>
+      </c>
+      <c r="BO138" t="n">
+        <v>0.33751</v>
+      </c>
+      <c r="BP138" t="n">
+        <v>0.35305</v>
+      </c>
+      <c r="BQ138" t="n">
+        <v>0.36744</v>
+      </c>
+      <c r="BR138" t="n">
+        <v>0.37316</v>
+      </c>
+      <c r="BS138" t="n">
+        <v>0.38334</v>
+      </c>
+      <c r="BT138" t="n">
+        <v>0.3737799999999999</v>
+      </c>
+      <c r="BU138" t="n">
+        <v>0.37355</v>
+      </c>
+      <c r="BV138" t="n">
+        <v>0.3414700000000001</v>
+      </c>
+      <c r="BW138" t="n">
+        <v>0.36775</v>
+      </c>
+      <c r="BX138" t="n">
+        <v>0.4075299999999999</v>
+      </c>
+      <c r="BY138" t="n">
+        <v>0.39498</v>
+      </c>
+      <c r="BZ138" t="n">
+        <v>0.38059</v>
+      </c>
+      <c r="CA138" t="n">
+        <v>0.35475</v>
+      </c>
+      <c r="CB138" t="n">
+        <v>0.38032</v>
+      </c>
+      <c r="CC138" t="n">
+        <v>0.39865</v>
+      </c>
+      <c r="CD138" t="n">
+        <v>0.45637</v>
+      </c>
+      <c r="CE138" t="n">
+        <v>0.46363</v>
+      </c>
+      <c r="CF138" t="n">
+        <v>0.73075</v>
+      </c>
+      <c r="CG138" t="n">
+        <v>0.43038</v>
+      </c>
+      <c r="CH138" t="n">
+        <v>0.60277</v>
+      </c>
+      <c r="CI138" t="n">
+        <v>0.4695299999999999</v>
+      </c>
+      <c r="CJ138" t="n">
+        <v>0.405</v>
+      </c>
+      <c r="CK138" t="n">
+        <v>0.42346</v>
+      </c>
+      <c r="CL138" t="n">
+        <v>0.40715</v>
+      </c>
+      <c r="CM138" t="n">
+        <v>0.38736</v>
+      </c>
+      <c r="CN138" t="n">
+        <v>0.4670899999999999</v>
+      </c>
+      <c r="CO138" t="n">
+        <v>0.35187</v>
+      </c>
+      <c r="CP138" t="n">
+        <v>0.35538</v>
+      </c>
+      <c r="CQ138" t="n">
+        <v>0.33833</v>
+      </c>
+      <c r="CR138" t="n">
+        <v>0.33986</v>
+      </c>
+      <c r="CS138" t="n">
+        <v>0.33651</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="n">
+        <v>46162</v>
+      </c>
+      <c r="B139" t="n">
+        <v>0.3271</v>
+      </c>
+      <c r="C139" t="n">
+        <v>0.41858</v>
+      </c>
+      <c r="D139" t="n">
+        <v>0.42149</v>
+      </c>
+      <c r="E139" t="n">
+        <v>0.40629</v>
+      </c>
+      <c r="F139" t="n">
+        <v>0.38927</v>
+      </c>
+      <c r="G139" t="n">
+        <v>0.38214</v>
+      </c>
+      <c r="H139" t="n">
+        <v>0.37809</v>
+      </c>
+      <c r="I139" t="n">
+        <v>0.37543</v>
+      </c>
+      <c r="J139" t="n">
+        <v>0.3561</v>
+      </c>
+      <c r="K139" t="n">
+        <v>0.35862</v>
+      </c>
+      <c r="L139" t="n">
+        <v>0.3512</v>
+      </c>
+      <c r="M139" t="n">
+        <v>0.35086</v>
+      </c>
+      <c r="N139" t="n">
+        <v>0.34538</v>
+      </c>
+      <c r="O139" t="n">
+        <v>0.3474</v>
+      </c>
+      <c r="P139" t="n">
+        <v>0.34522</v>
+      </c>
+      <c r="Q139" t="n">
+        <v>0.34093</v>
+      </c>
+      <c r="R139" t="n">
+        <v>0.35138</v>
+      </c>
+      <c r="S139" t="n">
+        <v>0.33551</v>
+      </c>
+      <c r="T139" t="n">
+        <v>0.33476</v>
+      </c>
+      <c r="U139" t="n">
+        <v>0.32881</v>
+      </c>
+      <c r="V139" t="n">
+        <v>0.33068</v>
+      </c>
+      <c r="W139" t="n">
+        <v>0.33217</v>
+      </c>
+      <c r="X139" t="n">
+        <v>0.33225</v>
+      </c>
+      <c r="Y139" t="n">
+        <v>0.34233</v>
+      </c>
+      <c r="Z139" t="n">
+        <v>0.33468</v>
+      </c>
+      <c r="AA139" t="n">
+        <v>0.35029</v>
+      </c>
+      <c r="AB139" t="n">
+        <v>0.34326</v>
+      </c>
+      <c r="AC139" t="n">
+        <v>0.351</v>
+      </c>
+      <c r="AD139" t="n">
+        <v>0.34422</v>
+      </c>
+      <c r="AE139" t="n">
+        <v>0.35376</v>
+      </c>
+      <c r="AF139" t="n">
+        <v>0.40316</v>
+      </c>
+      <c r="AG139" t="n">
+        <v>0.36469</v>
+      </c>
+      <c r="AH139" t="n">
+        <v>0.35525</v>
+      </c>
+      <c r="AI139" t="n">
+        <v>0.5459700000000001</v>
+      </c>
+      <c r="AJ139" t="n">
+        <v>0.75759</v>
+      </c>
+      <c r="AK139" t="n">
+        <v>0.53943</v>
+      </c>
+      <c r="AL139" t="n">
+        <v>0.53113</v>
+      </c>
+      <c r="AM139" t="n">
+        <v>0.56196</v>
+      </c>
+      <c r="AN139" t="n">
+        <v>0.4497</v>
+      </c>
+      <c r="AO139" t="n">
+        <v>0.38781</v>
+      </c>
+      <c r="AP139" t="n">
+        <v>0.37575</v>
+      </c>
+      <c r="AQ139" t="n">
+        <v>0.36467</v>
+      </c>
+      <c r="AR139" t="n">
+        <v>0.35467</v>
+      </c>
+      <c r="AS139" t="n">
+        <v>0.3629</v>
+      </c>
+      <c r="AT139" t="n">
+        <v>0.42117</v>
+      </c>
+      <c r="AU139" t="n">
+        <v>0.36063</v>
+      </c>
+      <c r="AV139" t="n">
+        <v>0.39371</v>
+      </c>
+      <c r="AW139" t="n">
+        <v>0.35732</v>
+      </c>
+      <c r="AX139" t="n">
+        <v>0.31175</v>
+      </c>
+      <c r="AY139" t="n">
+        <v>0.48939</v>
+      </c>
+      <c r="AZ139" t="n">
+        <v>0.46327</v>
+      </c>
+      <c r="BA139" t="n">
+        <v>0.48208</v>
+      </c>
+      <c r="BB139" t="n">
+        <v>0.49444</v>
+      </c>
+      <c r="BC139" t="n">
+        <v>0.41973</v>
+      </c>
+      <c r="BD139" t="n">
+        <v>0.3493</v>
+      </c>
+      <c r="BE139" t="n">
+        <v>0.47259</v>
+      </c>
+      <c r="BF139" t="n">
+        <v>0.33434</v>
+      </c>
+      <c r="BG139" t="n">
+        <v>0.33202</v>
+      </c>
+      <c r="BH139" t="n">
+        <v>0.46582</v>
+      </c>
+      <c r="BI139" t="n">
+        <v>0.35162</v>
+      </c>
+      <c r="BJ139" t="n">
+        <v>0.3375</v>
+      </c>
+      <c r="BK139" t="n">
+        <v>0.342</v>
+      </c>
+      <c r="BL139" t="n">
+        <v>0.33135</v>
+      </c>
+      <c r="BM139" t="n">
+        <v>0.3531</v>
+      </c>
+      <c r="BN139" t="n">
+        <v>0.35288</v>
+      </c>
+      <c r="BO139" t="n">
+        <v>1.1576</v>
+      </c>
+      <c r="BP139" t="n">
+        <v>0.6798500000000001</v>
+      </c>
+      <c r="BQ139" t="n">
+        <v>0.49207</v>
+      </c>
+      <c r="BR139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BS139" t="n">
+        <v>1.09602</v>
+      </c>
+      <c r="BT139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BU139" t="n">
+        <v>0.94476</v>
+      </c>
+      <c r="BV139" t="n">
+        <v>1.3043</v>
+      </c>
+      <c r="BW139" t="n">
+        <v>0.82598</v>
+      </c>
+      <c r="BX139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BY139" t="n">
+        <v>1.19392</v>
+      </c>
+      <c r="BZ139" t="n">
+        <v>1.13722</v>
+      </c>
+      <c r="CA139" t="n">
+        <v>0.72097</v>
+      </c>
+      <c r="CB139" t="n">
+        <v>0.56601</v>
+      </c>
+      <c r="CC139" t="n">
+        <v>0.45356</v>
+      </c>
+      <c r="CD139" t="n">
+        <v>0.45178</v>
+      </c>
+      <c r="CE139" t="n">
+        <v>0.69113</v>
+      </c>
+      <c r="CF139" t="n">
+        <v>0.83793</v>
+      </c>
+      <c r="CG139" t="n">
+        <v>0.9953</v>
+      </c>
+      <c r="CH139" t="n">
+        <v>0.5094</v>
+      </c>
+      <c r="CI139" t="n">
+        <v>0.4502</v>
+      </c>
+      <c r="CJ139" t="n">
+        <v>0.35205</v>
+      </c>
+      <c r="CK139" t="n">
+        <v>0.41813</v>
+      </c>
+      <c r="CL139" t="n">
+        <v>0.37737</v>
+      </c>
+      <c r="CM139" t="n">
+        <v>0.3554</v>
+      </c>
+      <c r="CN139" t="n">
+        <v>0.37917</v>
+      </c>
+      <c r="CO139" t="n">
+        <v>0.36261</v>
+      </c>
+      <c r="CP139" t="n">
+        <v>0.23405</v>
+      </c>
+      <c r="CQ139" t="n">
+        <v>0.35505</v>
+      </c>
+      <c r="CR139" t="n">
+        <v>0.34311</v>
+      </c>
+      <c r="CS139" t="n">
+        <v>0.35136</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="n">
+        <v>46163</v>
+      </c>
+      <c r="B140" t="n">
+        <v>0.33735</v>
+      </c>
+      <c r="C140" t="n">
+        <v>0.45237</v>
+      </c>
+      <c r="D140" t="n">
+        <v>0.38038</v>
+      </c>
+      <c r="E140" t="n">
+        <v>0.37631</v>
+      </c>
+      <c r="F140" t="n">
+        <v>0.36875</v>
+      </c>
+      <c r="G140" t="n">
+        <v>0.36419</v>
+      </c>
+      <c r="H140" t="n">
+        <v>0.3458</v>
+      </c>
+      <c r="I140" t="n">
+        <v>0.35549</v>
+      </c>
+      <c r="J140" t="n">
+        <v>0.36483</v>
+      </c>
+      <c r="K140" t="n">
+        <v>0.35988</v>
+      </c>
+      <c r="L140" t="n">
+        <v>0.35832</v>
+      </c>
+      <c r="M140" t="n">
+        <v>0.35698</v>
+      </c>
+      <c r="N140" t="n">
+        <v>0.35041</v>
+      </c>
+      <c r="O140" t="n">
+        <v>0.3469</v>
+      </c>
+      <c r="P140" t="n">
+        <v>0.34463</v>
+      </c>
+      <c r="Q140" t="n">
+        <v>0.34595</v>
+      </c>
+      <c r="R140" t="n">
+        <v>0.34557</v>
+      </c>
+      <c r="S140" t="n">
+        <v>0.33881</v>
+      </c>
+      <c r="T140" t="n">
+        <v>0.31875</v>
+      </c>
+      <c r="U140" t="n">
+        <v>0.33902</v>
+      </c>
+      <c r="V140" t="n">
+        <v>0.33346</v>
+      </c>
+      <c r="W140" t="n">
+        <v>0.33138</v>
+      </c>
+      <c r="X140" t="n">
+        <v>0.32956</v>
+      </c>
+      <c r="Y140" t="n">
+        <v>0.34004</v>
+      </c>
+      <c r="Z140" t="n">
+        <v>0.3384</v>
+      </c>
+      <c r="AA140" t="n">
+        <v>0.34843</v>
+      </c>
+      <c r="AB140" t="n">
+        <v>0.3695</v>
+      </c>
+      <c r="AC140" t="n">
+        <v>0.35117</v>
+      </c>
+      <c r="AD140" t="n">
+        <v>0.35581</v>
+      </c>
+      <c r="AE140" t="n">
+        <v>0.34392</v>
+      </c>
+      <c r="AF140" t="n">
+        <v>0.35042</v>
+      </c>
+      <c r="AG140" t="n">
+        <v>0.34897</v>
+      </c>
+      <c r="AH140" t="n">
+        <v>0.34785</v>
+      </c>
+      <c r="AI140" t="n">
+        <v>0.38025</v>
+      </c>
+      <c r="AJ140" t="n">
+        <v>0.39131</v>
+      </c>
+      <c r="AK140" t="n">
+        <v>0.36479</v>
+      </c>
+      <c r="AL140" t="n">
+        <v>0.35396</v>
+      </c>
+      <c r="AM140" t="n">
+        <v>0.43504</v>
+      </c>
+      <c r="AN140" t="n">
+        <v>0.38002</v>
+      </c>
+      <c r="AO140" t="n">
+        <v>0.36178</v>
+      </c>
+      <c r="AP140" t="n">
+        <v>0.37445</v>
+      </c>
+      <c r="AQ140" t="n">
+        <v>0.35472</v>
+      </c>
+      <c r="AR140" t="n">
+        <v>0.31056</v>
+      </c>
+      <c r="AS140" t="n">
+        <v>0.36363</v>
+      </c>
+      <c r="AT140" t="n">
+        <v>1.12448</v>
+      </c>
+      <c r="AU140" t="n">
+        <v>0.41374</v>
+      </c>
+      <c r="AV140" t="n">
+        <v>0.62587</v>
+      </c>
+      <c r="AW140" t="n">
+        <v>0.43018</v>
+      </c>
+      <c r="AX140" t="n">
+        <v>0.29259</v>
+      </c>
+      <c r="AY140" t="n">
+        <v>0.6685399999999999</v>
+      </c>
+      <c r="AZ140" t="n">
+        <v>0.47646</v>
+      </c>
+      <c r="BA140" t="n">
+        <v>0.40311</v>
+      </c>
+      <c r="BB140" t="n">
+        <v>0.5476</v>
+      </c>
+      <c r="BC140" t="n">
+        <v>0.31619</v>
+      </c>
+      <c r="BD140" t="n">
+        <v>0.33659</v>
+      </c>
+      <c r="BE140" t="n">
+        <v>0.34369</v>
+      </c>
+      <c r="BF140" t="n">
+        <v>0.32531</v>
+      </c>
+      <c r="BG140" t="n">
+        <v>0.33354</v>
+      </c>
+      <c r="BH140" t="n">
+        <v>0.34178</v>
+      </c>
+      <c r="BI140" t="n">
+        <v>0.33826</v>
+      </c>
+      <c r="BJ140" t="n">
+        <v>0.32488</v>
+      </c>
+      <c r="BK140" t="n">
+        <v>0.34423</v>
+      </c>
+      <c r="BL140" t="n">
+        <v>0.34324</v>
+      </c>
+      <c r="BM140" t="n">
+        <v>0.36808</v>
+      </c>
+      <c r="BN140" t="n">
+        <v>0.36491</v>
+      </c>
+      <c r="BO140" t="n">
+        <v>0.37129</v>
+      </c>
+      <c r="BP140" t="n">
+        <v>0.47876</v>
+      </c>
+      <c r="BQ140" t="n">
+        <v>0.37521</v>
+      </c>
+      <c r="BR140" t="n">
+        <v>0.39417</v>
+      </c>
+      <c r="BS140" t="n">
+        <v>0.3732</v>
+      </c>
+      <c r="BT140" t="n">
+        <v>0.3741</v>
+      </c>
+      <c r="BU140" t="n">
+        <v>0.41767</v>
+      </c>
+      <c r="BV140" t="n">
+        <v>0.41193</v>
+      </c>
+      <c r="BW140" t="n">
+        <v>0.5137699999999999</v>
+      </c>
+      <c r="BX140" t="n">
+        <v>0.88989</v>
+      </c>
+      <c r="BY140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BZ140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CA140" t="n">
+        <v>0.70539</v>
+      </c>
+      <c r="CB140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CC140" t="n">
+        <v>0.7583799999999999</v>
+      </c>
+      <c r="CD140" t="n">
+        <v>1.22879</v>
+      </c>
+      <c r="CE140" t="n">
+        <v>0.62675</v>
+      </c>
+      <c r="CF140" t="n">
+        <v>0.47498</v>
+      </c>
+      <c r="CG140" t="n">
+        <v>1.37266</v>
+      </c>
+      <c r="CH140" t="n">
+        <v>1.01633</v>
+      </c>
+      <c r="CI140" t="n">
+        <v>1.2358</v>
+      </c>
+      <c r="CJ140" t="n">
+        <v>1.12842</v>
+      </c>
+      <c r="CK140" t="n">
+        <v>1.53504</v>
+      </c>
+      <c r="CL140" t="n">
+        <v>1.7996</v>
+      </c>
+      <c r="CM140" t="n">
+        <v>0.75185</v>
+      </c>
+      <c r="CN140" t="n">
+        <v>0.7297400000000001</v>
+      </c>
+      <c r="CO140" t="n">
+        <v>0.43736</v>
+      </c>
+      <c r="CP140" t="n">
+        <v>0.35844</v>
+      </c>
+      <c r="CQ140" t="n">
+        <v>0.36213</v>
+      </c>
+      <c r="CR140" t="n">
+        <v>0.35161</v>
+      </c>
+      <c r="CS140" t="n">
+        <v>0.35575</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="n">
+        <v>46164</v>
+      </c>
+      <c r="B141" t="n">
+        <v>0.30067</v>
+      </c>
+      <c r="C141" t="n">
+        <v>0.35685</v>
+      </c>
+      <c r="D141" t="n">
+        <v>0.35866</v>
+      </c>
+      <c r="E141" t="n">
+        <v>0.3475</v>
+      </c>
+      <c r="F141" t="n">
+        <v>0.34885</v>
+      </c>
+      <c r="G141" t="n">
+        <v>0.33938</v>
+      </c>
+      <c r="H141" t="n">
+        <v>0.32611</v>
+      </c>
+      <c r="I141" t="n">
+        <v>0.33736</v>
+      </c>
+      <c r="J141" t="n">
+        <v>0.33093</v>
+      </c>
+      <c r="K141" t="n">
+        <v>0.33202</v>
+      </c>
+      <c r="L141" t="n">
+        <v>0.34249</v>
+      </c>
+      <c r="M141" t="n">
+        <v>0.3223</v>
+      </c>
+      <c r="N141" t="n">
+        <v>0.3655</v>
+      </c>
+      <c r="O141" t="n">
+        <v>0.34226</v>
+      </c>
+      <c r="P141" t="n">
+        <v>1.33184</v>
+      </c>
+      <c r="Q141" t="n">
+        <v>0.33885</v>
+      </c>
+      <c r="R141" t="n">
+        <v>0.33574</v>
+      </c>
+      <c r="S141" t="n">
+        <v>0.22335</v>
+      </c>
+      <c r="T141" t="n">
+        <v>0.32441</v>
+      </c>
+      <c r="U141" t="n">
+        <v>0.32688</v>
+      </c>
+      <c r="V141" t="n">
+        <v>0.3375</v>
+      </c>
+      <c r="W141" t="n">
+        <v>0.32669</v>
+      </c>
+      <c r="X141" t="n">
+        <v>0.33269</v>
+      </c>
+      <c r="Y141" t="n">
+        <v>0.34551</v>
+      </c>
+      <c r="Z141" t="n">
+        <v>0.34305</v>
+      </c>
+      <c r="AA141" t="n">
+        <v>1.33688</v>
+      </c>
+      <c r="AB141" t="n">
+        <v>0.37492</v>
+      </c>
+      <c r="AC141" t="n">
+        <v>0.37477</v>
+      </c>
+      <c r="AD141" t="n">
+        <v>0.35239</v>
+      </c>
+      <c r="AE141" t="n">
+        <v>0.33943</v>
+      </c>
+      <c r="AF141" t="n">
+        <v>0.33698</v>
+      </c>
+      <c r="AG141" t="n">
+        <v>0.33782</v>
+      </c>
+      <c r="AH141" t="n">
+        <v>0.36179</v>
+      </c>
+      <c r="AI141" t="n">
+        <v>0.33468</v>
+      </c>
+      <c r="AJ141" t="n">
+        <v>0.3482</v>
+      </c>
+      <c r="AK141" t="n">
+        <v>0.35139</v>
+      </c>
+      <c r="AL141" t="n">
+        <v>0.33556</v>
+      </c>
+      <c r="AM141" t="n">
+        <v>0.3451</v>
+      </c>
+      <c r="AN141" t="n">
+        <v>0.46088</v>
+      </c>
+      <c r="AO141" t="n">
+        <v>1.67791</v>
+      </c>
+      <c r="AP141" t="n">
+        <v>1.15106</v>
+      </c>
+      <c r="AQ141" t="n">
+        <v>0.5695800000000001</v>
+      </c>
+      <c r="AR141" t="n">
+        <v>0.96247</v>
+      </c>
+      <c r="AS141" t="n">
+        <v>1.16763</v>
+      </c>
+      <c r="AT141" t="n">
+        <v>0.60537</v>
+      </c>
+      <c r="AU141" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AV141" t="n">
+        <v>1.6885</v>
+      </c>
+      <c r="AW141" t="n">
+        <v>1.26067</v>
+      </c>
+      <c r="AX141" t="n">
+        <v>0.4364</v>
+      </c>
+      <c r="AY141" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AZ141" t="n">
+        <v>0.57384</v>
+      </c>
+      <c r="BA141" t="n">
+        <v>0.54335</v>
+      </c>
+      <c r="BB141" t="n">
+        <v>1.3253</v>
+      </c>
+      <c r="BC141" t="n">
+        <v>0.66364</v>
+      </c>
+      <c r="BD141" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BE141" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BF141" t="n">
+        <v>1.16455</v>
+      </c>
+      <c r="BG141" t="n">
+        <v>1.77558</v>
+      </c>
+      <c r="BH141" t="n">
+        <v>0.5696599999999999</v>
+      </c>
+      <c r="BI141" t="n">
+        <v>1.15244</v>
+      </c>
+      <c r="BJ141" t="n">
+        <v>1.36659</v>
+      </c>
+      <c r="BK141" t="n">
+        <v>1.16684</v>
+      </c>
+      <c r="BL141" t="n">
+        <v>0.5902500000000001</v>
+      </c>
+      <c r="BM141" t="n">
+        <v>0.34812</v>
+      </c>
+      <c r="BN141" t="n">
+        <v>0.34076</v>
+      </c>
+      <c r="BO141" t="n">
+        <v>0.465</v>
+      </c>
+      <c r="BP141" t="n">
+        <v>0.42836</v>
+      </c>
+      <c r="BQ141" t="n">
+        <v>0.36134</v>
+      </c>
+      <c r="BR141" t="n">
+        <v>0.47381</v>
+      </c>
+      <c r="BS141" t="n">
+        <v>1.13231</v>
+      </c>
+      <c r="BT141" t="n">
+        <v>0.9695199999999999</v>
+      </c>
+      <c r="BU141" t="n">
+        <v>0.44493</v>
+      </c>
+      <c r="BV141" t="n">
+        <v>0.36569</v>
+      </c>
+      <c r="BW141" t="n">
+        <v>0.37101</v>
+      </c>
+      <c r="BX141" t="n">
+        <v>0.63613</v>
+      </c>
+      <c r="BY141" t="n">
+        <v>1.25749</v>
+      </c>
+      <c r="BZ141" t="n">
+        <v>0.55536</v>
+      </c>
+      <c r="CA141" t="n">
+        <v>0.6539700000000001</v>
+      </c>
+      <c r="CB141" t="n">
+        <v>1.67204</v>
+      </c>
+      <c r="CC141" t="n">
+        <v>0.68077</v>
+      </c>
+      <c r="CD141" t="n">
+        <v>1.13354</v>
+      </c>
+      <c r="CE141" t="n">
+        <v>0.46435</v>
+      </c>
+      <c r="CF141" t="n">
+        <v>0.71354</v>
+      </c>
+      <c r="CG141" t="n">
+        <v>1.74575</v>
+      </c>
+      <c r="CH141" t="n">
+        <v>0.66203</v>
+      </c>
+      <c r="CI141" t="n">
+        <v>0.70138</v>
+      </c>
+      <c r="CJ141" t="n">
+        <v>0.6653</v>
+      </c>
+      <c r="CK141" t="n">
+        <v>1.05103</v>
+      </c>
+      <c r="CL141" t="n">
+        <v>0.39815</v>
+      </c>
+      <c r="CM141" t="n">
+        <v>0.45071</v>
+      </c>
+      <c r="CN141" t="n">
+        <v>0.40475</v>
+      </c>
+      <c r="CO141" t="n">
+        <v>0.36883</v>
+      </c>
+      <c r="CP141" t="n">
+        <v>0.3959</v>
+      </c>
+      <c r="CQ141" t="n">
+        <v>0.52565</v>
+      </c>
+      <c r="CR141" t="n">
+        <v>0.35195</v>
+      </c>
+      <c r="CS141" t="n">
+        <v>0.36227</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="n">
+        <v>46165</v>
+      </c>
+      <c r="B142" t="n">
+        <v>0.34263</v>
+      </c>
+      <c r="C142" t="n">
+        <v>1.22917</v>
+      </c>
+      <c r="D142" t="n">
+        <v>0.9368</v>
+      </c>
+      <c r="E142" t="n">
+        <v>0.56231</v>
+      </c>
+      <c r="F142" t="n">
+        <v>0.6229</v>
+      </c>
+      <c r="G142" t="n">
+        <v>0.95699</v>
+      </c>
+      <c r="H142" t="n">
+        <v>0.36534</v>
+      </c>
+      <c r="I142" t="n">
+        <v>0.44165</v>
+      </c>
+      <c r="J142" t="n">
+        <v>0.37128</v>
+      </c>
+      <c r="K142" t="n">
+        <v>0.3822</v>
+      </c>
+      <c r="L142" t="n">
+        <v>0.3698</v>
+      </c>
+      <c r="M142" t="n">
+        <v>0.36788</v>
+      </c>
+      <c r="N142" t="n">
+        <v>0.37107</v>
+      </c>
+      <c r="O142" t="n">
+        <v>0.3674</v>
+      </c>
+      <c r="P142" t="n">
+        <v>0.36352</v>
+      </c>
+      <c r="Q142" t="n">
+        <v>0.36771</v>
+      </c>
+      <c r="R142" t="n">
+        <v>0.36725</v>
+      </c>
+      <c r="S142" t="n">
+        <v>0.36617</v>
+      </c>
+      <c r="T142" t="n">
+        <v>1.36682</v>
+      </c>
+      <c r="U142" t="n">
+        <v>0.36239</v>
+      </c>
+      <c r="V142" t="n">
+        <v>0.35689</v>
+      </c>
+      <c r="W142" t="n">
+        <v>0.35881</v>
+      </c>
+      <c r="X142" t="n">
+        <v>0.36133</v>
+      </c>
+      <c r="Y142" t="n">
+        <v>0.35924</v>
+      </c>
+      <c r="Z142" t="n">
+        <v>0.35812</v>
+      </c>
+      <c r="AA142" t="n">
+        <v>0.34876</v>
+      </c>
+      <c r="AB142" t="n">
+        <v>0.35741</v>
+      </c>
+      <c r="AC142" t="n">
+        <v>0.35236</v>
+      </c>
+      <c r="AD142" t="n">
+        <v>0.37046</v>
+      </c>
+      <c r="AE142" t="n">
+        <v>0.35715</v>
+      </c>
+      <c r="AF142" t="n">
+        <v>0.34469</v>
+      </c>
+      <c r="AG142" t="n">
+        <v>0.34692</v>
+      </c>
+      <c r="AH142" t="n">
+        <v>0.35178</v>
+      </c>
+      <c r="AI142" t="n">
+        <v>0.3591</v>
+      </c>
+      <c r="AJ142" t="n">
+        <v>0.36102</v>
+      </c>
+      <c r="AK142" t="n">
+        <v>0.35555</v>
+      </c>
+      <c r="AL142" t="n">
+        <v>0.34201</v>
+      </c>
+      <c r="AM142" t="n">
+        <v>0.37506</v>
+      </c>
+      <c r="AN142" t="n">
+        <v>0.36445</v>
+      </c>
+      <c r="AO142" t="n">
+        <v>0.35718</v>
+      </c>
+      <c r="AP142" t="n">
+        <v>0.64137</v>
+      </c>
+      <c r="AQ142" t="n">
+        <v>0.7955599999999999</v>
+      </c>
+      <c r="AR142" t="n">
+        <v>0.65613</v>
+      </c>
+      <c r="AS142" t="n">
+        <v>0.72605</v>
+      </c>
+      <c r="AT142" t="n">
+        <v>0.87512</v>
+      </c>
+      <c r="AU142" t="n">
+        <v>1.77412</v>
+      </c>
+      <c r="AV142" t="n">
+        <v>1.325</v>
+      </c>
+      <c r="AW142" t="n">
+        <v>0.34833</v>
+      </c>
+      <c r="AX142" t="n">
+        <v>0.5660499999999999</v>
+      </c>
+      <c r="AY142" t="n">
+        <v>0.67431</v>
+      </c>
+      <c r="AZ142" t="n">
+        <v>0.34501</v>
+      </c>
+      <c r="BA142" t="n">
+        <v>0.34158</v>
+      </c>
+      <c r="BB142" t="n">
+        <v>0.47253</v>
+      </c>
+      <c r="BC142" t="n">
+        <v>0.35271</v>
+      </c>
+      <c r="BD142" t="n">
+        <v>0.99762</v>
+      </c>
+      <c r="BE142" t="n">
+        <v>0.72049</v>
+      </c>
+      <c r="BF142" t="n">
+        <v>0.34715</v>
+      </c>
+      <c r="BG142" t="n">
+        <v>0.32255</v>
+      </c>
+      <c r="BH142" t="n">
+        <v>0.33913</v>
+      </c>
+      <c r="BI142" t="n">
+        <v>0.34961</v>
+      </c>
+      <c r="BJ142" t="n">
+        <v>0.32338</v>
+      </c>
+      <c r="BK142" t="n">
+        <v>0.35661</v>
+      </c>
+      <c r="BL142" t="n">
+        <v>0.35858</v>
+      </c>
+      <c r="BM142" t="n">
+        <v>0.3304</v>
+      </c>
+      <c r="BN142" t="n">
+        <v>0.40963</v>
+      </c>
+      <c r="BO142" t="n">
+        <v>0.34586</v>
+      </c>
+      <c r="BP142" t="n">
+        <v>0.35002</v>
+      </c>
+      <c r="BQ142" t="n">
+        <v>0.37539</v>
+      </c>
+      <c r="BR142" t="n">
+        <v>0.46064</v>
+      </c>
+      <c r="BS142" t="n">
+        <v>0.42632</v>
+      </c>
+      <c r="BT142" t="n">
+        <v>0.40368</v>
+      </c>
+      <c r="BU142" t="n">
+        <v>0.38562</v>
+      </c>
+      <c r="BV142" t="n">
+        <v>0.35496</v>
+      </c>
+      <c r="BW142" t="n">
+        <v>0.36272</v>
+      </c>
+      <c r="BX142" t="n">
+        <v>0.38231</v>
+      </c>
+      <c r="BY142" t="n">
+        <v>0.45109</v>
+      </c>
+      <c r="BZ142" t="n">
+        <v>0.48092</v>
+      </c>
+      <c r="CA142" t="n">
+        <v>0.6196799999999999</v>
+      </c>
+      <c r="CB142" t="n">
+        <v>0.5578099999999999</v>
+      </c>
+      <c r="CC142" t="n">
+        <v>0.52685</v>
+      </c>
+      <c r="CD142" t="n">
+        <v>0.45428</v>
+      </c>
+      <c r="CE142" t="n">
+        <v>0.38313</v>
+      </c>
+      <c r="CF142" t="n">
+        <v>0.44681</v>
+      </c>
+      <c r="CG142" t="n">
+        <v>0.45619</v>
+      </c>
+      <c r="CH142" t="n">
+        <v>1.06019</v>
+      </c>
+      <c r="CI142" t="n">
+        <v>1.29963</v>
+      </c>
+      <c r="CJ142" t="n">
+        <v>0.98442</v>
+      </c>
+      <c r="CK142" t="n">
+        <v>0.5401900000000001</v>
+      </c>
+      <c r="CL142" t="n">
+        <v>0.99005</v>
+      </c>
+      <c r="CM142" t="n">
+        <v>1.12263</v>
+      </c>
+      <c r="CN142" t="n">
+        <v>1.05152</v>
+      </c>
+      <c r="CO142" t="n">
+        <v>0.78485</v>
+      </c>
+      <c r="CP142" t="n">
+        <v>0.7551100000000001</v>
+      </c>
+      <c r="CQ142" t="n">
+        <v>0.49896</v>
+      </c>
+      <c r="CR142" t="n">
+        <v>0.49433</v>
+      </c>
+      <c r="CS142" t="n">
+        <v>0.44466</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="n">
+        <v>46166</v>
+      </c>
+      <c r="B143" t="n">
+        <v>0.34816</v>
+      </c>
+      <c r="C143" t="n">
+        <v>0.73049</v>
+      </c>
+      <c r="D143" t="n">
+        <v>0.4412</v>
+      </c>
+      <c r="E143" t="n">
+        <v>0.3648</v>
+      </c>
+      <c r="F143" t="n">
+        <v>0.37131</v>
+      </c>
+      <c r="G143" t="n">
+        <v>0.37558</v>
+      </c>
+      <c r="H143" t="n">
+        <v>0.37395</v>
+      </c>
+      <c r="I143" t="n">
+        <v>0.36642</v>
+      </c>
+      <c r="J143" t="n">
+        <v>0.36831</v>
+      </c>
+      <c r="K143" t="n">
+        <v>0.36145</v>
+      </c>
+      <c r="L143" t="n">
+        <v>0.36691</v>
+      </c>
+      <c r="M143" t="n">
+        <v>0.35764</v>
+      </c>
+      <c r="N143" t="n">
+        <v>0.3594</v>
+      </c>
+      <c r="O143" t="n">
+        <v>0.36175</v>
+      </c>
+      <c r="P143" t="n">
+        <v>0.3521</v>
+      </c>
+      <c r="Q143" t="n">
+        <v>0.36488</v>
+      </c>
+      <c r="R143" t="n">
+        <v>0.35148</v>
+      </c>
+      <c r="S143" t="n">
+        <v>0.35687</v>
+      </c>
+      <c r="T143" t="n">
+        <v>0.35579</v>
+      </c>
+      <c r="U143" t="n">
+        <v>0.35665</v>
+      </c>
+      <c r="V143" t="n">
+        <v>0.35256</v>
+      </c>
+      <c r="W143" t="n">
+        <v>0.35287</v>
+      </c>
+      <c r="X143" t="n">
+        <v>0.35505</v>
+      </c>
+      <c r="Y143" t="n">
+        <v>0.35382</v>
+      </c>
+      <c r="Z143" t="n">
+        <v>0.35638</v>
+      </c>
+      <c r="AA143" t="n">
+        <v>0.34774</v>
+      </c>
+      <c r="AB143" t="n">
+        <v>0.34219</v>
+      </c>
+      <c r="AC143" t="n">
+        <v>0.35408</v>
+      </c>
+      <c r="AD143" t="n">
+        <v>0.34833</v>
+      </c>
+      <c r="AE143" t="n">
+        <v>0.34876</v>
+      </c>
+      <c r="AF143" t="n">
+        <v>0.31223</v>
+      </c>
+      <c r="AG143" t="n">
+        <v>0.31703</v>
+      </c>
+      <c r="AH143" t="n">
+        <v>0.31798</v>
+      </c>
+      <c r="AI143" t="n">
+        <v>0.17542</v>
+      </c>
+      <c r="AJ143" t="n">
+        <v>0.30647</v>
+      </c>
+      <c r="AK143" t="n">
+        <v>0.2943</v>
+      </c>
+      <c r="AL143" t="n">
+        <v>0.3103399999999999</v>
+      </c>
+      <c r="AM143" t="n">
+        <v>0.14511</v>
+      </c>
+      <c r="AN143" t="n">
+        <v>0.19771</v>
+      </c>
+      <c r="AO143" t="n">
+        <v>0.14155</v>
+      </c>
+      <c r="AP143" t="n">
+        <v>0.2921</v>
+      </c>
+      <c r="AQ143" t="n">
+        <v>0.04421</v>
+      </c>
+      <c r="AR143" t="n">
+        <v>0.12219</v>
+      </c>
+      <c r="AS143" t="n">
+        <v>0.3309</v>
+      </c>
+      <c r="AT143" t="n">
+        <v>0.22737</v>
+      </c>
+      <c r="AU143" t="n">
+        <v>0.26887</v>
+      </c>
+      <c r="AV143" t="n">
+        <v>0.2849</v>
+      </c>
+      <c r="AW143" t="n">
+        <v>0.4329</v>
+      </c>
+      <c r="AX143" t="n">
+        <v>0.36896</v>
+      </c>
+      <c r="AY143" t="n">
+        <v>0.44245</v>
+      </c>
+      <c r="AZ143" t="n">
+        <v>0.62483</v>
+      </c>
+      <c r="BA143" t="n">
+        <v>0.44359</v>
+      </c>
+      <c r="BB143" t="n">
+        <v>1.04914</v>
+      </c>
+      <c r="BC143" t="n">
+        <v>0.4711</v>
+      </c>
+      <c r="BD143" t="n">
+        <v>0.6736599999999999</v>
+      </c>
+      <c r="BE143" t="n">
+        <v>0.62575</v>
+      </c>
+      <c r="BF143" t="n">
+        <v>0.47007</v>
+      </c>
+      <c r="BG143" t="n">
+        <v>0.6357699999999999</v>
+      </c>
+      <c r="BH143" t="n">
+        <v>0.61625</v>
+      </c>
+      <c r="BI143" t="n">
+        <v>0.51475</v>
+      </c>
+      <c r="BJ143" t="n">
+        <v>0.46068</v>
+      </c>
+      <c r="BK143" t="n">
+        <v>0.5974299999999999</v>
+      </c>
+      <c r="BL143" t="n">
+        <v>0.7464299999999999</v>
+      </c>
+      <c r="BM143" t="n">
+        <v>0.6407999999999999</v>
+      </c>
+      <c r="BN143" t="n">
+        <v>0.63932</v>
+      </c>
+      <c r="BO143" t="n">
+        <v>0.7487200000000001</v>
+      </c>
+      <c r="BP143" t="n">
+        <v>0.61656</v>
+      </c>
+      <c r="BQ143" t="n">
+        <v>0.6543300000000001</v>
+      </c>
+      <c r="BR143" t="n">
+        <v>0.6659299999999999</v>
+      </c>
+      <c r="BS143" t="n">
+        <v>0.66153</v>
+      </c>
+      <c r="BT143" t="n">
+        <v>0.73498</v>
+      </c>
+      <c r="BU143" t="n">
+        <v>0.746</v>
+      </c>
+      <c r="BV143" t="n">
+        <v>0.7649900000000001</v>
+      </c>
+      <c r="BW143" t="n">
+        <v>0.70917</v>
+      </c>
+      <c r="BX143" t="n">
+        <v>1.30229</v>
+      </c>
+      <c r="BY143" t="n">
+        <v>1.02006</v>
+      </c>
+      <c r="BZ143" t="n">
+        <v>0.83788</v>
+      </c>
+      <c r="CA143" t="n">
+        <v>1.634</v>
+      </c>
+      <c r="CB143" t="n">
+        <v>0.67171</v>
+      </c>
+      <c r="CC143" t="n">
+        <v>0.75409</v>
+      </c>
+      <c r="CD143" t="n">
+        <v>1.0371</v>
+      </c>
+      <c r="CE143" t="n">
+        <v>0.5431</v>
+      </c>
+      <c r="CF143" t="n">
+        <v>0.46032</v>
+      </c>
+      <c r="CG143" t="n">
+        <v>0.38485</v>
+      </c>
+      <c r="CH143" t="n">
+        <v>0.39507</v>
+      </c>
+      <c r="CI143" t="n">
+        <v>0.46016</v>
+      </c>
+      <c r="CJ143" t="n">
+        <v>0.38641</v>
+      </c>
+      <c r="CK143" t="n">
+        <v>0.5008</v>
+      </c>
+      <c r="CL143" t="n">
+        <v>0.39647</v>
+      </c>
+      <c r="CM143" t="n">
+        <v>0.51923</v>
+      </c>
+      <c r="CN143" t="n">
+        <v>0.46036</v>
+      </c>
+      <c r="CO143" t="n">
+        <v>0.46156</v>
+      </c>
+      <c r="CP143" t="n">
+        <v>0.4863</v>
+      </c>
+      <c r="CQ143" t="n">
+        <v>0.38594</v>
+      </c>
+      <c r="CR143" t="n">
+        <v>0.38263</v>
+      </c>
+      <c r="CS143" t="n">
+        <v>0.38366</v>
       </c>
     </row>
   </sheetData>
